--- a/data/outputSpecialityRpt/File1/RPT_RPT8270621607594XL_outputSpecialityRpt.xlsx
+++ b/data/outputSpecialityRpt/File1/RPT_RPT8270621607594XL_outputSpecialityRpt.xlsx
@@ -901,7 +901,7 @@
       </c>
       <c r="P15" s="14" t="inlineStr">
         <is>
-          <t>$33321.01171159887</t>
+          <t>$33321.01171159886</t>
         </is>
       </c>
       <c r="Q15" s="14" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="R15" s="14" t="inlineStr">
         <is>
-          <t>$38007.16259473113</t>
+          <t>$38007.162594731126</t>
         </is>
       </c>
       <c r="S15" s="14" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T15" s="14" t="inlineStr">
         <is>
-          <t>$43117.811607133706</t>
+          <t>$43117.81160713372</t>
         </is>
       </c>
       <c r="U15" s="14" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="P16" s="14" t="inlineStr">
         <is>
-          <t>$177712.2566933077</t>
+          <t>$177712.25669330766</t>
         </is>
       </c>
       <c r="Q16" s="14" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="R16" s="14" t="inlineStr">
         <is>
-          <t>$202705.0887193798</t>
+          <t>$202705.08871937977</t>
         </is>
       </c>
       <c r="S16" s="14" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="T16" s="14" t="inlineStr">
         <is>
-          <t>$229961.91324266806</t>
+          <t>$229961.91324266812</t>
         </is>
       </c>
       <c r="U16" s="14" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="P17" s="14" t="inlineStr">
         <is>
-          <t>$44427.99133653428</t>
+          <t>$44427.99133653427</t>
         </is>
       </c>
       <c r="Q17" s="14" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="R17" s="14" t="inlineStr">
         <is>
-          <t>$50676.1890995398</t>
+          <t>$50676.18909953979</t>
         </is>
       </c>
       <c r="S17" s="14" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="T17" s="14" t="inlineStr">
         <is>
-          <t>$57490.3840589339</t>
+          <t>$57490.384058933916</t>
         </is>
       </c>
       <c r="U17" s="14" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="P18" s="14" t="inlineStr">
         <is>
-          <t>$363779.0504214811</t>
+          <t>$363779.05042148096</t>
         </is>
       </c>
       <c r="Q18" s="14" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="R18" s="14" t="inlineStr">
         <is>
-          <t>$451191.09679834585</t>
+          <t>$451191.09679834574</t>
         </is>
       </c>
       <c r="S18" s="14" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="T18" s="14" t="inlineStr">
         <is>
-          <t>$515593.3584332429</t>
+          <t>$515593.358433243</t>
         </is>
       </c>
       <c r="U18" s="14" t="inlineStr">
@@ -1446,7 +1446,7 @@
         <v>23.87978643933828</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>25.39240224959826</v>
+        <v>25.39240224959827</v>
       </c>
       <c r="M19" s="14" t="n">
         <v>26.77367021497039</v>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="P19" s="14" t="inlineStr">
         <is>
-          <t>$503694.0698143584</t>
+          <t>$503694.06981435826</t>
         </is>
       </c>
       <c r="Q19" s="14" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="R19" s="14" t="inlineStr">
         <is>
-          <t>$624726.1340284788</t>
+          <t>$624726.1340284786</t>
         </is>
       </c>
       <c r="S19" s="14" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="T19" s="14" t="inlineStr">
         <is>
-          <t>$713898.4962921822</t>
+          <t>$713898.4962921824</t>
         </is>
       </c>
       <c r="U19" s="14" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="P20" s="14" t="inlineStr">
         <is>
-          <t>$391762.05430005654</t>
+          <t>$391762.0543000564</t>
         </is>
       </c>
       <c r="Q20" s="14" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="R20" s="14" t="inlineStr">
         <is>
-          <t>$485898.10424437246</t>
+          <t>$485898.10424437234</t>
         </is>
       </c>
       <c r="S20" s="14" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="T20" s="14" t="inlineStr">
         <is>
-          <t>$555254.3860050307</t>
+          <t>$555254.3860050308</t>
         </is>
       </c>
       <c r="U20" s="14" t="inlineStr">
@@ -1741,7 +1741,7 @@
       </c>
       <c r="P21" s="14" t="inlineStr">
         <is>
-          <t>$83032.35030152061</t>
+          <t>$83032.35030152058</t>
         </is>
       </c>
       <c r="Q21" s="14" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="R21" s="14" t="inlineStr">
         <is>
-          <t>$94387.50918785362</t>
+          <t>$94387.5091878536</t>
         </is>
       </c>
       <c r="S21" s="14" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="T21" s="14" t="inlineStr">
         <is>
-          <t>$105675.85731811718</t>
+          <t>$105675.85731811721</t>
         </is>
       </c>
       <c r="U21" s="14" t="inlineStr">
@@ -1866,7 +1866,7 @@
         <v>1.222269840927197</v>
       </c>
       <c r="L22" s="14" t="n">
-        <v>1.260840983798665</v>
+        <v>1.260840983798666</v>
       </c>
       <c r="M22" s="14" t="n">
         <v>1.287823858462521</v>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="P22" s="14" t="inlineStr">
         <is>
-          <t>$6566.756130182277</t>
+          <t>$6566.756130182275</t>
         </is>
       </c>
       <c r="Q22" s="14" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="R22" s="14" t="inlineStr">
         <is>
-          <t>$7670.9265087141275</t>
+          <t>$7670.926508714127</t>
         </is>
       </c>
       <c r="S22" s="14" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="T22" s="14" t="inlineStr">
         <is>
-          <t>$8822.806026187467</t>
+          <t>$8822.806026187469</t>
         </is>
       </c>
       <c r="U22" s="14" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="P23" s="14" t="inlineStr">
         <is>
-          <t>$88283.51738287356</t>
+          <t>$88283.51738287353</t>
         </is>
       </c>
       <c r="Q23" s="14" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="R23" s="14" t="inlineStr">
         <is>
-          <t>$99224.27733361436</t>
+          <t>$99224.27733361433</t>
         </is>
       </c>
       <c r="S23" s="14" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="T23" s="14" t="inlineStr">
         <is>
-          <t>$110309.82544890202</t>
+          <t>$110309.82544890203</t>
         </is>
       </c>
       <c r="U23" s="14" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="P24" s="14" t="inlineStr">
         <is>
-          <t>$132425.0569733473</t>
+          <t>$132425.05697334727</t>
         </is>
       </c>
       <c r="Q24" s="14" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="R24" s="14" t="inlineStr">
         <is>
-          <t>$148836.16974681313</t>
+          <t>$148836.1697468131</t>
         </is>
       </c>
       <c r="S24" s="14" t="inlineStr">
@@ -2181,7 +2181,7 @@
       </c>
       <c r="T24" s="14" t="inlineStr">
         <is>
-          <t>$165464.46440776574</t>
+          <t>$165464.46440776577</t>
         </is>
       </c>
       <c r="U24" s="14" t="inlineStr">
@@ -2286,7 +2286,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L25" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M25" s="14" t="n">
         <v>3.66733174555146</v>
@@ -2301,7 +2301,7 @@
       </c>
       <c r="P25" s="14" t="inlineStr">
         <is>
-          <t>$26995.153468236465</t>
+          <t>$26995.15346823646</t>
         </is>
       </c>
       <c r="Q25" s="14" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="R25" s="14" t="inlineStr">
         <is>
-          <t>$31239.960609559417</t>
+          <t>$31239.96060955941</t>
         </is>
       </c>
       <c r="S25" s="14" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="T25" s="14" t="inlineStr">
         <is>
-          <t>$35533.462980352066</t>
+          <t>$35533.46298035207</t>
         </is>
       </c>
       <c r="U25" s="14" t="inlineStr">
@@ -2426,7 +2426,7 @@
         <v>19.80466702738677</v>
       </c>
       <c r="L26" s="14" t="n">
-        <v>20.35350642293612</v>
+        <v>20.35350642293613</v>
       </c>
       <c r="M26" s="14" t="n">
         <v>20.78154655812494</v>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="P26" s="14" t="inlineStr">
         <is>
-          <t>$152972.53632000662</t>
+          <t>$152972.5363200066</t>
         </is>
       </c>
       <c r="Q26" s="14" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="R26" s="14" t="inlineStr">
         <is>
-          <t>$177026.44345417002</t>
+          <t>$177026.44345416996</t>
         </is>
       </c>
       <c r="S26" s="14" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="T26" s="14" t="inlineStr">
         <is>
-          <t>$201356.29022199503</t>
+          <t>$201356.2902219951</t>
         </is>
       </c>
       <c r="U26" s="14" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="P27" s="14" t="inlineStr">
         <is>
-          <t>$16385.78980596899</t>
+          <t>$16385.789805968987</t>
         </is>
       </c>
       <c r="Q27" s="14" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>$8153.40925268488</t>
+          <t>$8153.409252684878</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="T27" s="14" t="inlineStr">
         <is>
-          <t>$8453.870616915803</t>
+          <t>$8453.870616915805</t>
         </is>
       </c>
       <c r="U27" s="14" t="inlineStr">
@@ -2706,7 +2706,7 @@
         <v>9.807048887442321</v>
       </c>
       <c r="L28" s="14" t="n">
-        <v>9.770930626880061</v>
+        <v>9.770930626880062</v>
       </c>
       <c r="M28" s="14" t="n">
         <v>9.704974973807753</v>
@@ -2721,7 +2721,7 @@
       </c>
       <c r="P28" s="14" t="inlineStr">
         <is>
-          <t>$24003.167239927592</t>
+          <t>$24003.167239927585</t>
         </is>
       </c>
       <c r="Q28" s="14" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="R28" s="14" t="inlineStr">
         <is>
-          <t>$26373.182380373564</t>
+          <t>$26373.182380373557</t>
         </is>
       </c>
       <c r="S28" s="14" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="T28" s="14" t="inlineStr">
         <is>
-          <t>$28487.305365803793</t>
+          <t>$28487.3053658038</t>
         </is>
       </c>
       <c r="U28" s="14" t="inlineStr">
@@ -2846,7 +2846,7 @@
         <v>11.19694438880214</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>11.67482506052711</v>
+        <v>11.67482506052712</v>
       </c>
       <c r="M29" s="14" t="n">
         <v>12.14522037828074</v>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="P29" s="14" t="inlineStr">
         <is>
-          <t>$48868.06394451132</t>
+          <t>$48868.063944511305</t>
         </is>
       </c>
       <c r="Q29" s="14" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="R29" s="14" t="inlineStr">
         <is>
-          <t>$58765.23903389736</t>
+          <t>$58765.23903389735</t>
         </is>
       </c>
       <c r="S29" s="14" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="T29" s="14" t="inlineStr">
         <is>
-          <t>$69638.14904232719</t>
+          <t>$69638.1490423272</t>
         </is>
       </c>
       <c r="U29" s="14" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="P30" s="14" t="inlineStr">
         <is>
-          <t>$3128.3138608207587</t>
+          <t>$3128.3138608207582</t>
         </is>
       </c>
       <c r="Q30" s="14" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="R30" s="14" t="inlineStr">
         <is>
-          <t>$3322.922979430419</t>
+          <t>$3322.9229794304183</t>
         </is>
       </c>
       <c r="S30" s="14" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="T30" s="14" t="inlineStr">
         <is>
-          <t>$3527.054336882328</t>
+          <t>$3527.0543368823287</t>
         </is>
       </c>
       <c r="U30" s="14" t="inlineStr">
@@ -3126,7 +3126,7 @@
         <v>9.319843307005538</v>
       </c>
       <c r="L31" s="14" t="n">
-        <v>9.578120669616998</v>
+        <v>9.578120669617</v>
       </c>
       <c r="M31" s="14" t="n">
         <v>9.779551321470558</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="P31" s="14" t="inlineStr">
         <is>
-          <t>$58003.86370829593</t>
+          <t>$58003.86370829592</t>
         </is>
       </c>
       <c r="Q31" s="14" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="R31" s="14" t="inlineStr">
         <is>
-          <t>$67453.62753784604</t>
+          <t>$67453.62753784603</t>
         </is>
       </c>
       <c r="S31" s="14" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="T31" s="14" t="inlineStr">
         <is>
-          <t>$77220.79923193462</t>
+          <t>$77220.79923193464</t>
         </is>
       </c>
       <c r="U31" s="14" t="inlineStr">
@@ -3266,7 +3266,7 @@
         <v>186.9826099239073</v>
       </c>
       <c r="L32" s="14" t="n">
-        <v>228.5736963756866</v>
+        <v>228.5736963756867</v>
       </c>
       <c r="M32" s="14" t="n">
         <v>277.5987652566804</v>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="P32" s="14" t="inlineStr">
         <is>
-          <t>$890243.1112663884</t>
+          <t>$890243.1112663882</t>
         </is>
       </c>
       <c r="Q32" s="14" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="R32" s="14" t="inlineStr">
         <is>
-          <t>$1456601.297341989</t>
+          <t>$1456601.2973419884</t>
         </is>
       </c>
       <c r="S32" s="14" t="inlineStr">
@@ -3301,7 +3301,7 @@
       </c>
       <c r="T32" s="14" t="inlineStr">
         <is>
-          <t>$2279217.1859847023</t>
+          <t>$2279217.185984703</t>
         </is>
       </c>
       <c r="U32" s="14" t="inlineStr">
@@ -3406,7 +3406,7 @@
         <v>446.0549007823332</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>545.2721913540475</v>
+        <v>545.2721913540477</v>
       </c>
       <c r="M33" s="14" t="n">
         <v>662.2235604918401</v>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P33" s="14" t="inlineStr">
         <is>
-          <t>$2136583.4670393327</t>
+          <t>$2136583.4670393323</t>
         </is>
       </c>
       <c r="Q33" s="14" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="R33" s="14" t="inlineStr">
         <is>
-          <t>$3495843.113620773</t>
+          <t>$3495843.1136207725</t>
         </is>
       </c>
       <c r="S33" s="14" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="T33" s="14" t="inlineStr">
         <is>
-          <t>$5470121.246363285</t>
+          <t>$5470121.246363286</t>
         </is>
       </c>
       <c r="U33" s="14" t="inlineStr">
@@ -3546,7 +3546,7 @@
         <v>15.76961770442592</v>
       </c>
       <c r="L34" s="14" t="n">
-        <v>19.27729969433501</v>
+        <v>19.27729969433502</v>
       </c>
       <c r="M34" s="14" t="n">
         <v>23.41194405779233</v>
@@ -3561,7 +3561,7 @@
       </c>
       <c r="P34" s="14" t="inlineStr">
         <is>
-          <t>$65596.86085622868</t>
+          <t>$65596.86085622867</t>
         </is>
       </c>
       <c r="Q34" s="14" t="inlineStr">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="R34" s="14" t="inlineStr">
         <is>
-          <t>$107328.51668891322</t>
+          <t>$107328.5166889132</t>
         </is>
       </c>
       <c r="S34" s="14" t="inlineStr">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="T34" s="14" t="inlineStr">
         <is>
-          <t>$167942.31903404833</t>
+          <t>$167942.31903404836</t>
         </is>
       </c>
       <c r="U34" s="14" t="inlineStr">
@@ -3686,7 +3686,7 @@
         <v>4.659921653502769</v>
       </c>
       <c r="L35" s="14" t="n">
-        <v>4.789060334808499</v>
+        <v>4.7890603348085</v>
       </c>
       <c r="M35" s="14" t="n">
         <v>4.889775660735279</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="P35" s="14" t="inlineStr">
         <is>
-          <t>$29001.931854147966</t>
+          <t>$29001.93185414796</t>
         </is>
       </c>
       <c r="Q35" s="14" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="R35" s="14" t="inlineStr">
         <is>
-          <t>$33726.81376892302</t>
+          <t>$33726.81376892301</t>
         </is>
       </c>
       <c r="S35" s="14" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="T35" s="14" t="inlineStr">
         <is>
-          <t>$38610.39961596731</t>
+          <t>$38610.39961596732</t>
         </is>
       </c>
       <c r="U35" s="14" t="inlineStr">
@@ -3841,7 +3841,7 @@
       </c>
       <c r="P36" s="14" t="inlineStr">
         <is>
-          <t>$153370.9406260089</t>
+          <t>$153370.94062600887</t>
         </is>
       </c>
       <c r="Q36" s="14" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="R36" s="14" t="inlineStr">
         <is>
-          <t>$186966.56434829708</t>
+          <t>$186966.56434829705</t>
         </is>
       </c>
       <c r="S36" s="14" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="T36" s="14" t="inlineStr">
         <is>
-          <t>$225758.74629704715</t>
+          <t>$225758.7462970472</t>
         </is>
       </c>
       <c r="U36" s="14" t="inlineStr">
@@ -4246,7 +4246,7 @@
         <v>8.783914110750151</v>
       </c>
       <c r="L39" s="14" t="n">
-        <v>7.313152916785685</v>
+        <v>7.313152916785686</v>
       </c>
       <c r="M39" s="14" t="n">
         <v>7.397862565620929</v>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="P39" s="14" t="inlineStr">
         <is>
-          <t>$373095.51448229817</t>
+          <t>$373095.5144822981</t>
         </is>
       </c>
       <c r="Q39" s="14" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="R39" s="14" t="inlineStr">
         <is>
-          <t>$199716.43405202028</t>
+          <t>$199716.43405202022</t>
         </is>
       </c>
       <c r="S39" s="14" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="T39" s="14" t="inlineStr">
         <is>
-          <t>$235865.4318193002</t>
+          <t>$235865.43181930025</t>
         </is>
       </c>
       <c r="U39" s="14" t="inlineStr">
@@ -4386,7 +4386,7 @@
         <v>4.620650232358479</v>
       </c>
       <c r="L40" s="14" t="n">
-        <v>4.684992260985136</v>
+        <v>4.684992260985137</v>
       </c>
       <c r="M40" s="14" t="n">
         <v>4.912076028773235</v>
@@ -4401,7 +4401,7 @@
       </c>
       <c r="P40" s="14" t="inlineStr">
         <is>
-          <t>$122663.79827906907</t>
+          <t>$122663.79827906904</t>
         </is>
       </c>
       <c r="Q40" s="14" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="R40" s="14" t="inlineStr">
         <is>
-          <t>$100925.68635762084</t>
+          <t>$100925.68635762083</t>
         </is>
       </c>
       <c r="S40" s="14" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="T40" s="14" t="inlineStr">
         <is>
-          <t>$117361.93008901176</t>
+          <t>$117361.93008901179</t>
         </is>
       </c>
       <c r="U40" s="14" t="inlineStr">
@@ -4526,7 +4526,7 @@
         <v>6.353394069492908</v>
       </c>
       <c r="L41" s="14" t="n">
-        <v>6.441864358854563</v>
+        <v>6.441864358854565</v>
       </c>
       <c r="M41" s="14" t="n">
         <v>6.754104539563198</v>
@@ -4541,7 +4541,7 @@
       </c>
       <c r="P41" s="14" t="inlineStr">
         <is>
-          <t>$162091.44772591273</t>
+          <t>$162091.44772591267</t>
         </is>
       </c>
       <c r="Q41" s="14" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="R41" s="14" t="inlineStr">
         <is>
-          <t>$133366.08554399898</t>
+          <t>$133366.08554399895</t>
         </is>
       </c>
       <c r="S41" s="14" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="T41" s="14" t="inlineStr">
         <is>
-          <t>$155085.40761762267</t>
+          <t>$155085.4076176227</t>
         </is>
       </c>
       <c r="U41" s="14" t="inlineStr">
@@ -4666,7 +4666,7 @@
         <v>5.306619208741842</v>
       </c>
       <c r="L42" s="14" t="n">
-        <v>5.64275605546628</v>
+        <v>5.642756055466282</v>
       </c>
       <c r="M42" s="14" t="n">
         <v>5.949704492215642</v>
@@ -4681,7 +4681,7 @@
       </c>
       <c r="P42" s="14" t="inlineStr">
         <is>
-          <t>$213468.8300190964</t>
+          <t>$213468.83001909635</t>
         </is>
       </c>
       <c r="Q42" s="14" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="R42" s="14" t="inlineStr">
         <is>
-          <t>$263275.0558998393</t>
+          <t>$263275.05589983927</t>
         </is>
       </c>
       <c r="S42" s="14" t="inlineStr">
@@ -4701,7 +4701,7 @@
       </c>
       <c r="T42" s="14" t="inlineStr">
         <is>
-          <t>$323416.8359217488</t>
+          <t>$323416.8359217489</t>
         </is>
       </c>
       <c r="U42" s="14" t="inlineStr">
@@ -4806,7 +4806,7 @@
         <v>5.573177990523304</v>
       </c>
       <c r="L43" s="14" t="n">
-        <v>6.049785155742874</v>
+        <v>6.049785155742875</v>
       </c>
       <c r="M43" s="14" t="n">
         <v>6.52447129963405</v>
@@ -4821,7 +4821,7 @@
       </c>
       <c r="P43" s="14" t="inlineStr">
         <is>
-          <t>$42950.2202399097</t>
+          <t>$42950.22023990969</t>
         </is>
       </c>
       <c r="Q43" s="14" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="R43" s="14" t="inlineStr">
         <is>
-          <t>$52358.38734170759</t>
+          <t>$52358.387341707574</t>
         </is>
       </c>
       <c r="S43" s="14" t="inlineStr">
@@ -4841,7 +4841,7 @@
       </c>
       <c r="T43" s="14" t="inlineStr">
         <is>
-          <t>$63221.80613202645</t>
+          <t>$63221.80613202647</t>
         </is>
       </c>
       <c r="U43" s="14" t="inlineStr">
@@ -4946,7 +4946,7 @@
         <v>12.12920685994101</v>
       </c>
       <c r="L44" s="14" t="n">
-        <v>12.29810468508598</v>
+        <v>12.29810468508599</v>
       </c>
       <c r="M44" s="14" t="n">
         <v>12.89419957552974</v>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="P44" s="14" t="inlineStr">
         <is>
-          <t>$331652.21334545536</t>
+          <t>$331652.2133454553</t>
         </is>
       </c>
       <c r="Q44" s="14" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="R44" s="14" t="inlineStr">
         <is>
-          <t>$272877.798776151</t>
+          <t>$272877.7987761509</t>
         </is>
       </c>
       <c r="S44" s="14" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="T44" s="14" t="inlineStr">
         <is>
-          <t>$317317.2885773674</t>
+          <t>$317317.28857736744</t>
         </is>
       </c>
       <c r="U44" s="14" t="inlineStr">
@@ -5086,7 +5086,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M45" s="14" t="n">
         <v>3.66733174555146</v>
@@ -5101,7 +5101,7 @@
       </c>
       <c r="P45" s="14" t="inlineStr">
         <is>
-          <t>$27320.4598062923</t>
+          <t>$27320.459806292292</t>
         </is>
       </c>
       <c r="Q45" s="14" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="R45" s="14" t="inlineStr">
         <is>
-          <t>$31692.927557094143</t>
+          <t>$31692.927557094135</t>
         </is>
       </c>
       <c r="S45" s="14" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="T45" s="14" t="inlineStr">
         <is>
-          <t>$36418.69005925874</t>
+          <t>$36418.69005925875</t>
         </is>
       </c>
       <c r="U45" s="14" t="inlineStr">
@@ -5241,7 +5241,7 @@
       </c>
       <c r="P46" s="14" t="inlineStr">
         <is>
-          <t>$63171.85016103911</t>
+          <t>$63171.850161039096</t>
         </is>
       </c>
       <c r="Q46" s="14" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="R46" s="14" t="inlineStr">
         <is>
-          <t>$51976.723576409706</t>
+          <t>$51976.7235764097</t>
         </is>
       </c>
       <c r="S46" s="14" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="T46" s="14" t="inlineStr">
         <is>
-          <t>$60441.388300450926</t>
+          <t>$60441.38830045094</t>
         </is>
       </c>
       <c r="U46" s="14" t="inlineStr">
@@ -5366,7 +5366,7 @@
         <v>10.48482372038123</v>
       </c>
       <c r="L47" s="14" t="n">
-        <v>5.945408884275103</v>
+        <v>5.945408884275105</v>
       </c>
       <c r="M47" s="14" t="n">
         <v>4.752953625528331</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="P47" s="14" t="inlineStr">
         <is>
-          <t>$102793.03706926366</t>
+          <t>$102793.03706926365</t>
         </is>
       </c>
       <c r="Q47" s="14" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="R47" s="14" t="inlineStr">
         <is>
-          <t>$64840.69132653351</t>
+          <t>$64840.691326533495</t>
         </is>
       </c>
       <c r="S47" s="14" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="T47" s="14" t="inlineStr">
         <is>
-          <t>$55381.83914614366</t>
+          <t>$55381.83914614368</t>
         </is>
       </c>
       <c r="U47" s="14" t="inlineStr">
@@ -5506,7 +5506,7 @@
         <v>9.241300464716959</v>
       </c>
       <c r="L48" s="14" t="n">
-        <v>9.369984521970272</v>
+        <v>9.369984521970274</v>
       </c>
       <c r="M48" s="14" t="n">
         <v>9.82415205754647</v>
@@ -5521,7 +5521,7 @@
       </c>
       <c r="P48" s="14" t="inlineStr">
         <is>
-          <t>$252687.40064415644</t>
+          <t>$252687.40064415638</t>
         </is>
       </c>
       <c r="Q48" s="14" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="R48" s="14" t="inlineStr">
         <is>
-          <t>$207906.89430563882</t>
+          <t>$207906.8943056388</t>
         </is>
       </c>
       <c r="S48" s="14" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="T48" s="14" t="inlineStr">
         <is>
-          <t>$241765.5532018037</t>
+          <t>$241765.55320180376</t>
         </is>
       </c>
       <c r="U48" s="14" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="P49" s="14" t="inlineStr">
         <is>
-          <t>$29551.08978197034</t>
+          <t>$29551.089781970335</t>
         </is>
       </c>
       <c r="Q49" s="14" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="R49" s="14" t="inlineStr">
         <is>
-          <t>$25529.596185354658</t>
+          <t>$25529.59618535465</t>
         </is>
       </c>
       <c r="S49" s="14" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="T49" s="14" t="inlineStr">
         <is>
-          <t>$28909.004329011834</t>
+          <t>$28909.00432901184</t>
         </is>
       </c>
       <c r="U49" s="14" t="inlineStr">
@@ -5786,7 +5786,7 @@
         <v>96.137320336527</v>
       </c>
       <c r="L50" s="14" t="n">
-        <v>57.58083421111565</v>
+        <v>57.58083421111566</v>
       </c>
       <c r="M50" s="14" t="n">
         <v>48.62129801762226</v>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="P50" s="14" t="inlineStr">
         <is>
-          <t>$4101565.266927432</t>
+          <t>$4101565.266927431</t>
         </is>
       </c>
       <c r="Q50" s="14" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="R50" s="14" t="inlineStr">
         <is>
-          <t>$2934250.9557610117</t>
+          <t>$2934250.955761011</t>
         </is>
       </c>
       <c r="S50" s="14" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="T50" s="14" t="inlineStr">
         <is>
-          <t>$2793039.8376069744</t>
+          <t>$2793039.837606975</t>
         </is>
       </c>
       <c r="U50" s="14" t="inlineStr">
@@ -6081,7 +6081,7 @@
       </c>
       <c r="P52" s="14" t="inlineStr">
         <is>
-          <t>$50200.367611740796</t>
+          <t>$50200.36761174078</t>
         </is>
       </c>
       <c r="Q52" s="14" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="R52" s="14" t="inlineStr">
         <is>
-          <t>$49769.24642578683</t>
+          <t>$49769.24642578682</t>
         </is>
       </c>
       <c r="S52" s="14" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="T52" s="14" t="inlineStr">
         <is>
-          <t>$51883.1491933743</t>
+          <t>$51883.14919337432</t>
         </is>
       </c>
       <c r="U52" s="14" t="inlineStr">
@@ -6221,7 +6221,7 @@
       </c>
       <c r="P53" s="14" t="inlineStr">
         <is>
-          <t>$8366.691002415633</t>
+          <t>$8366.691002415631</t>
         </is>
       </c>
       <c r="Q53" s="14" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="R53" s="14" t="inlineStr">
         <is>
-          <t>$8294.837788603149</t>
+          <t>$8294.837788603145</t>
         </is>
       </c>
       <c r="S53" s="14" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="T53" s="14" t="inlineStr">
         <is>
-          <t>$8647.153361316585</t>
+          <t>$8647.153361316587</t>
         </is>
       </c>
       <c r="U53" s="14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="P54" s="14" t="inlineStr">
         <is>
-          <t>$34116.67695148236</t>
+          <t>$34116.67695148235</t>
         </is>
       </c>
       <c r="Q54" s="14" t="inlineStr">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="R54" s="14" t="inlineStr">
         <is>
-          <t>$50439.2560296432</t>
+          <t>$50439.256029643184</t>
         </is>
       </c>
       <c r="S54" s="14" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="T54" s="14" t="inlineStr">
         <is>
-          <t>$75374.74535501502</t>
+          <t>$75374.74535501504</t>
         </is>
       </c>
       <c r="U54" s="14" t="inlineStr">
@@ -6501,7 +6501,7 @@
       </c>
       <c r="P55" s="14" t="inlineStr">
         <is>
-          <t>$1238270.2683575137</t>
+          <t>$1238270.2683575135</t>
         </is>
       </c>
       <c r="Q55" s="14" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="R55" s="14" t="inlineStr">
         <is>
-          <t>$1227635.9927132658</t>
+          <t>$1227635.9927132656</t>
         </is>
       </c>
       <c r="S55" s="14" t="inlineStr">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="T55" s="14" t="inlineStr">
         <is>
-          <t>$1279778.6974748548</t>
+          <t>$1279778.697474855</t>
         </is>
       </c>
       <c r="U55" s="14" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="P56" s="14" t="inlineStr">
         <is>
-          <t>$748.9421868166627</t>
+          <t>$748.9421868166626</t>
         </is>
       </c>
       <c r="Q56" s="14" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="R56" s="14" t="inlineStr">
         <is>
-          <t>$917.9259160030039</t>
+          <t>$917.9259160030036</t>
         </is>
       </c>
       <c r="S56" s="14" t="inlineStr">
@@ -6661,7 +6661,7 @@
       </c>
       <c r="T56" s="14" t="inlineStr">
         <is>
-          <t>$1116.8827365578654</t>
+          <t>$1116.8827365578657</t>
         </is>
       </c>
       <c r="U56" s="14" t="inlineStr">
@@ -6766,7 +6766,7 @@
         <v>2.653309604370921</v>
       </c>
       <c r="L57" s="14" t="n">
-        <v>2.82137802773314</v>
+        <v>2.821378027733141</v>
       </c>
       <c r="M57" s="14" t="n">
         <v>2.974852246107821</v>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="P57" s="14" t="inlineStr">
         <is>
-          <t>$8771.034891302766</t>
+          <t>$8771.034891302765</t>
         </is>
       </c>
       <c r="Q57" s="14" t="inlineStr">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="R57" s="14" t="inlineStr">
         <is>
-          <t>$10749.743792148673</t>
+          <t>$10749.74379214867</t>
         </is>
       </c>
       <c r="S57" s="14" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="T57" s="14" t="inlineStr">
         <is>
-          <t>$13079.208250784488</t>
+          <t>$13079.208250784492</t>
         </is>
       </c>
       <c r="U57" s="14" t="inlineStr">
@@ -6921,7 +6921,7 @@
       </c>
       <c r="P58" s="14" t="inlineStr">
         <is>
-          <t>$25677.61543570635</t>
+          <t>$25677.615435706346</t>
         </is>
       </c>
       <c r="Q58" s="14" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="R58" s="14" t="inlineStr">
         <is>
-          <t>$31472.006054334426</t>
+          <t>$31472.00605433442</t>
         </is>
       </c>
       <c r="S58" s="14" t="inlineStr">
@@ -6941,7 +6941,7 @@
       </c>
       <c r="T58" s="14" t="inlineStr">
         <is>
-          <t>$38293.58560579291</t>
+          <t>$38293.58560579292</t>
         </is>
       </c>
       <c r="U58" s="14" t="inlineStr">
@@ -7046,7 +7046,7 @@
         <v>27.85975084589467</v>
       </c>
       <c r="L59" s="14" t="n">
-        <v>29.62446929119797</v>
+        <v>29.62446929119798</v>
       </c>
       <c r="M59" s="14" t="n">
         <v>31.23594858413212</v>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="P59" s="14" t="inlineStr">
         <is>
-          <t>$216002.13538648112</t>
+          <t>$216002.13538648107</t>
         </is>
       </c>
       <c r="Q59" s="14" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="R59" s="14" t="inlineStr">
         <is>
-          <t>$253150.92180195526</t>
+          <t>$253150.9218019552</t>
         </is>
       </c>
       <c r="S59" s="14" t="inlineStr">
@@ -7081,7 +7081,7 @@
       </c>
       <c r="T59" s="14" t="inlineStr">
         <is>
-          <t>$292184.81705485587</t>
+          <t>$292184.8170548559</t>
         </is>
       </c>
       <c r="U59" s="14" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="P60" s="14" t="inlineStr">
         <is>
-          <t>$5542.085484265061</t>
+          <t>$5542.085484265059</t>
         </is>
       </c>
       <c r="Q60" s="14" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="R60" s="14" t="inlineStr">
         <is>
-          <t>$6792.70816058278</t>
+          <t>$6792.708160582778</t>
         </is>
       </c>
       <c r="S60" s="14" t="inlineStr">
@@ -7221,7 +7221,7 @@
       </c>
       <c r="T60" s="14" t="inlineStr">
         <is>
-          <t>$8265.032454345906</t>
+          <t>$8265.032454345908</t>
         </is>
       </c>
       <c r="U60" s="14" t="inlineStr">
@@ -7606,7 +7606,7 @@
         <v>6.506561563915875</v>
       </c>
       <c r="L63" s="14" t="n">
-        <v>7.762911693947747</v>
+        <v>7.762911693947749</v>
       </c>
       <c r="M63" s="14" t="n">
         <v>9.201616483597221</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="P63" s="14" t="inlineStr">
         <is>
-          <t>$166744.71100114577</t>
+          <t>$166744.7110011457</t>
         </is>
       </c>
       <c r="Q63" s="14" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="R63" s="14" t="inlineStr">
         <is>
-          <t>$271250.99669750367</t>
+          <t>$271250.9966975036</t>
         </is>
       </c>
       <c r="S63" s="14" t="inlineStr">
@@ -7641,7 +7641,7 @@
       </c>
       <c r="T63" s="14" t="inlineStr">
         <is>
-          <t>$428336.65834230196</t>
+          <t>$428336.6583423021</t>
         </is>
       </c>
       <c r="U63" s="14" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="P64" s="14" t="inlineStr">
         <is>
-          <t>$555815.7034148725</t>
+          <t>$555815.7034148724</t>
         </is>
       </c>
       <c r="Q64" s="14" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="R64" s="14" t="inlineStr">
         <is>
-          <t>$904169.9891181093</t>
+          <t>$904169.9891181091</t>
         </is>
       </c>
       <c r="S64" s="14" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="T64" s="14" t="inlineStr">
         <is>
-          <t>$1427788.8613406548</t>
+          <t>$1427788.861340655</t>
         </is>
       </c>
       <c r="U64" s="14" t="inlineStr">
@@ -7886,7 +7886,7 @@
         <v>19.51968469174763</v>
       </c>
       <c r="L65" s="14" t="n">
-        <v>23.28873508184324</v>
+        <v>23.28873508184325</v>
       </c>
       <c r="M65" s="14" t="n">
         <v>27.60484945079166</v>
@@ -7901,7 +7901,7 @@
       </c>
       <c r="P65" s="14" t="inlineStr">
         <is>
-          <t>$500234.13286354154</t>
+          <t>$500234.1328635414</t>
         </is>
       </c>
       <c r="Q65" s="14" t="inlineStr">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="R65" s="14" t="inlineStr">
         <is>
-          <t>$813752.9898649362</t>
+          <t>$813752.989864936</t>
         </is>
       </c>
       <c r="S65" s="14" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="T65" s="14" t="inlineStr">
         <is>
-          <t>$1285009.9746675394</t>
+          <t>$1285009.9746675396</t>
         </is>
       </c>
       <c r="U65" s="14" t="inlineStr">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="P66" s="14" t="inlineStr">
         <is>
-          <t>$16733.422301649065</t>
+          <t>$16733.42230164906</t>
         </is>
       </c>
       <c r="Q66" s="14" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="R66" s="14" t="inlineStr">
         <is>
-          <t>$16589.71552795468</t>
+          <t>$16589.715527954675</t>
         </is>
       </c>
       <c r="S66" s="14" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="T66" s="14" t="inlineStr">
         <is>
-          <t>$17294.348370252686</t>
+          <t>$17294.34837025269</t>
         </is>
       </c>
       <c r="U66" s="14" t="inlineStr">
@@ -8166,7 +8166,7 @@
         <v>71.57217720307463</v>
       </c>
       <c r="L67" s="14" t="n">
-        <v>85.39202863342521</v>
+        <v>85.39202863342523</v>
       </c>
       <c r="M67" s="14" t="n">
         <v>101.2177813195694</v>
@@ -8181,7 +8181,7 @@
       </c>
       <c r="P67" s="14" t="inlineStr">
         <is>
-          <t>$1772491.5460577162</t>
+          <t>$1772491.546057716</t>
         </is>
       </c>
       <c r="Q67" s="14" t="inlineStr">
@@ -8191,7 +8191,7 @@
       </c>
       <c r="R67" s="14" t="inlineStr">
         <is>
-          <t>$2748129.6794221746</t>
+          <t>$2748129.679422174</t>
         </is>
       </c>
       <c r="S67" s="14" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="T67" s="14" t="inlineStr">
         <is>
-          <t>$4136041.6049082903</t>
+          <t>$4136041.6049082913</t>
         </is>
       </c>
       <c r="U67" s="14" t="inlineStr">
@@ -8306,7 +8306,7 @@
         <v>86.754154185545</v>
       </c>
       <c r="L68" s="14" t="n">
-        <v>103.5054892526366</v>
+        <v>103.5054892526367</v>
       </c>
       <c r="M68" s="14" t="n">
         <v>122.6882197812963</v>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="P68" s="14" t="inlineStr">
         <is>
-          <t>$650974.7083730621</t>
+          <t>$650974.708373062</t>
         </is>
       </c>
       <c r="Q68" s="14" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="R68" s="14" t="inlineStr">
         <is>
-          <t>$1035872.9002566739</t>
+          <t>$1035872.9002566737</t>
         </is>
       </c>
       <c r="S68" s="14" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="T68" s="14" t="inlineStr">
         <is>
-          <t>$1600086.4725275584</t>
+          <t>$1600086.4725275587</t>
         </is>
       </c>
       <c r="U68" s="14" t="inlineStr">
@@ -8461,7 +8461,7 @@
       </c>
       <c r="P69" s="14" t="inlineStr">
         <is>
-          <t>$113920.57396528588</t>
+          <t>$113920.57396528585</t>
         </is>
       </c>
       <c r="Q69" s="14" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="R69" s="14" t="inlineStr">
         <is>
-          <t>$181277.75754491796</t>
+          <t>$181277.7575449179</t>
         </is>
       </c>
       <c r="S69" s="14" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="T69" s="14" t="inlineStr">
         <is>
-          <t>$280015.1326923228</t>
+          <t>$280015.13269232283</t>
         </is>
       </c>
       <c r="U69" s="14" t="inlineStr">
@@ -8741,7 +8741,7 @@
       </c>
       <c r="P71" s="14" t="inlineStr">
         <is>
-          <t>$100400.2920289876</t>
+          <t>$100400.29202898758</t>
         </is>
       </c>
       <c r="Q71" s="14" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="R71" s="14" t="inlineStr">
         <is>
-          <t>$99538.05346323777</t>
+          <t>$99538.05346323775</t>
         </is>
       </c>
       <c r="S71" s="14" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="T71" s="14" t="inlineStr">
         <is>
-          <t>$103765.84033579903</t>
+          <t>$103765.84033579906</t>
         </is>
       </c>
       <c r="U71" s="14" t="inlineStr">
@@ -8866,7 +8866,7 @@
         <v>19.80466702738676</v>
       </c>
       <c r="L72" s="14" t="n">
-        <v>20.35350642293612</v>
+        <v>20.35350642293613</v>
       </c>
       <c r="M72" s="14" t="n">
         <v>20.78154655812494</v>
@@ -8881,7 +8881,7 @@
       </c>
       <c r="P72" s="14" t="inlineStr">
         <is>
-          <t>$142233.74704106577</t>
+          <t>$142233.74704106574</t>
         </is>
       </c>
       <c r="Q72" s="14" t="inlineStr">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="R72" s="14" t="inlineStr">
         <is>
-          <t>$141012.2424062535</t>
+          <t>$141012.24240625347</t>
         </is>
       </c>
       <c r="S72" s="14" t="inlineStr">
@@ -8901,7 +8901,7 @@
       </c>
       <c r="T72" s="14" t="inlineStr">
         <is>
-          <t>$147001.60714238195</t>
+          <t>$147001.607142382</t>
         </is>
       </c>
       <c r="U72" s="14" t="inlineStr">
@@ -9006,7 +9006,7 @@
         <v>13.01312312783175</v>
       </c>
       <c r="L73" s="14" t="n">
-        <v>15.52582338789549</v>
+        <v>15.5258233878955</v>
       </c>
       <c r="M73" s="14" t="n">
         <v>18.40323296719444</v>
@@ -9021,7 +9021,7 @@
       </c>
       <c r="P73" s="14" t="inlineStr">
         <is>
-          <t>$152455.87121293455</t>
+          <t>$152455.87121293452</t>
         </is>
       </c>
       <c r="Q73" s="14" t="inlineStr">
@@ -9031,7 +9031,7 @@
       </c>
       <c r="R73" s="14" t="inlineStr">
         <is>
-          <t>$248006.70900206603</t>
+          <t>$248006.70900206597</t>
         </is>
       </c>
       <c r="S73" s="14" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="T73" s="14" t="inlineStr">
         <is>
-          <t>$391631.2429217862</t>
+          <t>$391631.2429217863</t>
         </is>
       </c>
       <c r="U73" s="14" t="inlineStr">
@@ -9161,7 +9161,7 @@
       </c>
       <c r="P74" s="14" t="inlineStr">
         <is>
-          <t>$116738.35254982884</t>
+          <t>$116738.35254982882</t>
         </is>
       </c>
       <c r="Q74" s="14" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="R74" s="14" t="inlineStr">
         <is>
-          <t>$129810.33812686685</t>
+          <t>$129810.33812686682</t>
         </is>
       </c>
       <c r="S74" s="14" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="T74" s="14" t="inlineStr">
         <is>
-          <t>$143565.13858717206</t>
+          <t>$143565.13858717208</t>
         </is>
       </c>
       <c r="U74" s="14" t="inlineStr">
@@ -9286,7 +9286,7 @@
         <v>15.144745373884</v>
       </c>
       <c r="L75" s="14" t="n">
-        <v>15.56444608812762</v>
+        <v>15.56444608812763</v>
       </c>
       <c r="M75" s="14" t="n">
         <v>15.89177089738966</v>
@@ -9301,7 +9301,7 @@
       </c>
       <c r="P75" s="14" t="inlineStr">
         <is>
-          <t>$198455.199334709</t>
+          <t>$198455.19933470894</t>
         </is>
       </c>
       <c r="Q75" s="14" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="R75" s="14" t="inlineStr">
         <is>
-          <t>$220677.57481567364</t>
+          <t>$220677.5748156736</t>
         </is>
       </c>
       <c r="S75" s="14" t="inlineStr">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="T75" s="14" t="inlineStr">
         <is>
-          <t>$244060.7355981925</t>
+          <t>$244060.73559819255</t>
         </is>
       </c>
       <c r="U75" s="14" t="inlineStr">
@@ -9441,7 +9441,7 @@
       </c>
       <c r="P76" s="14" t="inlineStr">
         <is>
-          <t>$123505.79626628739</t>
+          <t>$123505.79626628736</t>
         </is>
       </c>
       <c r="Q76" s="14" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="R76" s="14" t="inlineStr">
         <is>
-          <t>$147546.37538759937</t>
+          <t>$147546.37538759934</t>
         </is>
       </c>
       <c r="S76" s="14" t="inlineStr">
@@ -9461,7 +9461,7 @@
       </c>
       <c r="T76" s="14" t="inlineStr">
         <is>
-          <t>$173801.2854043221</t>
+          <t>$173801.28540432212</t>
         </is>
       </c>
       <c r="U76" s="14" t="inlineStr">
@@ -9566,7 +9566,7 @@
         <v>4.659921653502769</v>
       </c>
       <c r="L77" s="14" t="n">
-        <v>4.789060334808499</v>
+        <v>4.7890603348085</v>
       </c>
       <c r="M77" s="14" t="n">
         <v>4.889775660735279</v>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="P77" s="14" t="inlineStr">
         <is>
-          <t>$49402.318506514945</t>
+          <t>$49402.31850651494</t>
         </is>
       </c>
       <c r="Q77" s="14" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="R77" s="14" t="inlineStr">
         <is>
-          <t>$59018.55015503975</t>
+          <t>$59018.55015503974</t>
         </is>
       </c>
       <c r="S77" s="14" t="inlineStr">
@@ -9601,7 +9601,7 @@
       </c>
       <c r="T77" s="14" t="inlineStr">
         <is>
-          <t>$69520.51416172883</t>
+          <t>$69520.51416172885</t>
         </is>
       </c>
       <c r="U77" s="14" t="inlineStr">
@@ -9721,7 +9721,7 @@
       </c>
       <c r="P78" s="14" t="inlineStr">
         <is>
-          <t>$28176.18897045182</t>
+          <t>$28176.188970451814</t>
         </is>
       </c>
       <c r="Q78" s="14" t="inlineStr">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="R78" s="14" t="inlineStr">
         <is>
-          <t>$36287.41293120298</t>
+          <t>$36287.412931202976</t>
         </is>
       </c>
       <c r="S78" s="14" t="inlineStr">
@@ -9741,7 +9741,7 @@
       </c>
       <c r="T78" s="14" t="inlineStr">
         <is>
-          <t>$21113.411744843655</t>
+          <t>$21113.411744843663</t>
         </is>
       </c>
       <c r="U78" s="14" t="inlineStr">
@@ -9846,7 +9846,7 @@
         <v>6.484964368544962</v>
       </c>
       <c r="L79" s="14" t="n">
-        <v>7.002085079673143</v>
+        <v>7.002085079673145</v>
       </c>
       <c r="M79" s="14" t="n">
         <v>7.554996712051887</v>
@@ -9861,7 +9861,7 @@
       </c>
       <c r="P79" s="14" t="inlineStr">
         <is>
-          <t>$116984.99385283921</t>
+          <t>$116984.99385283918</t>
         </is>
       </c>
       <c r="Q79" s="14" t="inlineStr">
@@ -9871,7 +9871,7 @@
       </c>
       <c r="R79" s="14" t="inlineStr">
         <is>
-          <t>$153898.6449006919</t>
+          <t>$153898.64490069184</t>
         </is>
       </c>
       <c r="S79" s="14" t="inlineStr">
@@ -9881,7 +9881,7 @@
       </c>
       <c r="T79" s="14" t="inlineStr">
         <is>
-          <t>$205201.77002905027</t>
+          <t>$205201.77002905033</t>
         </is>
       </c>
       <c r="U79" s="14" t="inlineStr">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="P80" s="14" t="inlineStr">
         <is>
-          <t>$281310.8093188068</t>
+          <t>$281310.80931880674</t>
         </is>
       </c>
       <c r="Q80" s="14" t="inlineStr">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="R80" s="14" t="inlineStr">
         <is>
-          <t>$362240.3842528763</t>
+          <t>$362240.38425287616</t>
         </is>
       </c>
       <c r="S80" s="14" t="inlineStr">
@@ -10021,7 +10021,7 @@
       </c>
       <c r="T80" s="14" t="inlineStr">
         <is>
-          <t>$250967.8794562164</t>
+          <t>$250967.87945621647</t>
         </is>
       </c>
       <c r="U80" s="14" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="P81" s="14" t="inlineStr">
         <is>
-          <t>$52942.91392546044</t>
+          <t>$52942.91392546043</t>
         </is>
       </c>
       <c r="Q81" s="14" t="inlineStr">
@@ -10151,7 +10151,7 @@
       </c>
       <c r="R81" s="14" t="inlineStr">
         <is>
-          <t>$51919.290722937214</t>
+          <t>$51919.2907229372</t>
         </is>
       </c>
       <c r="S81" s="14" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="T81" s="14" t="inlineStr">
         <is>
-          <t>$50666.619519243686</t>
+          <t>$50666.6195192437</t>
         </is>
       </c>
       <c r="U81" s="14" t="inlineStr">
@@ -10266,7 +10266,7 @@
         <v>9.098324528751034</v>
       </c>
       <c r="L82" s="14" t="n">
-        <v>8.630699165878557</v>
+        <v>8.630699165878559</v>
       </c>
       <c r="M82" s="14" t="n">
         <v>8.133864792316498</v>
@@ -10281,7 +10281,7 @@
       </c>
       <c r="P82" s="14" t="inlineStr">
         <is>
-          <t>$127297.32466573436</t>
+          <t>$127297.32466573433</t>
         </is>
       </c>
       <c r="Q82" s="14" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="R82" s="14" t="inlineStr">
         <is>
-          <t>$127666.17700177147</t>
+          <t>$127666.17700177144</t>
         </is>
       </c>
       <c r="S82" s="14" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="T82" s="14" t="inlineStr">
         <is>
-          <t>$127343.25142453788</t>
+          <t>$127343.25142453791</t>
         </is>
       </c>
       <c r="U82" s="14" t="inlineStr">
@@ -10406,7 +10406,7 @@
         <v>41.93929488152492</v>
       </c>
       <c r="L83" s="14" t="n">
-        <v>43.10154301327649</v>
+        <v>43.1015430132765</v>
       </c>
       <c r="M83" s="14" t="n">
         <v>44.00798094661751</v>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="P83" s="14" t="inlineStr">
         <is>
-          <t>$577059.2972259285</t>
+          <t>$577059.2972259284</t>
         </is>
       </c>
       <c r="Q83" s="14" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="R83" s="14" t="inlineStr">
         <is>
-          <t>$630537.4800909403</t>
+          <t>$630537.48009094</t>
         </is>
       </c>
       <c r="S83" s="14" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="T83" s="14" t="inlineStr">
         <is>
-          <t>$682429.9043244615</t>
+          <t>$682429.9043244616</t>
         </is>
       </c>
       <c r="U83" s="14" t="inlineStr">
@@ -10546,7 +10546,7 @@
         <v>3.979964406556381</v>
       </c>
       <c r="L84" s="14" t="n">
-        <v>4.23206704159971</v>
+        <v>4.232067041599711</v>
       </c>
       <c r="M84" s="14" t="n">
         <v>4.462278369161732</v>
@@ -10561,7 +10561,7 @@
       </c>
       <c r="P84" s="14" t="inlineStr">
         <is>
-          <t>$112796.60773066233</t>
+          <t>$112796.6077306623</t>
         </is>
       </c>
       <c r="Q84" s="14" t="inlineStr">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="R84" s="14" t="inlineStr">
         <is>
-          <t>$146604.2486368146</t>
+          <t>$146604.24863681453</t>
         </is>
       </c>
       <c r="S84" s="14" t="inlineStr">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="T84" s="14" t="inlineStr">
         <is>
-          <t>$186361.30883374915</t>
+          <t>$186361.30883374918</t>
         </is>
       </c>
       <c r="U84" s="14" t="inlineStr">
@@ -10686,7 +10686,7 @@
         <v>0.7319928425625126</v>
       </c>
       <c r="L85" s="14" t="n">
-        <v>0.6094294097321404</v>
+        <v>0.6094294097321405</v>
       </c>
       <c r="M85" s="14" t="n">
         <v>0.6164885471350774</v>
@@ -10701,7 +10701,7 @@
       </c>
       <c r="P85" s="14" t="inlineStr">
         <is>
-          <t>$28423.842465578913</t>
+          <t>$28423.842465578906</t>
         </is>
       </c>
       <c r="Q85" s="14" t="inlineStr">
@@ -10711,7 +10711,7 @@
       </c>
       <c r="R85" s="14" t="inlineStr">
         <is>
-          <t>$14391.179175746482</t>
+          <t>$14391.179175746478</t>
         </is>
       </c>
       <c r="S85" s="14" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="T85" s="14" t="inlineStr">
         <is>
-          <t>$15871.649939407547</t>
+          <t>$15871.64993940755</t>
         </is>
       </c>
       <c r="U85" s="14" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="P90" s="14" t="inlineStr">
         <is>
-          <t>$27349.414461246328</t>
+          <t>$27349.414461246324</t>
         </is>
       </c>
       <c r="Q90" s="14" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="R90" s="14" t="inlineStr">
         <is>
-          <t>$32688.6782300157</t>
+          <t>$32688.678230015692</t>
         </is>
       </c>
       <c r="S90" s="14" t="inlineStr">
@@ -11421,7 +11421,7 @@
       </c>
       <c r="T90" s="14" t="inlineStr">
         <is>
-          <t>$38759.66447742056</t>
+          <t>$38759.66447742058</t>
         </is>
       </c>
       <c r="U90" s="14" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="P91" s="14" t="inlineStr">
         <is>
-          <t>$218795.31568997062</t>
+          <t>$218795.3156899706</t>
         </is>
       </c>
       <c r="Q91" s="14" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="R91" s="14" t="inlineStr">
         <is>
-          <t>$261509.4258401256</t>
+          <t>$261509.42584012554</t>
         </is>
       </c>
       <c r="S91" s="14" t="inlineStr">
@@ -11561,7 +11561,7 @@
       </c>
       <c r="T91" s="14" t="inlineStr">
         <is>
-          <t>$310077.3158193645</t>
+          <t>$310077.3158193646</t>
         </is>
       </c>
       <c r="U91" s="14" t="inlineStr">
@@ -11666,7 +11666,7 @@
         <v>79.89238049652107</v>
       </c>
       <c r="L92" s="14" t="n">
-        <v>89.85034925445933</v>
+        <v>89.85034925445936</v>
       </c>
       <c r="M92" s="14" t="n">
         <v>100.3921265389182</v>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="P92" s="14" t="inlineStr">
         <is>
-          <t>$363761.9662871118</t>
+          <t>$363761.96628711175</t>
         </is>
       </c>
       <c r="Q92" s="14" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="R92" s="14" t="inlineStr">
         <is>
-          <t>$515012.0965521045</t>
+          <t>$515012.0965521044</t>
         </is>
       </c>
       <c r="S92" s="14" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="T92" s="14" t="inlineStr">
         <is>
-          <t>$696836.5372402493</t>
+          <t>$696836.5372402495</t>
         </is>
       </c>
       <c r="U92" s="14" t="inlineStr">
@@ -11806,7 +11806,7 @@
         <v>4.510602388788568</v>
       </c>
       <c r="L93" s="14" t="n">
-        <v>5.012439116593007</v>
+        <v>5.012439116593008</v>
       </c>
       <c r="M93" s="14" t="n">
         <v>5.569918817277257</v>
@@ -11821,7 +11821,7 @@
       </c>
       <c r="P93" s="14" t="inlineStr">
         <is>
-          <t>$46491.44881800734</t>
+          <t>$46491.44881800733</t>
         </is>
       </c>
       <c r="Q93" s="14" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="R93" s="14" t="inlineStr">
         <is>
-          <t>$63295.879919260384</t>
+          <t>$63295.87991926037</t>
         </is>
       </c>
       <c r="S93" s="14" t="inlineStr">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="T93" s="14" t="inlineStr">
         <is>
-          <t>$86167.1167880564</t>
+          <t>$86167.11678805642</t>
         </is>
       </c>
       <c r="U93" s="14" t="inlineStr">
@@ -11946,7 +11946,7 @@
         <v>34.49302485682197</v>
       </c>
       <c r="L94" s="14" t="n">
-        <v>36.67791436053082</v>
+        <v>36.67791436053083</v>
       </c>
       <c r="M94" s="14" t="n">
         <v>38.67307919940167</v>
@@ -11961,7 +11961,7 @@
       </c>
       <c r="P94" s="14" t="inlineStr">
         <is>
-          <t>$753357.6304805628</t>
+          <t>$753357.6304805626</t>
         </is>
       </c>
       <c r="Q94" s="14" t="inlineStr">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="R94" s="14" t="inlineStr">
         <is>
-          <t>$924832.30780702</t>
+          <t>$924832.3078070199</t>
         </is>
       </c>
       <c r="S94" s="14" t="inlineStr">
@@ -11981,7 +11981,7 @@
       </c>
       <c r="T94" s="14" t="inlineStr">
         <is>
-          <t>$945779.3997877982</t>
+          <t>$945779.3997877984</t>
         </is>
       </c>
       <c r="U94" s="14" t="inlineStr">
@@ -12086,7 +12086,7 @@
         <v>19.89982203278191</v>
       </c>
       <c r="L95" s="14" t="n">
-        <v>21.16033520799855</v>
+        <v>21.16033520799856</v>
       </c>
       <c r="M95" s="14" t="n">
         <v>22.31139184580866</v>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="P95" s="14" t="inlineStr">
         <is>
-          <t>$434629.62096301606</t>
+          <t>$434629.620963016</t>
         </is>
       </c>
       <c r="Q95" s="14" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="R95" s="14" t="inlineStr">
         <is>
-          <t>$533556.8596748005</t>
+          <t>$533556.8596748004</t>
         </is>
       </c>
       <c r="S95" s="14" t="inlineStr">
@@ -12121,7 +12121,7 @@
       </c>
       <c r="T95" s="14" t="inlineStr">
         <is>
-          <t>$545641.7149747683</t>
+          <t>$545641.7149747685</t>
         </is>
       </c>
       <c r="U95" s="14" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="P96" s="14" t="inlineStr">
         <is>
-          <t>$313723.26344974333</t>
+          <t>$313723.2634497432</t>
         </is>
       </c>
       <c r="Q96" s="14" t="inlineStr">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="R96" s="14" t="inlineStr">
         <is>
-          <t>$374173.8644596863</t>
+          <t>$374173.86445968616</t>
         </is>
       </c>
       <c r="S96" s="14" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="T96" s="14" t="inlineStr">
         <is>
-          <t>$441310.38916751643</t>
+          <t>$441310.38916751655</t>
         </is>
       </c>
       <c r="U96" s="14" t="inlineStr">
@@ -12381,7 +12381,7 @@
       </c>
       <c r="P97" s="14" t="inlineStr">
         <is>
-          <t>$228162.37341799508</t>
+          <t>$228162.37341799503</t>
         </is>
       </c>
       <c r="Q97" s="14" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="R97" s="14" t="inlineStr">
         <is>
-          <t>$272126.4468797718</t>
+          <t>$272126.4468797717</t>
         </is>
       </c>
       <c r="S97" s="14" t="inlineStr">
@@ -12401,7 +12401,7 @@
       </c>
       <c r="T97" s="14" t="inlineStr">
         <is>
-          <t>$320953.0103036483</t>
+          <t>$320953.0103036484</t>
         </is>
       </c>
       <c r="U97" s="14" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P98" s="14" t="inlineStr">
         <is>
-          <t>$90433.1936440942</t>
+          <t>$90433.19364409418</t>
         </is>
       </c>
       <c r="Q98" s="14" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="R98" s="14" t="inlineStr">
         <is>
-          <t>$124994.29536126445</t>
+          <t>$124994.29536126442</t>
         </is>
       </c>
       <c r="S98" s="14" t="inlineStr">
@@ -12541,7 +12541,7 @@
       </c>
       <c r="T98" s="14" t="inlineStr">
         <is>
-          <t>$163867.68625501104</t>
+          <t>$163867.6862550111</t>
         </is>
       </c>
       <c r="U98" s="14" t="inlineStr">
@@ -12646,7 +12646,7 @@
         <v>23.96771414895632</v>
       </c>
       <c r="L99" s="14" t="n">
-        <v>26.9551047763378</v>
+        <v>26.95510477633781</v>
       </c>
       <c r="M99" s="14" t="n">
         <v>30.11763796167547</v>
@@ -12661,7 +12661,7 @@
       </c>
       <c r="P99" s="14" t="inlineStr">
         <is>
-          <t>$155028.33196130436</t>
+          <t>$155028.33196130433</t>
         </is>
       </c>
       <c r="Q99" s="14" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="R99" s="14" t="inlineStr">
         <is>
-          <t>$214275.93490502474</t>
+          <t>$214275.9349050247</t>
         </is>
       </c>
       <c r="S99" s="14" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="T99" s="14" t="inlineStr">
         <is>
-          <t>$280916.033580019</t>
+          <t>$280916.0335800191</t>
         </is>
       </c>
       <c r="U99" s="14" t="inlineStr">
@@ -12801,7 +12801,7 @@
       </c>
       <c r="P100" s="14" t="inlineStr">
         <is>
-          <t>$381766.98480418185</t>
+          <t>$381766.9848041818</t>
         </is>
       </c>
       <c r="Q100" s="14" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="R100" s="14" t="inlineStr">
         <is>
-          <t>$451468.901912379</t>
+          <t>$451468.9019123789</t>
         </is>
       </c>
       <c r="S100" s="14" t="inlineStr">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="T100" s="14" t="inlineStr">
         <is>
-          <t>$527960.3282617189</t>
+          <t>$527960.328261719</t>
         </is>
       </c>
       <c r="U100" s="14" t="inlineStr">
@@ -13066,7 +13066,7 @@
         <v>6.760787648330694</v>
       </c>
       <c r="L102" s="14" t="n">
-        <v>6.540142360153934</v>
+        <v>6.540142360153935</v>
       </c>
       <c r="M102" s="14" t="n">
         <v>6.754104539563198</v>
@@ -13081,7 +13081,7 @@
       </c>
       <c r="P102" s="14" t="inlineStr">
         <is>
-          <t>$225672.4608702733</t>
+          <t>$225672.46087027324</t>
         </is>
       </c>
       <c r="Q102" s="14" t="inlineStr">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="R102" s="14" t="inlineStr">
         <is>
-          <t>$131398.08909902102</t>
+          <t>$131398.089099021</t>
         </is>
       </c>
       <c r="S102" s="14" t="inlineStr">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="T102" s="14" t="inlineStr">
         <is>
-          <t>$150500.8508429389</t>
+          <t>$150500.85084293893</t>
         </is>
       </c>
       <c r="U102" s="14" t="inlineStr">
@@ -13206,7 +13206,7 @@
         <v>10.41235123975976</v>
       </c>
       <c r="L103" s="14" t="n">
-        <v>10.53536946536284</v>
+        <v>10.53536946536285</v>
       </c>
       <c r="M103" s="14" t="n">
         <v>10.6077975806271</v>
@@ -13221,7 +13221,7 @@
       </c>
       <c r="P103" s="14" t="inlineStr">
         <is>
-          <t>$17899.03601077074</t>
+          <t>$17899.036010770735</t>
         </is>
       </c>
       <c r="Q103" s="14" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="R103" s="14" t="inlineStr">
         <is>
-          <t>$19974.50309835583</t>
+          <t>$19974.503098355824</t>
         </is>
       </c>
       <c r="S103" s="14" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="T103" s="14" t="inlineStr">
         <is>
-          <t>$22022.768840491306</t>
+          <t>$22022.76884049131</t>
         </is>
       </c>
       <c r="U103" s="14" t="inlineStr">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="P104" s="14" t="inlineStr">
         <is>
-          <t>$348766.530435877</t>
+          <t>$348766.53043587686</t>
         </is>
       </c>
       <c r="Q104" s="14" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="R104" s="14" t="inlineStr">
         <is>
-          <t>$203069.77406212338</t>
+          <t>$203069.77406212335</t>
         </is>
       </c>
       <c r="S104" s="14" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="T104" s="14" t="inlineStr">
         <is>
-          <t>$232592.22402999652</t>
+          <t>$232592.22402999658</t>
         </is>
       </c>
       <c r="U104" s="14" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="P105" s="14" t="inlineStr">
         <is>
-          <t>$1552.6854259796032</t>
+          <t>$1552.685425979603</t>
         </is>
       </c>
       <c r="Q105" s="14" t="inlineStr">
@@ -13511,7 +13511,7 @@
       </c>
       <c r="R105" s="14" t="inlineStr">
         <is>
-          <t>$1732.7173944296635</t>
+          <t>$1732.717394429663</t>
         </is>
       </c>
       <c r="S105" s="14" t="inlineStr">
@@ -13521,7 +13521,7 @@
       </c>
       <c r="T105" s="14" t="inlineStr">
         <is>
-          <t>$1910.3788739595504</t>
+          <t>$1910.378873959551</t>
         </is>
       </c>
       <c r="U105" s="14" t="inlineStr">
@@ -13641,7 +13641,7 @@
       </c>
       <c r="P106" s="14" t="inlineStr">
         <is>
-          <t>$430829.22944877605</t>
+          <t>$430829.229448776</t>
         </is>
       </c>
       <c r="Q106" s="14" t="inlineStr">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="R106" s="14" t="inlineStr">
         <is>
-          <t>$250850.88920138503</t>
+          <t>$250850.889201385</t>
         </is>
       </c>
       <c r="S106" s="14" t="inlineStr">
@@ -13661,7 +13661,7 @@
       </c>
       <c r="T106" s="14" t="inlineStr">
         <is>
-          <t>$287319.7967975437</t>
+          <t>$287319.79679754376</t>
         </is>
       </c>
       <c r="U106" s="14" t="inlineStr">
@@ -14341,7 +14341,7 @@
       </c>
       <c r="P111" s="14" t="inlineStr">
         <is>
-          <t>$177838.31525420453</t>
+          <t>$177838.3152542045</t>
         </is>
       </c>
       <c r="Q111" s="14" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="R111" s="14" t="inlineStr">
         <is>
-          <t>$195217.90543333808</t>
+          <t>$195217.90543333802</t>
         </is>
       </c>
       <c r="S111" s="14" t="inlineStr">
@@ -14361,7 +14361,7 @@
       </c>
       <c r="T111" s="14" t="inlineStr">
         <is>
-          <t>$235638.66426958176</t>
+          <t>$235638.66426958182</t>
         </is>
       </c>
       <c r="U111" s="14" t="inlineStr">
@@ -14481,7 +14481,7 @@
       </c>
       <c r="P112" s="14" t="inlineStr">
         <is>
-          <t>$337892.7989829885</t>
+          <t>$337892.79898298846</t>
         </is>
       </c>
       <c r="Q112" s="14" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="R112" s="14" t="inlineStr">
         <is>
-          <t>$370914.02032334235</t>
+          <t>$370914.0203233423</t>
         </is>
       </c>
       <c r="S112" s="14" t="inlineStr">
@@ -14501,7 +14501,7 @@
       </c>
       <c r="T112" s="14" t="inlineStr">
         <is>
-          <t>$447713.46211220534</t>
+          <t>$447713.4621122054</t>
         </is>
       </c>
       <c r="U112" s="14" t="inlineStr">
@@ -14581,7 +14581,9 @@
           <t>JASCAYD</t>
         </is>
       </c>
-      <c r="F113" s="14" t="inlineStr"/>
+      <c r="F113" s="14" t="n">
+        <v/>
+      </c>
       <c r="G113" s="14" t="inlineStr">
         <is>
           <t>B</t>
@@ -14602,7 +14604,7 @@
         <v>3.007068259192379</v>
       </c>
       <c r="L113" s="14" t="n">
-        <v>3.341626077728671</v>
+        <v>3.341626077728672</v>
       </c>
       <c r="M113" s="14" t="n">
         <v>3.713279211518171</v>
@@ -14617,7 +14619,7 @@
       </c>
       <c r="P113" s="14" t="inlineStr">
         <is>
-          <t>$56459.76230042889</t>
+          <t>$56459.76230042888</t>
         </is>
       </c>
       <c r="Q113" s="14" t="inlineStr">
@@ -14627,7 +14629,7 @@
       </c>
       <c r="R113" s="14" t="inlineStr">
         <is>
-          <t>$76867.2610919743</t>
+          <t>$76867.26109197429</t>
         </is>
       </c>
       <c r="S113" s="14" t="inlineStr">
@@ -14637,7 +14639,7 @@
       </c>
       <c r="T113" s="14" t="inlineStr">
         <is>
-          <t>$104642.36016844948</t>
+          <t>$104642.36016844951</t>
         </is>
       </c>
       <c r="U113" s="14" t="inlineStr">
@@ -15317,7 +15319,7 @@
       </c>
       <c r="P118" s="14" t="inlineStr">
         <is>
-          <t>$134762.7041549164</t>
+          <t>$134762.70415491637</t>
         </is>
       </c>
       <c r="Q118" s="14" t="inlineStr">
@@ -15327,7 +15329,7 @@
       </c>
       <c r="R118" s="14" t="inlineStr">
         <is>
-          <t>$164648.8595751361</t>
+          <t>$164648.85957513607</t>
         </is>
       </c>
       <c r="S118" s="14" t="inlineStr">
@@ -15337,7 +15339,7 @@
       </c>
       <c r="T118" s="14" t="inlineStr">
         <is>
-          <t>$200216.68131572678</t>
+          <t>$200216.6813157268</t>
         </is>
       </c>
       <c r="U118" s="14" t="inlineStr">
@@ -18537,7 +18539,7 @@
       </c>
       <c r="P141" s="14" t="inlineStr">
         <is>
-          <t>$472473.01063067355</t>
+          <t>$472473.01063067344</t>
         </is>
       </c>
       <c r="Q141" s="14" t="inlineStr">
@@ -18547,7 +18549,7 @@
       </c>
       <c r="R141" s="14" t="inlineStr">
         <is>
-          <t>$577293.879625342</t>
+          <t>$577293.8796253419</t>
         </is>
       </c>
       <c r="S141" s="14" t="inlineStr">
@@ -18557,7 +18559,7 @@
       </c>
       <c r="T141" s="14" t="inlineStr">
         <is>
-          <t>$306719.46384473424</t>
+          <t>$306719.46384473436</t>
         </is>
       </c>
       <c r="U141" s="14" t="inlineStr">
@@ -19642,7 +19644,7 @@
         <v>0.76450188240252</v>
       </c>
       <c r="L149" s="14" t="n">
-        <v>0.7125505231349336</v>
+        <v>0.7125505231349337</v>
       </c>
       <c r="M149" s="14" t="n">
         <v>0.6715318772536502</v>
@@ -19657,7 +19659,7 @@
       </c>
       <c r="P149" s="14" t="inlineStr">
         <is>
-          <t>$130760.8315162253</t>
+          <t>$130760.83151622527</t>
         </is>
       </c>
       <c r="Q149" s="14" t="inlineStr">
@@ -19667,7 +19669,7 @@
       </c>
       <c r="R149" s="14" t="inlineStr">
         <is>
-          <t>$117152.89206151669</t>
+          <t>$117152.89206151666</t>
         </is>
       </c>
       <c r="S149" s="14" t="inlineStr">
@@ -19677,7 +19679,7 @@
       </c>
       <c r="T149" s="14" t="inlineStr">
         <is>
-          <t>$114396.99810549265</t>
+          <t>$114396.99810549266</t>
         </is>
       </c>
       <c r="U149" s="14" t="inlineStr">
@@ -19797,7 +19799,7 @@
       </c>
       <c r="P150" s="14" t="inlineStr">
         <is>
-          <t>$300659.94674248993</t>
+          <t>$300659.9467424899</t>
         </is>
       </c>
       <c r="Q150" s="14" t="inlineStr">
@@ -19807,7 +19809,7 @@
       </c>
       <c r="R150" s="14" t="inlineStr">
         <is>
-          <t>$297990.6348235679</t>
+          <t>$297990.6348235678</t>
         </is>
       </c>
       <c r="S150" s="14" t="inlineStr">
@@ -19817,7 +19819,7 @@
       </c>
       <c r="T150" s="14" t="inlineStr">
         <is>
-          <t>$290980.7302876148</t>
+          <t>$290980.73028761486</t>
         </is>
       </c>
       <c r="U150" s="14" t="inlineStr">
@@ -19922,7 +19924,7 @@
         <v>0.9098324528751034</v>
       </c>
       <c r="L151" s="14" t="n">
-        <v>0.8630699165878557</v>
+        <v>0.8630699165878558</v>
       </c>
       <c r="M151" s="14" t="n">
         <v>0.81338647923165</v>
@@ -19937,7 +19939,7 @@
       </c>
       <c r="P151" s="14" t="inlineStr">
         <is>
-          <t>$114537.12709279399</t>
+          <t>$114537.12709279396</t>
         </is>
       </c>
       <c r="Q151" s="14" t="inlineStr">
@@ -19947,7 +19949,7 @@
       </c>
       <c r="R151" s="14" t="inlineStr">
         <is>
-          <t>$113520.24632160919</t>
+          <t>$113520.24632160917</t>
         </is>
       </c>
       <c r="S151" s="14" t="inlineStr">
@@ -19957,7 +19959,7 @@
       </c>
       <c r="T151" s="14" t="inlineStr">
         <is>
-          <t>$110849.8063929064</t>
+          <t>$110849.80639290642</t>
         </is>
       </c>
       <c r="U151" s="14" t="inlineStr">
@@ -20202,7 +20204,7 @@
         <v>1.393294497630826</v>
       </c>
       <c r="L153" s="14" t="n">
-        <v>1.512446288935718</v>
+        <v>1.512446288935719</v>
       </c>
       <c r="M153" s="14" t="n">
         <v>1.631117824908513</v>
@@ -20217,7 +20219,7 @@
       </c>
       <c r="P153" s="14" t="inlineStr">
         <is>
-          <t>$8610.772493747878</t>
+          <t>$8610.772493747876</t>
         </is>
       </c>
       <c r="Q153" s="14" t="inlineStr">
@@ -20227,7 +20229,7 @@
       </c>
       <c r="R153" s="14" t="inlineStr">
         <is>
-          <t>$11200.757252293344</t>
+          <t>$11200.757252293342</t>
         </is>
       </c>
       <c r="S153" s="14" t="inlineStr">
@@ -20237,7 +20239,7 @@
       </c>
       <c r="T153" s="14" t="inlineStr">
         <is>
-          <t>$14455.570798945047</t>
+          <t>$14455.570798945051</t>
         </is>
       </c>
       <c r="U153" s="14" t="inlineStr">
@@ -20342,7 +20344,7 @@
         <v>11.13602417817932</v>
       </c>
       <c r="L154" s="14" t="n">
-        <v>1.483929271708725</v>
+        <v>1.483929271708726</v>
       </c>
       <c r="M154" s="14" t="n">
         <v>0.4294215440430628</v>
@@ -20357,7 +20359,7 @@
       </c>
       <c r="P154" s="14" t="inlineStr">
         <is>
-          <t>$61504.410195791206</t>
+          <t>$61504.41019579119</t>
         </is>
       </c>
       <c r="Q154" s="14" t="inlineStr">
@@ -20367,7 +20369,7 @@
       </c>
       <c r="R154" s="14" t="inlineStr">
         <is>
-          <t>$5226.349805038643</t>
+          <t>$5226.349805038642</t>
         </is>
       </c>
       <c r="S154" s="14" t="inlineStr">
@@ -20377,7 +20379,7 @@
       </c>
       <c r="T154" s="14" t="inlineStr">
         <is>
-          <t>$768.8742689845596</t>
+          <t>$768.8742689845599</t>
         </is>
       </c>
       <c r="U154" s="14" t="inlineStr">
@@ -20497,7 +20499,7 @@
       </c>
       <c r="P155" s="14" t="inlineStr">
         <is>
-          <t>$75441.98101477954</t>
+          <t>$75441.98101477952</t>
         </is>
       </c>
       <c r="Q155" s="14" t="inlineStr">
@@ -20507,7 +20509,7 @@
       </c>
       <c r="R155" s="14" t="inlineStr">
         <is>
-          <t>$8405.494833549385</t>
+          <t>$8405.494833549383</t>
         </is>
       </c>
       <c r="S155" s="14" t="inlineStr">
@@ -20517,7 +20519,7 @@
       </c>
       <c r="T155" s="14" t="inlineStr">
         <is>
-          <t>$1649.1696686568382</t>
+          <t>$1649.1696686568387</t>
         </is>
       </c>
       <c r="U155" s="14" t="inlineStr">
@@ -20622,7 +20624,7 @@
         <v>6.220524660445633</v>
       </c>
       <c r="L156" s="14" t="n">
-        <v>6.486013922515064</v>
+        <v>6.486013922515065</v>
       </c>
       <c r="M156" s="14" t="n">
         <v>6.74734465460041</v>
@@ -20637,7 +20639,7 @@
       </c>
       <c r="P156" s="14" t="inlineStr">
         <is>
-          <t>$52777.81066972529</t>
+          <t>$52777.81066972527</t>
         </is>
       </c>
       <c r="Q156" s="14" t="inlineStr">
@@ -20647,7 +20649,7 @@
       </c>
       <c r="R156" s="14" t="inlineStr">
         <is>
-          <t>$60433.96849422769</t>
+          <t>$60433.96849422767</t>
         </is>
       </c>
       <c r="S156" s="14" t="inlineStr">
@@ -20657,7 +20659,7 @@
       </c>
       <c r="T156" s="14" t="inlineStr">
         <is>
-          <t>$69049.10263751533</t>
+          <t>$69049.10263751535</t>
         </is>
       </c>
       <c r="U156" s="14" t="inlineStr">
@@ -20762,7 +20764,7 @@
         <v>41.05546275894118</v>
       </c>
       <c r="L157" s="14" t="n">
-        <v>42.80769188859941</v>
+        <v>42.80769188859943</v>
       </c>
       <c r="M157" s="14" t="n">
         <v>8.012134410105256</v>
@@ -20777,7 +20779,7 @@
       </c>
       <c r="P157" s="14" t="inlineStr">
         <is>
-          <t>$162218.496585437</t>
+          <t>$162218.49658543698</t>
         </is>
       </c>
       <c r="Q157" s="14" t="inlineStr">
@@ -20787,7 +20789,7 @@
       </c>
       <c r="R157" s="14" t="inlineStr">
         <is>
-          <t>$190974.03705543955</t>
+          <t>$190974.0370554395</t>
         </is>
       </c>
       <c r="S157" s="14" t="inlineStr">
@@ -20797,7 +20799,7 @@
       </c>
       <c r="T157" s="14" t="inlineStr">
         <is>
-          <t>$12674.196727128687</t>
+          <t>$12674.19672712869</t>
         </is>
       </c>
       <c r="U157" s="14" t="inlineStr">
@@ -20902,7 +20904,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L158" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M158" s="14" t="n">
         <v>3.66733174555146</v>
@@ -20917,7 +20919,7 @@
       </c>
       <c r="P158" s="14" t="inlineStr">
         <is>
-          <t>$18745.470834879994</t>
+          <t>$18745.47083487999</t>
         </is>
       </c>
       <c r="Q158" s="14" t="inlineStr">
@@ -20927,7 +20929,7 @@
       </c>
       <c r="R158" s="14" t="inlineStr">
         <is>
-          <t>$21661.88385615542</t>
+          <t>$21661.883856155415</t>
         </is>
       </c>
       <c r="S158" s="14" t="inlineStr">
@@ -20937,7 +20939,7 @@
       </c>
       <c r="T158" s="14" t="inlineStr">
         <is>
-          <t>$24896.60247996232</t>
+          <t>$24896.602479962326</t>
         </is>
       </c>
       <c r="U158" s="14" t="inlineStr">
@@ -21042,7 +21044,7 @@
         <v>2.653309604370921</v>
       </c>
       <c r="L159" s="14" t="n">
-        <v>2.82137802773314</v>
+        <v>2.821378027733141</v>
       </c>
       <c r="M159" s="14" t="n">
         <v>2.974852246107821</v>
@@ -21057,7 +21059,7 @@
       </c>
       <c r="P159" s="14" t="inlineStr">
         <is>
-          <t>$28294.12576135914</t>
+          <t>$28294.125761359133</t>
         </is>
       </c>
       <c r="Q159" s="14" t="inlineStr">
@@ -21067,7 +21069,7 @@
       </c>
       <c r="R159" s="14" t="inlineStr">
         <is>
-          <t>$31808.89301527684</t>
+          <t>$31808.893015276837</t>
         </is>
       </c>
       <c r="S159" s="14" t="inlineStr">
@@ -21077,7 +21079,7 @@
       </c>
       <c r="T159" s="14" t="inlineStr">
         <is>
-          <t>$35362.650457412754</t>
+          <t>$35362.65045741276</t>
         </is>
       </c>
       <c r="U159" s="14" t="inlineStr">
@@ -21197,7 +21199,7 @@
       </c>
       <c r="P160" s="14" t="inlineStr">
         <is>
-          <t>$284690.13985702384</t>
+          <t>$284690.1398570238</t>
         </is>
       </c>
       <c r="Q160" s="14" t="inlineStr">
@@ -21207,7 +21209,7 @@
       </c>
       <c r="R160" s="14" t="inlineStr">
         <is>
-          <t>$348926.8530475125</t>
+          <t>$348926.85304751236</t>
         </is>
       </c>
       <c r="S160" s="14" t="inlineStr">
@@ -21217,7 +21219,7 @@
       </c>
       <c r="T160" s="14" t="inlineStr">
         <is>
-          <t>$419188.03567829647</t>
+          <t>$419188.0356782966</t>
         </is>
       </c>
       <c r="U160" s="14" t="inlineStr">
@@ -21337,7 +21339,7 @@
       </c>
       <c r="P161" s="14" t="inlineStr">
         <is>
-          <t>$54289.248341098355</t>
+          <t>$54289.24834109834</t>
         </is>
       </c>
       <c r="Q161" s="14" t="inlineStr">
@@ -21347,7 +21349,7 @@
       </c>
       <c r="R161" s="14" t="inlineStr">
         <is>
-          <t>$56235.76085674024</t>
+          <t>$56235.76085674023</t>
         </is>
       </c>
       <c r="S161" s="14" t="inlineStr">
@@ -21357,7 +21359,7 @@
       </c>
       <c r="T161" s="14" t="inlineStr">
         <is>
-          <t>$58649.141342872106</t>
+          <t>$58649.14134287212</t>
         </is>
       </c>
       <c r="U161" s="14" t="inlineStr">
@@ -21462,7 +21464,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L162" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M162" s="14" t="n">
         <v>3.66733174555146</v>
@@ -21477,7 +21479,7 @@
       </c>
       <c r="P162" s="14" t="inlineStr">
         <is>
-          <t>$40277.94067702524</t>
+          <t>$40277.94067702523</t>
         </is>
       </c>
       <c r="Q162" s="14" t="inlineStr">
@@ -21487,7 +21489,7 @@
       </c>
       <c r="R162" s="14" t="inlineStr">
         <is>
-          <t>$44538.86257088573</t>
+          <t>$44538.86257088572</t>
         </is>
       </c>
       <c r="S162" s="14" t="inlineStr">
@@ -21497,7 +21499,7 @@
       </c>
       <c r="T162" s="14" t="inlineStr">
         <is>
-          <t>$48740.71494550521</t>
+          <t>$48740.71494550522</t>
         </is>
       </c>
       <c r="U162" s="14" t="inlineStr">
@@ -21602,7 +21604,7 @@
         <v>62.90894232228738</v>
       </c>
       <c r="L163" s="14" t="n">
-        <v>64.65231451991474</v>
+        <v>64.65231451991475</v>
       </c>
       <c r="M163" s="14" t="n">
         <v>66.01197141992625</v>
@@ -21617,7 +21619,7 @@
       </c>
       <c r="P163" s="14" t="inlineStr">
         <is>
-          <t>$349075.4858675521</t>
+          <t>$349075.485867552</t>
         </is>
       </c>
       <c r="Q163" s="14" t="inlineStr">
@@ -21627,7 +21629,7 @@
       </c>
       <c r="R163" s="14" t="inlineStr">
         <is>
-          <t>$386003.47561434295</t>
+          <t>$386003.4756143429</t>
         </is>
       </c>
       <c r="S163" s="14" t="inlineStr">
@@ -21637,7 +21639,7 @@
       </c>
       <c r="T163" s="14" t="inlineStr">
         <is>
-          <t>$422419.5295277118</t>
+          <t>$422419.52952771186</t>
         </is>
       </c>
       <c r="U163" s="14" t="inlineStr">
@@ -21757,7 +21759,7 @@
       </c>
       <c r="P164" s="14" t="inlineStr">
         <is>
-          <t>$108922.36175342051</t>
+          <t>$108922.36175342048</t>
         </is>
       </c>
       <c r="Q164" s="14" t="inlineStr">
@@ -21767,7 +21769,7 @@
       </c>
       <c r="R164" s="14" t="inlineStr">
         <is>
-          <t>$149151.5332381147</t>
+          <t>$149151.53323811467</t>
         </is>
       </c>
       <c r="S164" s="14" t="inlineStr">
@@ -21777,7 +21779,7 @@
       </c>
       <c r="T164" s="14" t="inlineStr">
         <is>
-          <t>$194671.01188579513</t>
+          <t>$194671.01188579516</t>
         </is>
       </c>
       <c r="U164" s="14" t="inlineStr">
@@ -21882,7 +21884,7 @@
         <v>49.93273781032568</v>
       </c>
       <c r="L165" s="14" t="n">
-        <v>56.15646828403708</v>
+        <v>56.1564682840371</v>
       </c>
       <c r="M165" s="14" t="n">
         <v>62.7450790868239</v>
@@ -21897,7 +21899,7 @@
       </c>
       <c r="P165" s="14" t="inlineStr">
         <is>
-          <t>$130258.03991275151</t>
+          <t>$130258.03991275148</t>
         </is>
       </c>
       <c r="Q165" s="14" t="inlineStr">
@@ -21907,7 +21909,7 @@
       </c>
       <c r="R165" s="14" t="inlineStr">
         <is>
-          <t>$188091.0044190492</t>
+          <t>$188091.00441904916</t>
         </is>
       </c>
       <c r="S165" s="14" t="inlineStr">
@@ -21917,7 +21919,7 @@
       </c>
       <c r="T165" s="14" t="inlineStr">
         <is>
-          <t>$258877.5584757062</t>
+          <t>$258877.55847570626</t>
         </is>
       </c>
       <c r="U165" s="14" t="inlineStr">
@@ -22037,7 +22039,7 @@
       </c>
       <c r="P166" s="14" t="inlineStr">
         <is>
-          <t>$59447.23562748261</t>
+          <t>$59447.235627482594</t>
         </is>
       </c>
       <c r="Q166" s="14" t="inlineStr">
@@ -22047,7 +22049,7 @@
       </c>
       <c r="R166" s="14" t="inlineStr">
         <is>
-          <t>$81168.1683152965</t>
+          <t>$81168.16831529648</t>
         </is>
       </c>
       <c r="S166" s="14" t="inlineStr">
@@ -22057,7 +22059,7 @@
       </c>
       <c r="T166" s="14" t="inlineStr">
         <is>
-          <t>$105199.91880202746</t>
+          <t>$105199.91880202747</t>
         </is>
       </c>
       <c r="U166" s="14" t="inlineStr">
@@ -22162,7 +22164,7 @@
         <v>27.96233317378238</v>
       </c>
       <c r="L167" s="14" t="n">
-        <v>31.44762223906077</v>
+        <v>31.44762223906078</v>
       </c>
       <c r="M167" s="14" t="n">
         <v>35.13724428862139</v>
@@ -22177,7 +22179,7 @@
       </c>
       <c r="P167" s="14" t="inlineStr">
         <is>
-          <t>$92473.47764275073</t>
+          <t>$92473.4776427507</t>
         </is>
       </c>
       <c r="Q167" s="14" t="inlineStr">
@@ -22187,7 +22189,7 @@
       </c>
       <c r="R167" s="14" t="inlineStr">
         <is>
-          <t>$126261.59515712789</t>
+          <t>$126261.59515712786</t>
         </is>
       </c>
       <c r="S167" s="14" t="inlineStr">
@@ -22197,7 +22199,7 @@
       </c>
       <c r="T167" s="14" t="inlineStr">
         <is>
-          <t>$163644.31813648719</t>
+          <t>$163644.3181364872</t>
         </is>
       </c>
       <c r="U167" s="14" t="inlineStr">
@@ -22317,7 +22319,7 @@
       </c>
       <c r="P168" s="14" t="inlineStr">
         <is>
-          <t>$1381454.6220614796</t>
+          <t>$1381454.6220614794</t>
         </is>
       </c>
       <c r="Q168" s="14" t="inlineStr">
@@ -22327,7 +22329,7 @@
       </c>
       <c r="R168" s="14" t="inlineStr">
         <is>
-          <t>$1623567.4399605081</t>
+          <t>$1623567.439960508</t>
         </is>
       </c>
       <c r="S168" s="14" t="inlineStr">
@@ -22337,7 +22339,7 @@
       </c>
       <c r="T168" s="14" t="inlineStr">
         <is>
-          <t>$1910478.535727721</t>
+          <t>$1910478.5357277214</t>
         </is>
       </c>
       <c r="U168" s="14" t="inlineStr">
@@ -22457,7 +22459,7 @@
       </c>
       <c r="P169" s="14" t="inlineStr">
         <is>
-          <t>$9568.752616922942</t>
+          <t>$9568.75261692294</t>
         </is>
       </c>
       <c r="Q169" s="14" t="inlineStr">
@@ -22467,7 +22469,7 @@
       </c>
       <c r="R169" s="14" t="inlineStr">
         <is>
-          <t>$8393.484513118552</t>
+          <t>$8393.48451311855</t>
         </is>
       </c>
       <c r="S169" s="14" t="inlineStr">
@@ -22477,7 +22479,7 @@
       </c>
       <c r="T169" s="14" t="inlineStr">
         <is>
-          <t>$8914.093563685827</t>
+          <t>$8914.093563685828</t>
         </is>
       </c>
       <c r="U169" s="14" t="inlineStr">
@@ -22582,7 +22584,7 @@
         <v>0.8211113848407426</v>
       </c>
       <c r="L170" s="14" t="n">
-        <v>0.7828631201369057</v>
+        <v>0.7828631201369058</v>
       </c>
       <c r="M170" s="14" t="n">
         <v>0.7680699431111464</v>
@@ -22597,7 +22599,7 @@
       </c>
       <c r="P170" s="14" t="inlineStr">
         <is>
-          <t>$19137.505233845885</t>
+          <t>$19137.50523384588</t>
         </is>
       </c>
       <c r="Q170" s="14" t="inlineStr">
@@ -22607,7 +22609,7 @@
       </c>
       <c r="R170" s="14" t="inlineStr">
         <is>
-          <t>$16786.969026237104</t>
+          <t>$16786.9690262371</t>
         </is>
       </c>
       <c r="S170" s="14" t="inlineStr">
@@ -22617,7 +22619,7 @@
       </c>
       <c r="T170" s="14" t="inlineStr">
         <is>
-          <t>$17828.187127371653</t>
+          <t>$17828.187127371657</t>
         </is>
       </c>
       <c r="U170" s="14" t="inlineStr">
@@ -22737,7 +22739,7 @@
       </c>
       <c r="P171" s="14" t="inlineStr">
         <is>
-          <t>$9568.752616922942</t>
+          <t>$9568.75261692294</t>
         </is>
       </c>
       <c r="Q171" s="14" t="inlineStr">
@@ -22747,7 +22749,7 @@
       </c>
       <c r="R171" s="14" t="inlineStr">
         <is>
-          <t>$8393.484513118552</t>
+          <t>$8393.48451311855</t>
         </is>
       </c>
       <c r="S171" s="14" t="inlineStr">
@@ -22757,7 +22759,7 @@
       </c>
       <c r="T171" s="14" t="inlineStr">
         <is>
-          <t>$8914.093563685827</t>
+          <t>$8914.093563685828</t>
         </is>
       </c>
       <c r="U171" s="14" t="inlineStr">
@@ -22877,7 +22879,7 @@
       </c>
       <c r="P172" s="14" t="inlineStr">
         <is>
-          <t>$9568.752616922942</t>
+          <t>$9568.75261692294</t>
         </is>
       </c>
       <c r="Q172" s="14" t="inlineStr">
@@ -22887,7 +22889,7 @@
       </c>
       <c r="R172" s="14" t="inlineStr">
         <is>
-          <t>$8393.484513118552</t>
+          <t>$8393.48451311855</t>
         </is>
       </c>
       <c r="S172" s="14" t="inlineStr">
@@ -22897,7 +22899,7 @@
       </c>
       <c r="T172" s="14" t="inlineStr">
         <is>
-          <t>$8914.093563685827</t>
+          <t>$8914.093563685828</t>
         </is>
       </c>
       <c r="U172" s="14" t="inlineStr">
@@ -23002,7 +23004,7 @@
         <v>4.516112616624085</v>
       </c>
       <c r="L173" s="14" t="n">
-        <v>4.305747160752982</v>
+        <v>4.305747160752983</v>
       </c>
       <c r="M173" s="14" t="n">
         <v>4.224384687111305</v>
@@ -23017,7 +23019,7 @@
       </c>
       <c r="P173" s="14" t="inlineStr">
         <is>
-          <t>$105256.27878615235</t>
+          <t>$105256.27878615232</t>
         </is>
       </c>
       <c r="Q173" s="14" t="inlineStr">
@@ -23027,7 +23029,7 @@
       </c>
       <c r="R173" s="14" t="inlineStr">
         <is>
-          <t>$92328.32964430407</t>
+          <t>$92328.32964430406</t>
         </is>
       </c>
       <c r="S173" s="14" t="inlineStr">
@@ -23037,7 +23039,7 @@
       </c>
       <c r="T173" s="14" t="inlineStr">
         <is>
-          <t>$98055.02920054407</t>
+          <t>$98055.0292005441</t>
         </is>
       </c>
       <c r="U173" s="14" t="inlineStr">
@@ -23142,7 +23144,7 @@
         <v>67.65939491145848</v>
       </c>
       <c r="L174" s="14" t="n">
-        <v>71.94513970719508</v>
+        <v>71.9451397071951</v>
       </c>
       <c r="M174" s="14" t="n">
         <v>75.85873227574945</v>
@@ -23157,7 +23159,7 @@
       </c>
       <c r="P174" s="14" t="inlineStr">
         <is>
-          <t>$1241862.2529822649</t>
+          <t>$1241862.2529822646</t>
         </is>
       </c>
       <c r="Q174" s="14" t="inlineStr">
@@ -23167,7 +23169,7 @@
       </c>
       <c r="R174" s="14" t="inlineStr">
         <is>
-          <t>$1518209.9714887918</t>
+          <t>$1518209.9714887913</t>
         </is>
       </c>
       <c r="S174" s="14" t="inlineStr">
@@ -23177,7 +23179,7 @@
       </c>
       <c r="T174" s="14" t="inlineStr">
         <is>
-          <t>$1811349.8023058272</t>
+          <t>$1811349.8023058276</t>
         </is>
       </c>
       <c r="U174" s="14" t="inlineStr">
@@ -23297,7 +23299,7 @@
       </c>
       <c r="P175" s="14" t="inlineStr">
         <is>
-          <t>$13928.025822249338</t>
+          <t>$13928.025822249336</t>
         </is>
       </c>
       <c r="Q175" s="14" t="inlineStr">
@@ -23307,7 +23309,7 @@
       </c>
       <c r="R175" s="14" t="inlineStr">
         <is>
-          <t>$17972.57345302455</t>
+          <t>$17972.573453024546</t>
         </is>
       </c>
       <c r="S175" s="14" t="inlineStr">
@@ -23317,7 +23319,7 @@
       </c>
       <c r="T175" s="14" t="inlineStr">
         <is>
-          <t>$22951.780352050806</t>
+          <t>$22951.78035205081</t>
         </is>
       </c>
       <c r="U175" s="14" t="inlineStr">
@@ -23437,7 +23439,7 @@
       </c>
       <c r="P176" s="14" t="inlineStr">
         <is>
-          <t>$45963.13912019356</t>
+          <t>$45963.13912019355</t>
         </is>
       </c>
       <c r="Q176" s="14" t="inlineStr">
@@ -23447,7 +23449,7 @@
       </c>
       <c r="R176" s="14" t="inlineStr">
         <is>
-          <t>$59310.731364199964</t>
+          <t>$59310.73136419996</t>
         </is>
       </c>
       <c r="S176" s="14" t="inlineStr">
@@ -23457,7 +23459,7 @@
       </c>
       <c r="T176" s="14" t="inlineStr">
         <is>
-          <t>$75742.60194680665</t>
+          <t>$75742.60194680667</t>
         </is>
       </c>
       <c r="U176" s="14" t="inlineStr">
@@ -23577,7 +23579,7 @@
       </c>
       <c r="P177" s="14" t="inlineStr">
         <is>
-          <t>$175628.50147526938</t>
+          <t>$175628.50147526935</t>
         </is>
       </c>
       <c r="Q177" s="14" t="inlineStr">
@@ -23587,7 +23589,7 @@
       </c>
       <c r="R177" s="14" t="inlineStr">
         <is>
-          <t>$202566.3225317862</t>
+          <t>$202566.32253178614</t>
         </is>
       </c>
       <c r="S177" s="14" t="inlineStr">
@@ -23597,7 +23599,7 @@
       </c>
       <c r="T177" s="14" t="inlineStr">
         <is>
-          <t>$232371.83318284707</t>
+          <t>$232371.8331828471</t>
         </is>
       </c>
       <c r="U177" s="14" t="inlineStr">
@@ -23702,7 +23704,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L178" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M178" s="14" t="n">
         <v>3.66733174555146</v>
@@ -23717,7 +23719,7 @@
       </c>
       <c r="P178" s="14" t="inlineStr">
         <is>
-          <t>$73621.86976567452</t>
+          <t>$73621.8697656745</t>
         </is>
       </c>
       <c r="Q178" s="14" t="inlineStr">
@@ -23727,7 +23729,7 @@
       </c>
       <c r="R178" s="14" t="inlineStr">
         <is>
-          <t>$85075.93147084863</t>
+          <t>$85075.93147084862</t>
         </is>
       </c>
       <c r="S178" s="14" t="inlineStr">
@@ -23737,7 +23739,7 @@
       </c>
       <c r="T178" s="14" t="inlineStr">
         <is>
-          <t>$97780.12201096518</t>
+          <t>$97780.1220109652</t>
         </is>
       </c>
       <c r="U178" s="14" t="inlineStr">
@@ -23857,7 +23859,7 @@
       </c>
       <c r="P179" s="14" t="inlineStr">
         <is>
-          <t>$83076.37885745447</t>
+          <t>$83076.37885745446</t>
         </is>
       </c>
       <c r="Q179" s="14" t="inlineStr">
@@ -23867,7 +23869,7 @@
       </c>
       <c r="R179" s="14" t="inlineStr">
         <is>
-          <t>$48813.98357389415</t>
+          <t>$48813.98357389413</t>
         </is>
       </c>
       <c r="S179" s="14" t="inlineStr">
@@ -23877,7 +23879,7 @@
       </c>
       <c r="T179" s="14" t="inlineStr">
         <is>
-          <t>$44320.740490133336</t>
+          <t>$44320.74049013334</t>
         </is>
       </c>
       <c r="U179" s="14" t="inlineStr">
@@ -23982,7 +23984,7 @@
         <v>1.315897842831073</v>
       </c>
       <c r="L180" s="14" t="n">
-        <v>0.7260346124699948</v>
+        <v>0.7260346124699949</v>
       </c>
       <c r="M180" s="14" t="n">
         <v>0.6378579024362855</v>
@@ -23997,7 +23999,7 @@
       </c>
       <c r="P180" s="14" t="inlineStr">
         <is>
-          <t>$27692.126285818158</t>
+          <t>$27692.12628581815</t>
         </is>
       </c>
       <c r="Q180" s="14" t="inlineStr">
@@ -24007,7 +24009,7 @@
       </c>
       <c r="R180" s="14" t="inlineStr">
         <is>
-          <t>$16271.327857964718</t>
+          <t>$16271.327857964714</t>
         </is>
       </c>
       <c r="S180" s="14" t="inlineStr">
@@ -24017,7 +24019,7 @@
       </c>
       <c r="T180" s="14" t="inlineStr">
         <is>
-          <t>$14773.580163377781</t>
+          <t>$14773.580163377785</t>
         </is>
       </c>
       <c r="U180" s="14" t="inlineStr">
@@ -24122,7 +24124,7 @@
         <v>14.4748762711418</v>
       </c>
       <c r="L181" s="14" t="n">
-        <v>7.986380737169942</v>
+        <v>7.986380737169944</v>
       </c>
       <c r="M181" s="14" t="n">
         <v>7.016436926799138</v>
@@ -24137,7 +24139,7 @@
       </c>
       <c r="P181" s="14" t="inlineStr">
         <is>
-          <t>$304613.3891439997</t>
+          <t>$304613.38914399967</t>
         </is>
       </c>
       <c r="Q181" s="14" t="inlineStr">
@@ -24147,7 +24149,7 @@
       </c>
       <c r="R181" s="14" t="inlineStr">
         <is>
-          <t>$178984.60643761186</t>
+          <t>$178984.60643761183</t>
         </is>
       </c>
       <c r="S181" s="14" t="inlineStr">
@@ -24157,7 +24159,7 @@
       </c>
       <c r="T181" s="14" t="inlineStr">
         <is>
-          <t>$162509.38179715554</t>
+          <t>$162509.38179715557</t>
         </is>
       </c>
       <c r="U181" s="14" t="inlineStr">
@@ -24417,7 +24419,7 @@
       </c>
       <c r="P183" s="14" t="inlineStr">
         <is>
-          <t>$51551.633547635036</t>
+          <t>$51551.63354763503</t>
         </is>
       </c>
       <c r="Q183" s="14" t="inlineStr">
@@ -24427,7 +24429,7 @@
       </c>
       <c r="R183" s="14" t="inlineStr">
         <is>
-          <t>$60940.01492977458</t>
+          <t>$60940.01492977457</t>
         </is>
       </c>
       <c r="S183" s="14" t="inlineStr">
@@ -24437,7 +24439,7 @@
       </c>
       <c r="T183" s="14" t="inlineStr">
         <is>
-          <t>$72389.65759904489</t>
+          <t>$72389.6575990449</t>
         </is>
       </c>
       <c r="U183" s="14" t="inlineStr">
@@ -25257,7 +25259,7 @@
       </c>
       <c r="P189" s="14" t="inlineStr">
         <is>
-          <t>$111300.68582945557</t>
+          <t>$111300.68582945556</t>
         </is>
       </c>
       <c r="Q189" s="14" t="inlineStr">
@@ -25267,7 +25269,7 @@
       </c>
       <c r="R189" s="14" t="inlineStr">
         <is>
-          <t>$159612.01994345486</t>
+          <t>$159612.01994345483</t>
         </is>
       </c>
       <c r="S189" s="14" t="inlineStr">
@@ -25277,7 +25279,7 @@
       </c>
       <c r="T189" s="14" t="inlineStr">
         <is>
-          <t>$216551.56936443527</t>
+          <t>$216551.5693644353</t>
         </is>
       </c>
       <c r="U189" s="14" t="inlineStr">
@@ -25382,7 +25384,7 @@
         <v>151.79552294339</v>
       </c>
       <c r="L190" s="14" t="n">
-        <v>170.7156635834727</v>
+        <v>170.7156635834728</v>
       </c>
       <c r="M190" s="14" t="n">
         <v>190.7450404239447</v>
@@ -25397,7 +25399,7 @@
       </c>
       <c r="P190" s="14" t="inlineStr">
         <is>
-          <t>$793001.6404617627</t>
+          <t>$793001.6404617626</t>
         </is>
       </c>
       <c r="Q190" s="14" t="inlineStr">
@@ -25407,7 +25409,7 @@
       </c>
       <c r="R190" s="14" t="inlineStr">
         <is>
-          <t>$1082749.936946602</t>
+          <t>$1082749.9369466018</t>
         </is>
       </c>
       <c r="S190" s="14" t="inlineStr">
@@ -25417,7 +25419,7 @@
       </c>
       <c r="T190" s="14" t="inlineStr">
         <is>
-          <t>$1403323.5911794866</t>
+          <t>$1403323.591179487</t>
         </is>
       </c>
       <c r="U190" s="14" t="inlineStr">
@@ -25537,7 +25539,7 @@
       </c>
       <c r="P191" s="14" t="inlineStr">
         <is>
-          <t>$699564.6850204577</t>
+          <t>$699564.6850204575</t>
         </is>
       </c>
       <c r="Q191" s="14" t="inlineStr">
@@ -25547,7 +25549,7 @@
       </c>
       <c r="R191" s="14" t="inlineStr">
         <is>
-          <t>$425574.15661073267</t>
+          <t>$425574.15661073255</t>
         </is>
       </c>
       <c r="S191" s="14" t="inlineStr">
@@ -25557,7 +25559,7 @@
       </c>
       <c r="T191" s="14" t="inlineStr">
         <is>
-          <t>$350556.8155177855</t>
+          <t>$350556.81551778555</t>
         </is>
       </c>
       <c r="U191" s="14" t="inlineStr">
@@ -25677,7 +25679,7 @@
       </c>
       <c r="P192" s="14" t="inlineStr">
         <is>
-          <t>$24390.07880078014</t>
+          <t>$24390.078800780135</t>
         </is>
       </c>
       <c r="Q192" s="14" t="inlineStr">
@@ -25687,7 +25689,7 @@
       </c>
       <c r="R192" s="14" t="inlineStr">
         <is>
-          <t>$29584.123129991316</t>
+          <t>$29584.123129991312</t>
         </is>
       </c>
       <c r="S192" s="14" t="inlineStr">
@@ -25697,7 +25699,7 @@
       </c>
       <c r="T192" s="14" t="inlineStr">
         <is>
-          <t>$35100.383765797495</t>
+          <t>$35100.3837657975</t>
         </is>
       </c>
       <c r="U192" s="14" t="inlineStr">
@@ -25817,7 +25819,7 @@
       </c>
       <c r="P193" s="14" t="inlineStr">
         <is>
-          <t>$626871.0738691229</t>
+          <t>$626871.0738691228</t>
         </is>
       </c>
       <c r="Q193" s="14" t="inlineStr">
@@ -25827,7 +25829,7 @@
       </c>
       <c r="R193" s="14" t="inlineStr">
         <is>
-          <t>$732276.6131038385</t>
+          <t>$732276.6131038384</t>
         </is>
       </c>
       <c r="S193" s="14" t="inlineStr">
@@ -25837,7 +25839,7 @@
       </c>
       <c r="T193" s="14" t="inlineStr">
         <is>
-          <t>$842236.5287412592</t>
+          <t>$842236.5287412595</t>
         </is>
       </c>
       <c r="U193" s="14" t="inlineStr">
@@ -25942,7 +25944,7 @@
         <v>12.22269840927197</v>
       </c>
       <c r="L194" s="14" t="n">
-        <v>12.60840983798665</v>
+        <v>12.60840983798666</v>
       </c>
       <c r="M194" s="14" t="n">
         <v>12.87823858462521</v>
@@ -25957,7 +25959,7 @@
       </c>
       <c r="P194" s="14" t="inlineStr">
         <is>
-          <t>$42254.34147021533</t>
+          <t>$42254.34147021532</t>
         </is>
       </c>
       <c r="Q194" s="14" t="inlineStr">
@@ -25967,7 +25969,7 @@
       </c>
       <c r="R194" s="14" t="inlineStr">
         <is>
-          <t>$49359.218108064015</t>
+          <t>$49359.218108064</t>
         </is>
       </c>
       <c r="S194" s="14" t="inlineStr">
@@ -25977,7 +25979,7 @@
       </c>
       <c r="T194" s="14" t="inlineStr">
         <is>
-          <t>$56771.08319014896</t>
+          <t>$56771.08319014897</t>
         </is>
       </c>
       <c r="U194" s="14" t="inlineStr">
@@ -26082,7 +26084,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L195" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M195" s="14" t="n">
         <v>3.66733174555146</v>
@@ -26097,7 +26099,7 @@
       </c>
       <c r="P195" s="14" t="inlineStr">
         <is>
-          <t>$125869.8265073626</t>
+          <t>$125869.82650736257</t>
         </is>
       </c>
       <c r="Q195" s="14" t="inlineStr">
@@ -26107,7 +26109,7 @@
       </c>
       <c r="R195" s="14" t="inlineStr">
         <is>
-          <t>$131929.80035248847</t>
+          <t>$131929.80035248844</t>
         </is>
       </c>
       <c r="S195" s="14" t="inlineStr">
@@ -26117,7 +26119,7 @@
       </c>
       <c r="T195" s="14" t="inlineStr">
         <is>
-          <t>$137533.3967522903</t>
+          <t>$137533.39675229034</t>
         </is>
       </c>
       <c r="U195" s="14" t="inlineStr">
@@ -26237,7 +26239,7 @@
       </c>
       <c r="P196" s="14" t="inlineStr">
         <is>
-          <t>$41956.608835787534</t>
+          <t>$41956.60883578753</t>
         </is>
       </c>
       <c r="Q196" s="14" t="inlineStr">
@@ -26247,7 +26249,7 @@
       </c>
       <c r="R196" s="14" t="inlineStr">
         <is>
-          <t>$43976.60011749616</t>
+          <t>$43976.60011749614</t>
         </is>
       </c>
       <c r="S196" s="14" t="inlineStr">
@@ -26257,7 +26259,7 @@
       </c>
       <c r="T196" s="14" t="inlineStr">
         <is>
-          <t>$45844.46558409675</t>
+          <t>$45844.46558409676</t>
         </is>
       </c>
       <c r="U196" s="14" t="inlineStr">
@@ -26362,7 +26364,7 @@
         <v>9.319843307005538</v>
       </c>
       <c r="L197" s="14" t="n">
-        <v>9.578120669616998</v>
+        <v>9.578120669617</v>
       </c>
       <c r="M197" s="14" t="n">
         <v>9.779551321470558</v>
@@ -26377,7 +26379,7 @@
       </c>
       <c r="P197" s="14" t="inlineStr">
         <is>
-          <t>$335652.5051596691</t>
+          <t>$335652.50515966903</t>
         </is>
       </c>
       <c r="Q197" s="14" t="inlineStr">
@@ -26387,7 +26389,7 @@
       </c>
       <c r="R197" s="14" t="inlineStr">
         <is>
-          <t>$351812.41781514237</t>
+          <t>$351812.4178151423</t>
         </is>
       </c>
       <c r="S197" s="14" t="inlineStr">
@@ -26397,7 +26399,7 @@
       </c>
       <c r="T197" s="14" t="inlineStr">
         <is>
-          <t>$366755.3252750741</t>
+          <t>$366755.3252750742</t>
         </is>
       </c>
       <c r="U197" s="14" t="inlineStr">
@@ -26642,7 +26644,7 @@
         <v>5.824902066878461</v>
       </c>
       <c r="L199" s="14" t="n">
-        <v>5.986325418510623</v>
+        <v>5.986325418510625</v>
       </c>
       <c r="M199" s="14" t="n">
         <v>6.1122195759191</v>
@@ -26657,7 +26659,7 @@
       </c>
       <c r="P199" s="14" t="inlineStr">
         <is>
-          <t>$106143.97947089301</t>
+          <t>$106143.97947089298</t>
         </is>
       </c>
       <c r="Q199" s="14" t="inlineStr">
@@ -26667,7 +26669,7 @@
       </c>
       <c r="R199" s="14" t="inlineStr">
         <is>
-          <t>$121158.9908361434</t>
+          <t>$121158.99083614339</t>
         </is>
       </c>
       <c r="S199" s="14" t="inlineStr">
@@ -26677,7 +26679,7 @@
       </c>
       <c r="T199" s="14" t="inlineStr">
         <is>
-          <t>$137549.78665649</t>
+          <t>$137549.78665649003</t>
         </is>
       </c>
       <c r="U199" s="14" t="inlineStr">
@@ -26797,7 +26799,7 @@
       </c>
       <c r="P200" s="14" t="inlineStr">
         <is>
-          <t>$212287.95894178603</t>
+          <t>$212287.95894178597</t>
         </is>
       </c>
       <c r="Q200" s="14" t="inlineStr">
@@ -26807,7 +26809,7 @@
       </c>
       <c r="R200" s="14" t="inlineStr">
         <is>
-          <t>$242317.9816722868</t>
+          <t>$242317.98167228678</t>
         </is>
       </c>
       <c r="S200" s="14" t="inlineStr">
@@ -26817,7 +26819,7 @@
       </c>
       <c r="T200" s="14" t="inlineStr">
         <is>
-          <t>$275099.57331298</t>
+          <t>$275099.57331298006</t>
         </is>
       </c>
       <c r="U200" s="14" t="inlineStr">
@@ -26922,7 +26924,7 @@
         <v>3.007068259192379</v>
       </c>
       <c r="L201" s="14" t="n">
-        <v>3.341626077728671</v>
+        <v>3.341626077728672</v>
       </c>
       <c r="M201" s="14" t="n">
         <v>3.713279211518171</v>
@@ -26937,7 +26939,7 @@
       </c>
       <c r="P201" s="14" t="inlineStr">
         <is>
-          <t>$50704.92491811343</t>
+          <t>$50704.924918113415</t>
         </is>
       </c>
       <c r="Q201" s="14" t="inlineStr">
@@ -26947,7 +26949,7 @@
       </c>
       <c r="R201" s="14" t="inlineStr">
         <is>
-          <t>$69032.32574006023</t>
+          <t>$69032.32574006022</t>
         </is>
       </c>
       <c r="S201" s="14" t="inlineStr">
@@ -26957,7 +26959,7 @@
       </c>
       <c r="T201" s="14" t="inlineStr">
         <is>
-          <t>$93976.36120680426</t>
+          <t>$93976.36120680429</t>
         </is>
       </c>
       <c r="U201" s="14" t="inlineStr">
@@ -27062,7 +27064,7 @@
         <v>4.510602388788568</v>
       </c>
       <c r="L202" s="14" t="n">
-        <v>5.012439116593007</v>
+        <v>5.012439116593008</v>
       </c>
       <c r="M202" s="14" t="n">
         <v>5.569918817277257</v>
@@ -27077,7 +27079,7 @@
       </c>
       <c r="P202" s="14" t="inlineStr">
         <is>
-          <t>$152114.77475434024</t>
+          <t>$152114.7747543402</t>
         </is>
       </c>
       <c r="Q202" s="14" t="inlineStr">
@@ -27087,7 +27089,7 @@
       </c>
       <c r="R202" s="14" t="inlineStr">
         <is>
-          <t>$207096.97722018068</t>
+          <t>$207096.97722018062</t>
         </is>
       </c>
       <c r="S202" s="14" t="inlineStr">
@@ -27097,7 +27099,7 @@
       </c>
       <c r="T202" s="14" t="inlineStr">
         <is>
-          <t>$281929.0836204128</t>
+          <t>$281929.08362041286</t>
         </is>
       </c>
       <c r="U202" s="14" t="inlineStr">
@@ -27217,7 +27219,7 @@
       </c>
       <c r="P203" s="14" t="inlineStr">
         <is>
-          <t>$200151.51996954193</t>
+          <t>$200151.5199695419</t>
         </is>
       </c>
       <c r="Q203" s="14" t="inlineStr">
@@ -27227,7 +27229,7 @@
       </c>
       <c r="R203" s="14" t="inlineStr">
         <is>
-          <t>$225014.8436906637</t>
+          <t>$225014.84369066363</t>
         </is>
       </c>
       <c r="S203" s="14" t="inlineStr">
@@ -27237,7 +27239,7 @@
       </c>
       <c r="T203" s="14" t="inlineStr">
         <is>
-          <t>$250153.98245203766</t>
+          <t>$250153.98245203772</t>
         </is>
       </c>
       <c r="U203" s="14" t="inlineStr">
@@ -27357,7 +27359,7 @@
       </c>
       <c r="P204" s="14" t="inlineStr">
         <is>
-          <t>$79441.90808546597</t>
+          <t>$79441.90808546596</t>
         </is>
       </c>
       <c r="Q204" s="14" t="inlineStr">
@@ -27367,7 +27369,7 @@
       </c>
       <c r="R204" s="14" t="inlineStr">
         <is>
-          <t>$89310.38112056015</t>
+          <t>$89310.38112056014</t>
         </is>
       </c>
       <c r="S204" s="14" t="inlineStr">
@@ -27377,7 +27379,7 @@
       </c>
       <c r="T204" s="14" t="inlineStr">
         <is>
-          <t>$99288.32758398326</t>
+          <t>$99288.32758398328</t>
         </is>
       </c>
       <c r="U204" s="14" t="inlineStr">
@@ -27497,7 +27499,7 @@
       </c>
       <c r="P205" s="14" t="inlineStr">
         <is>
-          <t>$133438.6099962448</t>
+          <t>$133438.60999624478</t>
         </is>
       </c>
       <c r="Q205" s="14" t="inlineStr">
@@ -27507,7 +27509,7 @@
       </c>
       <c r="R205" s="14" t="inlineStr">
         <is>
-          <t>$150014.6887476728</t>
+          <t>$150014.68874767277</t>
         </is>
       </c>
       <c r="S205" s="14" t="inlineStr">
@@ -27517,7 +27519,7 @@
       </c>
       <c r="T205" s="14" t="inlineStr">
         <is>
-          <t>$166774.65006763153</t>
+          <t>$166774.6500676316</t>
         </is>
       </c>
       <c r="U205" s="14" t="inlineStr">
@@ -27622,7 +27624,7 @@
         <v>19.89982203278191</v>
       </c>
       <c r="L206" s="14" t="n">
-        <v>21.16033520799855</v>
+        <v>21.16033520799856</v>
       </c>
       <c r="M206" s="14" t="n">
         <v>22.31139184580866</v>
@@ -27637,7 +27639,7 @@
       </c>
       <c r="P206" s="14" t="inlineStr">
         <is>
-          <t>$166815.93481888357</t>
+          <t>$166815.93481888354</t>
         </is>
       </c>
       <c r="Q206" s="14" t="inlineStr">
@@ -27647,7 +27649,7 @@
       </c>
       <c r="R206" s="14" t="inlineStr">
         <is>
-          <t>$187538.22855851945</t>
+          <t>$187538.22855851942</t>
         </is>
       </c>
       <c r="S206" s="14" t="inlineStr">
@@ -27657,7 +27659,7 @@
       </c>
       <c r="T206" s="14" t="inlineStr">
         <is>
-          <t>$208490.39986183203</t>
+          <t>$208490.39986183206</t>
         </is>
       </c>
       <c r="U206" s="14" t="inlineStr">
@@ -27762,7 +27764,7 @@
         <v>2.653309604370921</v>
       </c>
       <c r="L207" s="14" t="n">
-        <v>2.82137802773314</v>
+        <v>2.821378027733141</v>
       </c>
       <c r="M207" s="14" t="n">
         <v>2.974852246107821</v>
@@ -27777,7 +27779,7 @@
       </c>
       <c r="P207" s="14" t="inlineStr">
         <is>
-          <t>$6448.083294746532</t>
+          <t>$6448.083294746531</t>
         </is>
       </c>
       <c r="Q207" s="14" t="inlineStr">
@@ -27787,7 +27789,7 @@
       </c>
       <c r="R207" s="14" t="inlineStr">
         <is>
-          <t>$8148.2463593151315</t>
+          <t>$8148.24635931513</t>
         </is>
       </c>
       <c r="S207" s="14" t="inlineStr">
@@ -27797,7 +27799,7 @@
       </c>
       <c r="T207" s="14" t="inlineStr">
         <is>
-          <t>$9979.559188837902</t>
+          <t>$9979.559188837904</t>
         </is>
       </c>
       <c r="U207" s="14" t="inlineStr">
@@ -27917,7 +27919,7 @@
       </c>
       <c r="P208" s="14" t="inlineStr">
         <is>
-          <t>$121717.76284820362</t>
+          <t>$121717.7628482036</t>
         </is>
       </c>
       <c r="Q208" s="14" t="inlineStr">
@@ -27927,7 +27929,7 @@
       </c>
       <c r="R208" s="14" t="inlineStr">
         <is>
-          <t>$134199.97345667868</t>
+          <t>$134199.97345667865</t>
         </is>
       </c>
       <c r="S208" s="14" t="inlineStr">
@@ -27937,7 +27939,7 @@
       </c>
       <c r="T208" s="14" t="inlineStr">
         <is>
-          <t>$147161.7320408899</t>
+          <t>$147161.73204088997</t>
         </is>
       </c>
       <c r="U208" s="14" t="inlineStr">
@@ -28042,7 +28044,7 @@
         <v>157.2723558057184</v>
       </c>
       <c r="L209" s="14" t="n">
-        <v>161.6307862997868</v>
+        <v>161.6307862997869</v>
       </c>
       <c r="M209" s="14" t="n">
         <v>165.0299285498157</v>
@@ -28057,7 +28059,7 @@
       </c>
       <c r="P209" s="14" t="inlineStr">
         <is>
-          <t>$1716220.4561596708</t>
+          <t>$1716220.4561596706</t>
         </is>
       </c>
       <c r="Q209" s="14" t="inlineStr">
@@ -28067,7 +28069,7 @@
       </c>
       <c r="R209" s="14" t="inlineStr">
         <is>
-          <t>$1892219.6257391693</t>
+          <t>$1892219.6257391688</t>
         </is>
       </c>
       <c r="S209" s="14" t="inlineStr">
@@ -28077,7 +28079,7 @@
       </c>
       <c r="T209" s="14" t="inlineStr">
         <is>
-          <t>$2074980.421776548</t>
+          <t>$2074980.4217765485</t>
         </is>
       </c>
       <c r="U209" s="14" t="inlineStr">
@@ -28182,7 +28184,7 @@
         <v>27.95952992101661</v>
       </c>
       <c r="L210" s="14" t="n">
-        <v>28.73436200885099</v>
+        <v>28.734362008851</v>
       </c>
       <c r="M210" s="14" t="n">
         <v>29.33865396441168</v>
@@ -28197,7 +28199,7 @@
       </c>
       <c r="P210" s="14" t="inlineStr">
         <is>
-          <t>$340809.73597497016</t>
+          <t>$340809.7359749701</t>
         </is>
       </c>
       <c r="Q210" s="14" t="inlineStr">
@@ -28207,7 +28209,7 @@
       </c>
       <c r="R210" s="14" t="inlineStr">
         <is>
-          <t>$375759.9256787003</t>
+          <t>$375759.9256787002</t>
         </is>
       </c>
       <c r="S210" s="14" t="inlineStr">
@@ -28217,7 +28219,7 @@
       </c>
       <c r="T210" s="14" t="inlineStr">
         <is>
-          <t>$412052.84971449175</t>
+          <t>$412052.84971449187</t>
         </is>
       </c>
       <c r="U210" s="14" t="inlineStr">
@@ -28322,7 +28324,7 @@
         <v>6.79185824858757</v>
       </c>
       <c r="L211" s="14" t="n">
-        <v>7.141891958077824</v>
+        <v>7.141891958077825</v>
       </c>
       <c r="M211" s="14" t="n">
         <v>7.548978056139772</v>
@@ -28337,7 +28339,7 @@
       </c>
       <c r="P211" s="14" t="inlineStr">
         <is>
-          <t>$296805.1345864124</t>
+          <t>$296805.13458641234</t>
         </is>
       </c>
       <c r="Q211" s="14" t="inlineStr">
@@ -28347,7 +28349,7 @@
       </c>
       <c r="R211" s="14" t="inlineStr">
         <is>
-          <t>$329199.56059502653</t>
+          <t>$329199.5605950265</t>
         </is>
       </c>
       <c r="S211" s="14" t="inlineStr">
@@ -28357,7 +28359,7 @@
       </c>
       <c r="T211" s="14" t="inlineStr">
         <is>
-          <t>$389645.80792046024</t>
+          <t>$389645.8079204603</t>
         </is>
       </c>
       <c r="U211" s="14" t="inlineStr">
@@ -28477,7 +28479,7 @@
       </c>
       <c r="P212" s="14" t="inlineStr">
         <is>
-          <t>$128655.85273365755</t>
+          <t>$128655.85273365752</t>
         </is>
       </c>
       <c r="Q212" s="14" t="inlineStr">
@@ -28487,7 +28489,7 @@
       </c>
       <c r="R212" s="14" t="inlineStr">
         <is>
-          <t>$144637.80538443264</t>
+          <t>$144637.8053844326</t>
         </is>
       </c>
       <c r="S212" s="14" t="inlineStr">
@@ -28497,7 +28499,7 @@
       </c>
       <c r="T212" s="14" t="inlineStr">
         <is>
-          <t>$160797.04981498452</t>
+          <t>$160797.04981498455</t>
         </is>
       </c>
       <c r="U212" s="14" t="inlineStr">
@@ -28617,7 +28619,7 @@
       </c>
       <c r="P213" s="14" t="inlineStr">
         <is>
-          <t>$110762.95550063117</t>
+          <t>$110762.95550063116</t>
         </is>
       </c>
       <c r="Q213" s="14" t="inlineStr">
@@ -28627,7 +28629,7 @@
       </c>
       <c r="R213" s="14" t="inlineStr">
         <is>
-          <t>$120553.87841045824</t>
+          <t>$120553.87841045822</t>
         </is>
       </c>
       <c r="S213" s="14" t="inlineStr">
@@ -28637,7 +28639,7 @@
       </c>
       <c r="T213" s="14" t="inlineStr">
         <is>
-          <t>$134022.4150984139</t>
+          <t>$134022.41509841394</t>
         </is>
       </c>
       <c r="U213" s="14" t="inlineStr">
@@ -28757,7 +28759,7 @@
       </c>
       <c r="P214" s="14" t="inlineStr">
         <is>
-          <t>$116037.38195304219</t>
+          <t>$116037.38195304216</t>
         </is>
       </c>
       <c r="Q214" s="14" t="inlineStr">
@@ -28767,7 +28769,7 @@
       </c>
       <c r="R214" s="14" t="inlineStr">
         <is>
-          <t>$126294.53928714672</t>
+          <t>$126294.53928714669</t>
         </is>
       </c>
       <c r="S214" s="14" t="inlineStr">
@@ -28777,7 +28779,7 @@
       </c>
       <c r="T214" s="14" t="inlineStr">
         <is>
-          <t>$140404.43486500508</t>
+          <t>$140404.4348650051</t>
         </is>
       </c>
       <c r="U214" s="14" t="inlineStr">
@@ -28882,7 +28884,7 @@
         <v>0.7235950258333755</v>
       </c>
       <c r="L215" s="14" t="n">
-        <v>0.766543670160972</v>
+        <v>0.7665436701609722</v>
       </c>
       <c r="M215" s="14" t="n">
         <v>0.8082412695154753</v>
@@ -28897,7 +28899,7 @@
       </c>
       <c r="P215" s="14" t="inlineStr">
         <is>
-          <t>$10548.86227185159</t>
+          <t>$10548.862271851589</t>
         </is>
       </c>
       <c r="Q215" s="14" t="inlineStr">
@@ -28907,7 +28909,7 @@
       </c>
       <c r="R215" s="14" t="inlineStr">
         <is>
-          <t>$11481.331948407787</t>
+          <t>$11481.331948407786</t>
         </is>
       </c>
       <c r="S215" s="14" t="inlineStr">
@@ -28917,7 +28919,7 @@
       </c>
       <c r="T215" s="14" t="inlineStr">
         <is>
-          <t>$12764.0508672237</t>
+          <t>$12764.050867223703</t>
         </is>
       </c>
       <c r="U215" s="14" t="inlineStr">
@@ -29037,7 +29039,7 @@
       </c>
       <c r="P216" s="14" t="inlineStr">
         <is>
-          <t>$61139.516518887605</t>
+          <t>$61139.51651888759</t>
         </is>
       </c>
       <c r="Q216" s="14" t="inlineStr">
@@ -29047,7 +29049,7 @@
       </c>
       <c r="R216" s="14" t="inlineStr">
         <is>
-          <t>$63876.9128739145</t>
+          <t>$63876.91287391449</t>
         </is>
       </c>
       <c r="S216" s="14" t="inlineStr">
@@ -29057,7 +29059,7 @@
       </c>
       <c r="T216" s="14" t="inlineStr">
         <is>
-          <t>$71004.0609727928</t>
+          <t>$71004.06097279281</t>
         </is>
       </c>
       <c r="U216" s="14" t="inlineStr">
@@ -29162,7 +29164,7 @@
         <v>0.7235950258333755</v>
       </c>
       <c r="L217" s="14" t="n">
-        <v>0.766543670160972</v>
+        <v>0.7665436701609722</v>
       </c>
       <c r="M217" s="14" t="n">
         <v>0.8082412695154753</v>
@@ -29177,7 +29179,7 @@
       </c>
       <c r="P217" s="14" t="inlineStr">
         <is>
-          <t>$15823.293407777388</t>
+          <t>$15823.293407777384</t>
         </is>
       </c>
       <c r="Q217" s="14" t="inlineStr">
@@ -29187,7 +29189,7 @@
       </c>
       <c r="R217" s="14" t="inlineStr">
         <is>
-          <t>$17221.99792261168</t>
+          <t>$17221.997922611677</t>
         </is>
       </c>
       <c r="S217" s="14" t="inlineStr">
@@ -29197,7 +29199,7 @@
       </c>
       <c r="T217" s="14" t="inlineStr">
         <is>
-          <t>$19146.076300835553</t>
+          <t>$19146.076300835557</t>
         </is>
       </c>
       <c r="U217" s="14" t="inlineStr">
@@ -29317,7 +29319,7 @@
       </c>
       <c r="P218" s="14" t="inlineStr">
         <is>
-          <t>$34048.638438578004</t>
+          <t>$34048.638438578</t>
         </is>
       </c>
       <c r="Q218" s="14" t="inlineStr">
@@ -29327,7 +29329,7 @@
       </c>
       <c r="R218" s="14" t="inlineStr">
         <is>
-          <t>$38178.04946341709</t>
+          <t>$38178.04946341708</t>
         </is>
       </c>
       <c r="S218" s="14" t="inlineStr">
@@ -29337,7 +29339,7 @@
       </c>
       <c r="T218" s="14" t="inlineStr">
         <is>
-          <t>$44646.47607336151</t>
+          <t>$44646.47607336152</t>
         </is>
       </c>
       <c r="U218" s="14" t="inlineStr">
@@ -29457,7 +29459,7 @@
       </c>
       <c r="P219" s="14" t="inlineStr">
         <is>
-          <t>$136194.55375431202</t>
+          <t>$136194.553754312</t>
         </is>
       </c>
       <c r="Q219" s="14" t="inlineStr">
@@ -29467,7 +29469,7 @@
       </c>
       <c r="R219" s="14" t="inlineStr">
         <is>
-          <t>$152712.19785366836</t>
+          <t>$152712.19785366833</t>
         </is>
       </c>
       <c r="S219" s="14" t="inlineStr">
@@ -29477,7 +29479,7 @@
       </c>
       <c r="T219" s="14" t="inlineStr">
         <is>
-          <t>$178585.90429344604</t>
+          <t>$178585.90429344607</t>
         </is>
       </c>
       <c r="U219" s="14" t="inlineStr">
@@ -30142,7 +30144,7 @@
         <v>6.530918071567588</v>
       </c>
       <c r="L224" s="14" t="n">
-        <v>5.991973148419847</v>
+        <v>5.991973148419848</v>
       </c>
       <c r="M224" s="14" t="n">
         <v>5.479139987473489</v>
@@ -30157,7 +30159,7 @@
       </c>
       <c r="P224" s="14" t="inlineStr">
         <is>
-          <t>$4615.517681275421</t>
+          <t>$4615.51768127542</t>
         </is>
       </c>
       <c r="Q224" s="14" t="inlineStr">
@@ -30167,7 +30169,7 @@
       </c>
       <c r="R224" s="14" t="inlineStr">
         <is>
-          <t>$3843.251577382809</t>
+          <t>$3843.251577382808</t>
         </is>
       </c>
       <c r="S224" s="14" t="inlineStr">
@@ -30177,7 +30179,7 @@
       </c>
       <c r="T224" s="14" t="inlineStr">
         <is>
-          <t>$3213.4526278870376</t>
+          <t>$3213.452627887038</t>
         </is>
       </c>
       <c r="U224" s="14" t="inlineStr">
@@ -30282,7 +30284,7 @@
         <v>4.976419728356506</v>
       </c>
       <c r="L225" s="14" t="n">
-        <v>3.946350311015065</v>
+        <v>3.946350311015066</v>
       </c>
       <c r="M225" s="14" t="n">
         <v>0.5979047009929911</v>
@@ -30297,7 +30299,7 @@
       </c>
       <c r="P225" s="14" t="inlineStr">
         <is>
-          <t>$15022.562327249074</t>
+          <t>$15022.56232724907</t>
         </is>
       </c>
       <c r="Q225" s="14" t="inlineStr">
@@ -30307,7 +30309,7 @@
       </c>
       <c r="R225" s="14" t="inlineStr">
         <is>
-          <t>$13609.913528321911</t>
+          <t>$13609.913528321908</t>
         </is>
       </c>
       <c r="S225" s="14" t="inlineStr">
@@ -30317,7 +30319,7 @@
       </c>
       <c r="T225" s="14" t="inlineStr">
         <is>
-          <t>$786.5146990528218</t>
+          <t>$786.514699052822</t>
         </is>
       </c>
       <c r="U225" s="14" t="inlineStr">
@@ -30422,7 +30424,7 @@
         <v>58.37281129616025</v>
       </c>
       <c r="L226" s="14" t="n">
-        <v>62.07031661012908</v>
+        <v>62.0703166101291</v>
       </c>
       <c r="M226" s="14" t="n">
         <v>65.44674941437208</v>
@@ -30437,7 +30439,7 @@
       </c>
       <c r="P226" s="14" t="inlineStr">
         <is>
-          <t>$1115363.8187917534</t>
+          <t>$1115363.8187917531</t>
         </is>
       </c>
       <c r="Q226" s="14" t="inlineStr">
@@ -30447,7 +30449,7 @@
       </c>
       <c r="R226" s="14" t="inlineStr">
         <is>
-          <t>$1371942.0429962927</t>
+          <t>$1371942.0429962922</t>
         </is>
       </c>
       <c r="S226" s="14" t="inlineStr">
@@ -30457,7 +30459,7 @@
       </c>
       <c r="T226" s="14" t="inlineStr">
         <is>
-          <t>$1656011.2699815559</t>
+          <t>$1656011.2699815563</t>
         </is>
       </c>
       <c r="U226" s="14" t="inlineStr">
@@ -30562,7 +30564,7 @@
         <v>23.87978643933828</v>
       </c>
       <c r="L227" s="14" t="n">
-        <v>25.39240224959826</v>
+        <v>25.39240224959827</v>
       </c>
       <c r="M227" s="14" t="n">
         <v>26.77367021497039</v>
@@ -30577,7 +30579,7 @@
       </c>
       <c r="P227" s="14" t="inlineStr">
         <is>
-          <t>$439869.7197128381</t>
+          <t>$439869.71971283806</t>
         </is>
       </c>
       <c r="Q227" s="14" t="inlineStr">
@@ -30587,7 +30589,7 @@
       </c>
       <c r="R227" s="14" t="inlineStr">
         <is>
-          <t>$515520.0193684842</t>
+          <t>$515520.0193684841</t>
         </is>
       </c>
       <c r="S227" s="14" t="inlineStr">
@@ -30597,7 +30599,7 @@
       </c>
       <c r="T227" s="14" t="inlineStr">
         <is>
-          <t>$595009.1805912314</t>
+          <t>$595009.1805912316</t>
         </is>
       </c>
       <c r="U227" s="14" t="inlineStr">
@@ -30702,7 +30704,7 @@
         <v>8.708734524623885</v>
       </c>
       <c r="L228" s="14" t="n">
-        <v>9.080419491521088</v>
+        <v>9.08041949152109</v>
       </c>
       <c r="M228" s="14" t="n">
         <v>9.446282516440576</v>
@@ -30717,7 +30719,7 @@
       </c>
       <c r="P228" s="14" t="inlineStr">
         <is>
-          <t>$50041.870586467034</t>
+          <t>$50041.87058646702</t>
         </is>
       </c>
       <c r="Q228" s="14" t="inlineStr">
@@ -30727,7 +30729,7 @@
       </c>
       <c r="R228" s="14" t="inlineStr">
         <is>
-          <t>$59272.81656697929</t>
+          <t>$59272.81656697927</t>
         </is>
       </c>
       <c r="S228" s="14" t="inlineStr">
@@ -30737,7 +30739,7 @@
       </c>
       <c r="T228" s="14" t="inlineStr">
         <is>
-          <t>$70118.06673136685</t>
+          <t>$70118.06673136687</t>
         </is>
       </c>
       <c r="U228" s="14" t="inlineStr">
@@ -32382,7 +32384,7 @@
         <v>89.22569838768536</v>
       </c>
       <c r="L240" s="14" t="n">
-        <v>92.04139181730257</v>
+        <v>92.04139181730258</v>
       </c>
       <c r="M240" s="14" t="n">
         <v>94.01114166776402</v>
@@ -32397,7 +32399,7 @@
       </c>
       <c r="P240" s="14" t="inlineStr">
         <is>
-          <t>$179253.60008429977</t>
+          <t>$179253.60008429972</t>
         </is>
       </c>
       <c r="Q240" s="14" t="inlineStr">
@@ -32407,7 +32409,7 @@
       </c>
       <c r="R240" s="14" t="inlineStr">
         <is>
-          <t>$209394.28317569153</t>
+          <t>$209394.2831756915</t>
         </is>
       </c>
       <c r="S240" s="14" t="inlineStr">
@@ -32417,7 +32419,7 @@
       </c>
       <c r="T240" s="14" t="inlineStr">
         <is>
-          <t>$240837.28886634615</t>
+          <t>$240837.2888663462</t>
         </is>
       </c>
       <c r="U240" s="14" t="inlineStr">
@@ -32677,7 +32679,7 @@
       </c>
       <c r="P242" s="14" t="inlineStr">
         <is>
-          <t>$130343.63391400123</t>
+          <t>$130343.6339140012</t>
         </is>
       </c>
       <c r="Q242" s="14" t="inlineStr">
@@ -32687,7 +32689,7 @@
       </c>
       <c r="R242" s="14" t="inlineStr">
         <is>
-          <t>$142423.05230870045</t>
+          <t>$142423.05230870043</t>
         </is>
       </c>
       <c r="S242" s="14" t="inlineStr">
@@ -32697,7 +32699,7 @@
       </c>
       <c r="T242" s="14" t="inlineStr">
         <is>
-          <t>$154144.28646907132</t>
+          <t>$154144.28646907135</t>
         </is>
       </c>
       <c r="U242" s="14" t="inlineStr">
@@ -32802,7 +32804,7 @@
         <v>175.7731735629926</v>
       </c>
       <c r="L243" s="14" t="n">
-        <v>207.6472516936747</v>
+        <v>207.6472516936748</v>
       </c>
       <c r="M243" s="14" t="n">
         <v>245.2928960163071</v>
@@ -32817,7 +32819,7 @@
       </c>
       <c r="P243" s="14" t="inlineStr">
         <is>
-          <t>$161419.57125561175</t>
+          <t>$161419.57125561172</t>
         </is>
       </c>
       <c r="Q243" s="14" t="inlineStr">
@@ -32827,7 +32829,7 @@
       </c>
       <c r="R243" s="14" t="inlineStr">
         <is>
-          <t>$241171.45911706582</t>
+          <t>$241171.45911706577</t>
         </is>
       </c>
       <c r="S243" s="14" t="inlineStr">
@@ -32837,7 +32839,7 @@
       </c>
       <c r="T243" s="14" t="inlineStr">
         <is>
-          <t>$359225.78084408573</t>
+          <t>$359225.7808440858</t>
         </is>
       </c>
       <c r="U243" s="14" t="inlineStr">
@@ -32942,7 +32944,7 @@
         <v>235.5722944658663</v>
       </c>
       <c r="L244" s="14" t="n">
-        <v>278.2901311358527</v>
+        <v>278.2901311358528</v>
       </c>
       <c r="M244" s="14" t="n">
         <v>328.7430565167003</v>
@@ -32957,7 +32959,7 @@
       </c>
       <c r="P244" s="14" t="inlineStr">
         <is>
-          <t>$231194.48270158586</t>
+          <t>$231194.4827015858</t>
         </is>
       </c>
       <c r="Q244" s="14" t="inlineStr">
@@ -32967,7 +32969,7 @@
       </c>
       <c r="R244" s="14" t="inlineStr">
         <is>
-          <t>$345419.7672515395</t>
+          <t>$345419.7672515394</t>
         </is>
       </c>
       <c r="S244" s="14" t="inlineStr">
@@ -32977,7 +32979,7 @@
       </c>
       <c r="T244" s="14" t="inlineStr">
         <is>
-          <t>$514504.0215960454</t>
+          <t>$514504.0215960455</t>
         </is>
       </c>
       <c r="U244" s="14" t="inlineStr">
@@ -33082,7 +33084,7 @@
         <v>3.73231479626738</v>
       </c>
       <c r="L245" s="14" t="n">
-        <v>3.891608353509038</v>
+        <v>3.891608353509039</v>
       </c>
       <c r="M245" s="14" t="n">
         <v>4.048406792760247</v>
@@ -33097,7 +33099,7 @@
       </c>
       <c r="P245" s="14" t="inlineStr">
         <is>
-          <t>$61574.63027080377</t>
+          <t>$61574.630270803755</t>
         </is>
       </c>
       <c r="Q245" s="14" t="inlineStr">
@@ -33107,7 +33109,7 @@
       </c>
       <c r="R245" s="14" t="inlineStr">
         <is>
-          <t>$74760.29639393913</t>
+          <t>$74760.29639393912</t>
         </is>
       </c>
       <c r="S245" s="14" t="inlineStr">
@@ -33117,7 +33119,7 @@
       </c>
       <c r="T245" s="14" t="inlineStr">
         <is>
-          <t>$90246.28135815937</t>
+          <t>$90246.2813581594</t>
         </is>
       </c>
       <c r="U245" s="14" t="inlineStr">
@@ -33222,7 +33224,7 @@
         <v>41.05546275894118</v>
       </c>
       <c r="L246" s="14" t="n">
-        <v>42.80769188859941</v>
+        <v>42.80769188859943</v>
       </c>
       <c r="M246" s="14" t="n">
         <v>44.53247472036271</v>
@@ -33237,7 +33239,7 @@
       </c>
       <c r="P246" s="14" t="inlineStr">
         <is>
-          <t>$122834.7526310805</t>
+          <t>$122834.75263108047</t>
         </is>
       </c>
       <c r="Q246" s="14" t="inlineStr">
@@ -33247,7 +33249,7 @@
       </c>
       <c r="R246" s="14" t="inlineStr">
         <is>
-          <t>$133699.62959967816</t>
+          <t>$133699.62959967813</t>
         </is>
       </c>
       <c r="S246" s="14" t="inlineStr">
@@ -33257,7 +33259,7 @@
       </c>
       <c r="T246" s="14" t="inlineStr">
         <is>
-          <t>$128545.58651266966</t>
+          <t>$128545.58651266969</t>
         </is>
       </c>
       <c r="U246" s="14" t="inlineStr">
@@ -33362,7 +33364,7 @@
         <v>2.39352617366414</v>
       </c>
       <c r="L247" s="14" t="n">
-        <v>2.111707805624269</v>
+        <v>2.11170780562427</v>
       </c>
       <c r="M247" s="14" t="n">
         <v>1.831910398328788</v>
@@ -33377,7 +33379,7 @@
       </c>
       <c r="P247" s="14" t="inlineStr">
         <is>
-          <t>$80918.92681515183</t>
+          <t>$80918.92681515182</t>
         </is>
       </c>
       <c r="Q247" s="14" t="inlineStr">
@@ -33387,7 +33389,7 @@
       </c>
       <c r="R247" s="14" t="inlineStr">
         <is>
-          <t>$63148.510219163356</t>
+          <t>$63148.51021916334</t>
         </is>
       </c>
       <c r="S247" s="14" t="inlineStr">
@@ -33397,7 +33399,7 @@
       </c>
       <c r="T247" s="14" t="inlineStr">
         <is>
-          <t>$47521.695420372256</t>
+          <t>$47521.69542037227</t>
         </is>
       </c>
       <c r="U247" s="14" t="inlineStr">
@@ -33517,7 +33519,7 @@
       </c>
       <c r="P248" s="14" t="inlineStr">
         <is>
-          <t>$27542.407015575158</t>
+          <t>$27542.407015575154</t>
         </is>
       </c>
       <c r="Q248" s="14" t="inlineStr">
@@ -33527,7 +33529,7 @@
       </c>
       <c r="R248" s="14" t="inlineStr">
         <is>
-          <t>$30392.92558466933</t>
+          <t>$30392.925584669323</t>
         </is>
       </c>
       <c r="S248" s="14" t="inlineStr">
@@ -33537,7 +33539,7 @@
       </c>
       <c r="T248" s="14" t="inlineStr">
         <is>
-          <t>$29354.68038336563</t>
+          <t>$29354.680383365638</t>
         </is>
       </c>
       <c r="U248" s="14" t="inlineStr">
@@ -33657,7 +33659,7 @@
       </c>
       <c r="P249" s="14" t="inlineStr">
         <is>
-          <t>$743512.6922437344</t>
+          <t>$743512.6922437343</t>
         </is>
       </c>
       <c r="Q249" s="14" t="inlineStr">
@@ -33667,7 +33669,7 @@
       </c>
       <c r="R249" s="14" t="inlineStr">
         <is>
-          <t>$902729.4033327479</t>
+          <t>$902729.4033327476</t>
         </is>
       </c>
       <c r="S249" s="14" t="inlineStr">
@@ -33677,7 +33679,7 @@
       </c>
       <c r="T249" s="14" t="inlineStr">
         <is>
-          <t>$1089722.428254781</t>
+          <t>$1089722.4282547813</t>
         </is>
       </c>
       <c r="U249" s="14" t="inlineStr">
@@ -33782,7 +33784,7 @@
         <v>3.007068259192379</v>
       </c>
       <c r="L250" s="14" t="n">
-        <v>3.341626077728671</v>
+        <v>3.341626077728672</v>
       </c>
       <c r="M250" s="14" t="n">
         <v>3.713279211518171</v>
@@ -33797,7 +33799,7 @@
       </c>
       <c r="P250" s="14" t="inlineStr">
         <is>
-          <t>$43880.743021847906</t>
+          <t>$43880.7430218479</t>
         </is>
       </c>
       <c r="Q250" s="14" t="inlineStr">
@@ -33807,7 +33809,7 @@
       </c>
       <c r="R250" s="14" t="inlineStr">
         <is>
-          <t>$59741.529070245306</t>
+          <t>$59741.52907024529</t>
         </is>
       </c>
       <c r="S250" s="14" t="inlineStr">
@@ -33817,7 +33819,7 @@
       </c>
       <c r="T250" s="14" t="inlineStr">
         <is>
-          <t>$81328.44221550158</t>
+          <t>$81328.4422155016</t>
         </is>
       </c>
       <c r="U250" s="14" t="inlineStr">
@@ -33922,7 +33924,7 @@
         <v>2.653309604370921</v>
       </c>
       <c r="L251" s="14" t="n">
-        <v>2.82137802773314</v>
+        <v>2.821378027733141</v>
       </c>
       <c r="M251" s="14" t="n">
         <v>2.974852246107821</v>
@@ -33937,7 +33939,7 @@
       </c>
       <c r="P251" s="14" t="inlineStr">
         <is>
-          <t>$82508.4770952285</t>
+          <t>$82508.47709522849</t>
         </is>
       </c>
       <c r="Q251" s="14" t="inlineStr">
@@ -33947,7 +33949,7 @@
       </c>
       <c r="R251" s="14" t="inlineStr">
         <is>
-          <t>$101808.515063036</t>
+          <t>$101808.51506303597</t>
         </is>
       </c>
       <c r="S251" s="14" t="inlineStr">
@@ -33957,7 +33959,7 @@
       </c>
       <c r="T251" s="14" t="inlineStr">
         <is>
-          <t>$124742.66109684843</t>
+          <t>$124742.66109684846</t>
         </is>
       </c>
       <c r="U251" s="14" t="inlineStr">
@@ -34062,7 +34064,7 @@
         <v>7.959928813112762</v>
       </c>
       <c r="L252" s="14" t="n">
-        <v>8.46413408319942</v>
+        <v>8.464134083199422</v>
       </c>
       <c r="M252" s="14" t="n">
         <v>8.924556738323464</v>
@@ -34077,7 +34079,7 @@
       </c>
       <c r="P252" s="14" t="inlineStr">
         <is>
-          <t>$247525.43128568557</t>
+          <t>$247525.4312856855</t>
         </is>
       </c>
       <c r="Q252" s="14" t="inlineStr">
@@ -34087,7 +34089,7 @@
       </c>
       <c r="R252" s="14" t="inlineStr">
         <is>
-          <t>$305425.54518910794</t>
+          <t>$305425.5451891079</t>
         </is>
       </c>
       <c r="S252" s="14" t="inlineStr">
@@ -34097,7 +34099,7 @@
       </c>
       <c r="T252" s="14" t="inlineStr">
         <is>
-          <t>$374227.98329054523</t>
+          <t>$374227.98329054535</t>
         </is>
       </c>
       <c r="U252" s="14" t="inlineStr">
@@ -34202,7 +34204,7 @@
         <v>6.633274010927301</v>
       </c>
       <c r="L253" s="14" t="n">
-        <v>7.053445069332851</v>
+        <v>7.053445069332852</v>
       </c>
       <c r="M253" s="14" t="n">
         <v>7.437130615269553</v>
@@ -34217,7 +34219,7 @@
       </c>
       <c r="P253" s="14" t="inlineStr">
         <is>
-          <t>$206271.19273807132</t>
+          <t>$206271.19273807126</t>
         </is>
       </c>
       <c r="Q253" s="14" t="inlineStr">
@@ -34227,7 +34229,7 @@
       </c>
       <c r="R253" s="14" t="inlineStr">
         <is>
-          <t>$254521.28765758994</t>
+          <t>$254521.2876575899</t>
         </is>
       </c>
       <c r="S253" s="14" t="inlineStr">
@@ -34237,7 +34239,7 @@
       </c>
       <c r="T253" s="14" t="inlineStr">
         <is>
-          <t>$311856.6527421211</t>
+          <t>$311856.65274212114</t>
         </is>
       </c>
       <c r="U253" s="14" t="inlineStr">
@@ -34342,7 +34344,7 @@
         <v>5.306619208741842</v>
       </c>
       <c r="L254" s="14" t="n">
-        <v>5.64275605546628</v>
+        <v>5.642756055466282</v>
       </c>
       <c r="M254" s="14" t="n">
         <v>5.949704492215642</v>
@@ -34357,7 +34359,7 @@
       </c>
       <c r="P254" s="14" t="inlineStr">
         <is>
-          <t>$125408.7955259046</t>
+          <t>$125408.79552590457</t>
         </is>
       </c>
       <c r="Q254" s="14" t="inlineStr">
@@ -34367,7 +34369,7 @@
       </c>
       <c r="R254" s="14" t="inlineStr">
         <is>
-          <t>$146977.02933654722</t>
+          <t>$146977.0293365472</t>
         </is>
       </c>
       <c r="S254" s="14" t="inlineStr">
@@ -34377,7 +34379,7 @@
       </c>
       <c r="T254" s="14" t="inlineStr">
         <is>
-          <t>$169639.7394972217</t>
+          <t>$169639.73949722172</t>
         </is>
       </c>
       <c r="U254" s="14" t="inlineStr">
@@ -35602,7 +35604,7 @@
         <v>24.56547622762779</v>
       </c>
       <c r="L263" s="14" t="n">
-        <v>23.3028877478721</v>
+        <v>23.30288774787211</v>
       </c>
       <c r="M263" s="14" t="n">
         <v>21.96143493925455</v>
@@ -35617,7 +35619,7 @@
       </c>
       <c r="P263" s="14" t="inlineStr">
         <is>
-          <t>$433357.8751240706</t>
+          <t>$433357.8751240705</t>
         </is>
       </c>
       <c r="Q263" s="14" t="inlineStr">
@@ -35627,7 +35629,7 @@
       </c>
       <c r="R263" s="14" t="inlineStr">
         <is>
-          <t>$419587.6583590626</t>
+          <t>$419587.65835906257</t>
         </is>
       </c>
       <c r="S263" s="14" t="inlineStr">
@@ -35637,7 +35639,7 @@
       </c>
       <c r="T263" s="14" t="inlineStr">
         <is>
-          <t>$401230.1047473288</t>
+          <t>$401230.10474732885</t>
         </is>
       </c>
       <c r="U263" s="14" t="inlineStr">
@@ -35757,7 +35759,7 @@
       </c>
       <c r="P264" s="14" t="inlineStr">
         <is>
-          <t>$164860.4404927546</t>
+          <t>$164860.44049275457</t>
         </is>
       </c>
       <c r="Q264" s="14" t="inlineStr">
@@ -35767,7 +35769,7 @@
       </c>
       <c r="R264" s="14" t="inlineStr">
         <is>
-          <t>$180138.65683249777</t>
+          <t>$180138.65683249774</t>
         </is>
       </c>
       <c r="S264" s="14" t="inlineStr">
@@ -35777,7 +35779,7 @@
       </c>
       <c r="T264" s="14" t="inlineStr">
         <is>
-          <t>$194963.8367724127</t>
+          <t>$194963.83677241276</t>
         </is>
       </c>
       <c r="U264" s="14" t="inlineStr">
@@ -35882,7 +35884,7 @@
         <v>3.494941240127077</v>
       </c>
       <c r="L265" s="14" t="n">
-        <v>3.591795251106374</v>
+        <v>3.591795251106375</v>
       </c>
       <c r="M265" s="14" t="n">
         <v>3.66733174555146</v>
@@ -35897,7 +35899,7 @@
       </c>
       <c r="P265" s="14" t="inlineStr">
         <is>
-          <t>$60226.891369715675</t>
+          <t>$60226.89136971566</t>
         </is>
       </c>
       <c r="Q265" s="14" t="inlineStr">
@@ -35907,7 +35909,7 @@
       </c>
       <c r="R265" s="14" t="inlineStr">
         <is>
-          <t>$70403.17605792789</t>
+          <t>$70403.17605792788</t>
         </is>
       </c>
       <c r="S265" s="14" t="inlineStr">
@@ -35917,7 +35919,7 @@
       </c>
       <c r="T265" s="14" t="inlineStr">
         <is>
-          <t>$81151.06850801772</t>
+          <t>$81151.06850801775</t>
         </is>
       </c>
       <c r="U265" s="14" t="inlineStr">
@@ -36022,7 +36024,7 @@
         <v>3.979964406556381</v>
       </c>
       <c r="L266" s="14" t="n">
-        <v>4.23206704159971</v>
+        <v>4.232067041599711</v>
       </c>
       <c r="M266" s="14" t="n">
         <v>4.462278369161732</v>
@@ -36037,7 +36039,7 @@
       </c>
       <c r="P266" s="14" t="inlineStr">
         <is>
-          <t>$42002.82982312639</t>
+          <t>$42002.829823126376</t>
         </is>
       </c>
       <c r="Q266" s="14" t="inlineStr">
@@ -36047,7 +36049,7 @@
       </c>
       <c r="R266" s="14" t="inlineStr">
         <is>
-          <t>$49444.55940583243</t>
+          <t>$49444.55940583241</t>
         </is>
       </c>
       <c r="S266" s="14" t="inlineStr">
@@ -36057,7 +36059,7 @@
       </c>
       <c r="T266" s="14" t="inlineStr">
         <is>
-          <t>$57548.74101330103</t>
+          <t>$57548.74101330104</t>
         </is>
       </c>
       <c r="U266" s="14" t="inlineStr">
@@ -36162,7 +36164,7 @@
         <v>7.959928813112762</v>
       </c>
       <c r="L267" s="14" t="n">
-        <v>8.46413408319942</v>
+        <v>8.464134083199422</v>
       </c>
       <c r="M267" s="14" t="n">
         <v>8.924556738323464</v>
@@ -36177,7 +36179,7 @@
       </c>
       <c r="P267" s="14" t="inlineStr">
         <is>
-          <t>$144634.74043318746</t>
+          <t>$144634.74043318743</t>
         </is>
       </c>
       <c r="Q267" s="14" t="inlineStr">
@@ -36187,7 +36189,7 @@
       </c>
       <c r="R267" s="14" t="inlineStr">
         <is>
-          <t>$176785.3602892166</t>
+          <t>$176785.36028921657</t>
         </is>
       </c>
       <c r="S267" s="14" t="inlineStr">
@@ -36197,7 +36199,7 @@
       </c>
       <c r="T267" s="14" t="inlineStr">
         <is>
-          <t>$212745.6896159817</t>
+          <t>$212745.68961598174</t>
         </is>
       </c>
       <c r="U267" s="14" t="inlineStr">
@@ -36302,7 +36304,7 @@
         <v>7.959928813112762</v>
       </c>
       <c r="L268" s="14" t="n">
-        <v>8.46413408319942</v>
+        <v>8.464134083199422</v>
       </c>
       <c r="M268" s="14" t="n">
         <v>8.924556738323464</v>
@@ -36317,7 +36319,7 @@
       </c>
       <c r="P268" s="14" t="inlineStr">
         <is>
-          <t>$86780.80420304304</t>
+          <t>$86780.80420304301</t>
         </is>
       </c>
       <c r="Q268" s="14" t="inlineStr">
@@ -36327,7 +36329,7 @@
       </c>
       <c r="R268" s="14" t="inlineStr">
         <is>
-          <t>$106071.26901848921</t>
+          <t>$106071.26901848918</t>
         </is>
       </c>
       <c r="S268" s="14" t="inlineStr">
@@ -36337,7 +36339,7 @@
       </c>
       <c r="T268" s="14" t="inlineStr">
         <is>
-          <t>$127647.72274057232</t>
+          <t>$127647.72274057235</t>
         </is>
       </c>
       <c r="U268" s="14" t="inlineStr">
@@ -36737,7 +36739,7 @@
       </c>
       <c r="P271" s="14" t="inlineStr">
         <is>
-          <t>$5250.5777974836265</t>
+          <t>$5250.577797483626</t>
         </is>
       </c>
       <c r="Q271" s="14" t="inlineStr">
@@ -36747,7 +36749,7 @@
       </c>
       <c r="R271" s="14" t="inlineStr">
         <is>
-          <t>$4603.590527944106</t>
+          <t>$4603.590527944105</t>
         </is>
       </c>
       <c r="S271" s="14" t="inlineStr">
@@ -36757,7 +36759,7 @@
       </c>
       <c r="T271" s="14" t="inlineStr">
         <is>
-          <t>$5760.541599512686</t>
+          <t>$5760.541599512687</t>
         </is>
       </c>
       <c r="U271" s="14" t="inlineStr">
@@ -37157,7 +37159,7 @@
       </c>
       <c r="P274" s="14" t="inlineStr">
         <is>
-          <t>$220460.59286334846</t>
+          <t>$220460.5928633484</t>
         </is>
       </c>
       <c r="Q274" s="14" t="inlineStr">
@@ -37167,7 +37169,7 @@
       </c>
       <c r="R274" s="14" t="inlineStr">
         <is>
-          <t>$221620.5130196295</t>
+          <t>$221620.51301962943</t>
         </is>
       </c>
       <c r="S274" s="14" t="inlineStr">
@@ -37177,7 +37179,7 @@
       </c>
       <c r="T274" s="14" t="inlineStr">
         <is>
-          <t>$235312.0702499227</t>
+          <t>$235312.07024992275</t>
         </is>
       </c>
       <c r="U274" s="14" t="inlineStr">
@@ -37857,7 +37859,7 @@
       </c>
       <c r="P279" s="14" t="inlineStr">
         <is>
-          <t>$65289.84036764376</t>
+          <t>$65289.840367643745</t>
         </is>
       </c>
       <c r="Q279" s="14" t="inlineStr">
@@ -37867,7 +37869,7 @@
       </c>
       <c r="R279" s="14" t="inlineStr">
         <is>
-          <t>$68293.13882579724</t>
+          <t>$68293.13882579723</t>
         </is>
       </c>
       <c r="S279" s="14" t="inlineStr">
@@ -37877,7 +37879,7 @@
       </c>
       <c r="T279" s="14" t="inlineStr">
         <is>
-          <t>$72513.89988893432</t>
+          <t>$72513.89988893433</t>
         </is>
       </c>
       <c r="U279" s="14" t="inlineStr">
@@ -37982,7 +37984,7 @@
         <v>3.859815347104714</v>
       </c>
       <c r="L280" s="14" t="n">
-        <v>3.78682579879187</v>
+        <v>3.786825798791871</v>
       </c>
       <c r="M280" s="14" t="n">
         <v>3.72126910422067</v>
@@ -37997,7 +37999,7 @@
       </c>
       <c r="P280" s="14" t="inlineStr">
         <is>
-          <t>$130579.68675377507</t>
+          <t>$130579.68675377504</t>
         </is>
       </c>
       <c r="Q280" s="14" t="inlineStr">
@@ -38007,7 +38009,7 @@
       </c>
       <c r="R280" s="14" t="inlineStr">
         <is>
-          <t>$136586.28394692927</t>
+          <t>$136586.28394692924</t>
         </is>
       </c>
       <c r="S280" s="14" t="inlineStr">
@@ -38017,7 +38019,7 @@
       </c>
       <c r="T280" s="14" t="inlineStr">
         <is>
-          <t>$145027.80646227777</t>
+          <t>$145027.8064622778</t>
         </is>
       </c>
       <c r="U280" s="14" t="inlineStr">
@@ -38122,7 +38124,7 @@
         <v>23.15889208262828</v>
       </c>
       <c r="L281" s="14" t="n">
-        <v>22.72095479275121</v>
+        <v>22.72095479275122</v>
       </c>
       <c r="M281" s="14" t="n">
         <v>22.32761462532402</v>
@@ -38137,7 +38139,7 @@
       </c>
       <c r="P281" s="14" t="inlineStr">
         <is>
-          <t>$783478.1205226504</t>
+          <t>$783478.1205226503</t>
         </is>
       </c>
       <c r="Q281" s="14" t="inlineStr">
@@ -38147,7 +38149,7 @@
       </c>
       <c r="R281" s="14" t="inlineStr">
         <is>
-          <t>$819517.7036815758</t>
+          <t>$819517.7036815756</t>
         </is>
       </c>
       <c r="S281" s="14" t="inlineStr">
@@ -38157,7 +38159,7 @@
       </c>
       <c r="T281" s="14" t="inlineStr">
         <is>
-          <t>$870166.8387736669</t>
+          <t>$870166.8387736671</t>
         </is>
       </c>
       <c r="U281" s="14" t="inlineStr">
@@ -38402,7 +38404,7 @@
         <v>1.393294497630826</v>
       </c>
       <c r="L283" s="14" t="n">
-        <v>1.512446288935718</v>
+        <v>1.512446288935719</v>
       </c>
       <c r="M283" s="14" t="n">
         <v>1.631117824908513</v>
@@ -38417,7 +38419,7 @@
       </c>
       <c r="P283" s="14" t="inlineStr">
         <is>
-          <t>$24629.94201546576</t>
+          <t>$24629.942015465756</t>
         </is>
       </c>
       <c r="Q283" s="14" t="inlineStr">
@@ -38427,7 +38429,7 @@
       </c>
       <c r="R283" s="14" t="inlineStr">
         <is>
-          <t>$32061.58574819098</t>
+          <t>$32061.585748190973</t>
         </is>
       </c>
       <c r="S283" s="14" t="inlineStr">
@@ -38437,7 +38439,7 @@
       </c>
       <c r="T283" s="14" t="inlineStr">
         <is>
-          <t>$41736.70383829421</t>
+          <t>$41736.70383829422</t>
         </is>
       </c>
       <c r="U283" s="14" t="inlineStr">
@@ -38822,7 +38824,7 @@
         <v>2.786588995261652</v>
       </c>
       <c r="L286" s="14" t="n">
-        <v>3.024892577871437</v>
+        <v>3.024892577871438</v>
       </c>
       <c r="M286" s="14" t="n">
         <v>3.262235649817025</v>
@@ -38837,7 +38839,7 @@
       </c>
       <c r="P286" s="14" t="inlineStr">
         <is>
-          <t>$25151.728795639578</t>
+          <t>$25151.72879563957</t>
         </is>
       </c>
       <c r="Q286" s="14" t="inlineStr">
@@ -38847,7 +38849,7 @@
       </c>
       <c r="R286" s="14" t="inlineStr">
         <is>
-          <t>$31975.822077580066</t>
+          <t>$31975.82207758006</t>
         </is>
       </c>
       <c r="S286" s="14" t="inlineStr">
@@ -38857,7 +38859,7 @@
       </c>
       <c r="T286" s="14" t="inlineStr">
         <is>
-          <t>$40069.153095180955</t>
+          <t>$40069.15309518096</t>
         </is>
       </c>
       <c r="U286" s="14" t="inlineStr">
@@ -41077,7 +41079,7 @@
       </c>
       <c r="P302" s="14" t="inlineStr">
         <is>
-          <t>$93236.51865866153</t>
+          <t>$93236.51865866152</t>
         </is>
       </c>
       <c r="Q302" s="14" t="inlineStr">
@@ -41087,7 +41089,7 @@
       </c>
       <c r="R302" s="14" t="inlineStr">
         <is>
-          <t>$83259.25053771437</t>
+          <t>$83259.25053771434</t>
         </is>
       </c>
       <c r="S302" s="14" t="inlineStr">
@@ -41097,7 +41099,7 @@
       </c>
       <c r="T302" s="14" t="inlineStr">
         <is>
-          <t>$73947.32175161384</t>
+          <t>$73947.32175161385</t>
         </is>
       </c>
       <c r="U302" s="14" t="inlineStr">
@@ -41217,7 +41219,7 @@
       </c>
       <c r="P303" s="14" t="inlineStr">
         <is>
-          <t>$8217.5509912962</t>
+          <t>$8217.550991296199</t>
         </is>
       </c>
       <c r="Q303" s="14" t="inlineStr">
@@ -41227,7 +41229,7 @@
       </c>
       <c r="R303" s="14" t="inlineStr">
         <is>
-          <t>$10836.458806868748</t>
+          <t>$10836.458806868744</t>
         </is>
       </c>
       <c r="S303" s="14" t="inlineStr">
@@ -41237,7 +41239,7 @@
       </c>
       <c r="T303" s="14" t="inlineStr">
         <is>
-          <t>$14212.767722048045</t>
+          <t>$14212.76772204805</t>
         </is>
       </c>
       <c r="U303" s="14" t="inlineStr">
@@ -41342,7 +41344,7 @@
         <v>7.766527224633224</v>
       </c>
       <c r="L304" s="14" t="n">
-        <v>8.734564914584675</v>
+        <v>8.734564914584677</v>
       </c>
       <c r="M304" s="14" t="n">
         <v>9.759356011895081</v>
@@ -41357,7 +41359,7 @@
       </c>
       <c r="P304" s="14" t="inlineStr">
         <is>
-          <t>$118120.48099403502</t>
+          <t>$118120.480994035</t>
         </is>
       </c>
       <c r="Q304" s="14" t="inlineStr">
@@ -41367,7 +41369,7 @@
       </c>
       <c r="R304" s="14" t="inlineStr">
         <is>
-          <t>$163457.6639609435</t>
+          <t>$163457.66396094346</t>
         </is>
       </c>
       <c r="S304" s="14" t="inlineStr">
@@ -41377,7 +41379,7 @@
       </c>
       <c r="T304" s="14" t="inlineStr">
         <is>
-          <t>$224973.65618866324</t>
+          <t>$224973.6561886633</t>
         </is>
       </c>
       <c r="U304" s="14" t="inlineStr">
@@ -41497,7 +41499,7 @@
       </c>
       <c r="P305" s="14" t="inlineStr">
         <is>
-          <t>$272147.9012925062</t>
+          <t>$272147.90129250614</t>
         </is>
       </c>
       <c r="Q305" s="14" t="inlineStr">
@@ -41507,7 +41509,7 @@
       </c>
       <c r="R305" s="14" t="inlineStr">
         <is>
-          <t>$376604.1233729224</t>
+          <t>$376604.1233729223</t>
         </is>
       </c>
       <c r="S305" s="14" t="inlineStr">
@@ -41517,7 +41519,7 @@
       </c>
       <c r="T305" s="14" t="inlineStr">
         <is>
-          <t>$518336.09093530866</t>
+          <t>$518336.0909353088</t>
         </is>
       </c>
       <c r="U305" s="14" t="inlineStr">
@@ -41622,7 +41624,7 @@
         <v>3.10661088985329</v>
       </c>
       <c r="L306" s="14" t="n">
-        <v>3.49382596583387</v>
+        <v>3.493825965833871</v>
       </c>
       <c r="M306" s="14" t="n">
         <v>3.903742404758032</v>
@@ -41637,7 +41639,7 @@
       </c>
       <c r="P306" s="14" t="inlineStr">
         <is>
-          <t>$26459.00461948008</t>
+          <t>$26459.004619480078</t>
         </is>
       </c>
       <c r="Q306" s="14" t="inlineStr">
@@ -41647,7 +41649,7 @@
       </c>
       <c r="R306" s="14" t="inlineStr">
         <is>
-          <t>$36614.5400817529</t>
+          <t>$36614.54008175289</t>
         </is>
       </c>
       <c r="S306" s="14" t="inlineStr">
@@ -41657,7 +41659,7 @@
       </c>
       <c r="T306" s="14" t="inlineStr">
         <is>
-          <t>$50394.13113004308</t>
+          <t>$50394.1311300431</t>
         </is>
       </c>
       <c r="U306" s="14" t="inlineStr">
@@ -42602,7 +42604,7 @@
         <v>5.573177990523304</v>
       </c>
       <c r="L313" s="14" t="n">
-        <v>6.049785155742874</v>
+        <v>6.049785155742875</v>
       </c>
       <c r="M313" s="14" t="n">
         <v>6.52447129963405</v>
@@ -42617,7 +42619,7 @@
       </c>
       <c r="P313" s="14" t="inlineStr">
         <is>
-          <t>$68399.53755765002</t>
+          <t>$68399.53755765001</t>
         </is>
       </c>
       <c r="Q313" s="14" t="inlineStr">
@@ -42627,7 +42629,7 @@
       </c>
       <c r="R313" s="14" t="inlineStr">
         <is>
-          <t>$89688.25120797331</t>
+          <t>$89688.2512079733</t>
         </is>
       </c>
       <c r="S313" s="14" t="inlineStr">
@@ -42637,7 +42639,7 @@
       </c>
       <c r="T313" s="14" t="inlineStr">
         <is>
-          <t>$104053.00186176146</t>
+          <t>$104053.00186176148</t>
         </is>
       </c>
       <c r="U313" s="14" t="inlineStr">
@@ -42742,7 +42744,7 @@
         <v>2.145399433363619</v>
       </c>
       <c r="L314" s="14" t="n">
-        <v>2.133954249770983</v>
+        <v>2.133954249770984</v>
       </c>
       <c r="M314" s="14" t="n">
         <v>2.107500927881548</v>
@@ -42757,7 +42759,7 @@
       </c>
       <c r="P314" s="14" t="inlineStr">
         <is>
-          <t>$21765.154710459963</t>
+          <t>$21765.15471045996</t>
         </is>
       </c>
       <c r="Q314" s="14" t="inlineStr">
@@ -42767,7 +42769,7 @@
       </c>
       <c r="R314" s="14" t="inlineStr">
         <is>
-          <t>$21382.221582629132</t>
+          <t>$21382.22158262913</t>
         </is>
       </c>
       <c r="S314" s="14" t="inlineStr">
@@ -42777,7 +42779,7 @@
       </c>
       <c r="T314" s="14" t="inlineStr">
         <is>
-          <t>$20854.80715742594</t>
+          <t>$20854.80715742595</t>
         </is>
       </c>
       <c r="U314" s="14" t="inlineStr">
@@ -42882,7 +42884,7 @@
         <v>18.63966533911974</v>
       </c>
       <c r="L315" s="14" t="n">
-        <v>20.96295579500322</v>
+        <v>20.96295579500323</v>
       </c>
       <c r="M315" s="14" t="n">
         <v>23.42245442854819</v>
@@ -42897,7 +42899,7 @@
       </c>
       <c r="P315" s="14" t="inlineStr">
         <is>
-          <t>$202091.38456855842</t>
+          <t>$202091.38456855837</t>
         </is>
       </c>
       <c r="Q315" s="14" t="inlineStr">
@@ -42907,7 +42909,7 @@
       </c>
       <c r="R315" s="14" t="inlineStr">
         <is>
-          <t>$275710.0635398961</t>
+          <t>$275710.063539896</t>
         </is>
       </c>
       <c r="S315" s="14" t="inlineStr">
@@ -42917,7 +42919,7 @@
       </c>
       <c r="T315" s="14" t="inlineStr">
         <is>
-          <t>$375999.75875263335</t>
+          <t>$375999.75875263347</t>
         </is>
       </c>
       <c r="U315" s="14" t="inlineStr">
@@ -43037,7 +43039,7 @@
       </c>
       <c r="P316" s="14" t="inlineStr">
         <is>
-          <t>$449725.7128629392</t>
+          <t>$449725.7128629391</t>
         </is>
       </c>
       <c r="Q316" s="14" t="inlineStr">
@@ -43047,7 +43049,7 @@
       </c>
       <c r="R316" s="14" t="inlineStr">
         <is>
-          <t>$610477.8894154591</t>
+          <t>$610477.889415459</t>
         </is>
       </c>
       <c r="S316" s="14" t="inlineStr">
@@ -43057,7 +43059,7 @@
       </c>
       <c r="T316" s="14" t="inlineStr">
         <is>
-          <t>$827076.2907950975</t>
+          <t>$827076.2907950976</t>
         </is>
       </c>
       <c r="U316" s="14" t="inlineStr">
@@ -43177,7 +43179,7 @@
       </c>
       <c r="P317" s="14" t="inlineStr">
         <is>
-          <t>$439022.5622556093</t>
+          <t>$439022.5622556092</t>
         </is>
       </c>
       <c r="Q317" s="14" t="inlineStr">
@@ -43187,7 +43189,7 @@
       </c>
       <c r="R317" s="14" t="inlineStr">
         <is>
-          <t>$594982.5998474619</t>
+          <t>$594982.5998474618</t>
         </is>
       </c>
       <c r="S317" s="14" t="inlineStr">
@@ -43197,7 +43199,7 @@
       </c>
       <c r="T317" s="14" t="inlineStr">
         <is>
-          <t>$804377.2019946437</t>
+          <t>$804377.2019946438</t>
         </is>
       </c>
       <c r="U317" s="14" t="inlineStr">
@@ -43862,7 +43864,7 @@
         <v>9.286583615298223</v>
       </c>
       <c r="L322" s="14" t="n">
-        <v>9.87482309706599</v>
+        <v>9.874823097065992</v>
       </c>
       <c r="M322" s="14" t="n">
         <v>10.32755903367637</v>
@@ -43877,7 +43879,7 @@
       </c>
       <c r="P322" s="14" t="inlineStr">
         <is>
-          <t>$275290.306656644</t>
+          <t>$275290.3066566439</t>
         </is>
       </c>
       <c r="Q322" s="14" t="inlineStr">
@@ -43887,7 +43889,7 @@
       </c>
       <c r="R322" s="14" t="inlineStr">
         <is>
-          <t>$351759.8399081907</t>
+          <t>$351759.8399081906</t>
         </is>
       </c>
       <c r="S322" s="14" t="inlineStr">
@@ -43897,7 +43899,7 @@
       </c>
       <c r="T322" s="14" t="inlineStr">
         <is>
-          <t>$226573.08706657938</t>
+          <t>$226573.08706657944</t>
         </is>
       </c>
       <c r="U322" s="14" t="inlineStr">
@@ -44002,7 +44004,7 @@
         <v>23.33138743564198</v>
       </c>
       <c r="L323" s="14" t="n">
-        <v>22.81684471046021</v>
+        <v>22.81684471046022</v>
       </c>
       <c r="M323" s="14" t="n">
         <v>22.16852776713784</v>
@@ -44017,7 +44019,7 @@
       </c>
       <c r="P323" s="14" t="inlineStr">
         <is>
-          <t>$438838.2396703448</t>
+          <t>$438838.2396703447</t>
         </is>
       </c>
       <c r="Q323" s="14" t="inlineStr">
@@ -44027,7 +44029,7 @@
       </c>
       <c r="R323" s="14" t="inlineStr">
         <is>
-          <t>$441086.59064924537</t>
+          <t>$441086.5906492453</t>
         </is>
       </c>
       <c r="S323" s="14" t="inlineStr">
@@ -44037,7 +44039,7 @@
       </c>
       <c r="T323" s="14" t="inlineStr">
         <is>
-          <t>$440866.2325022876</t>
+          <t>$440866.2325022877</t>
         </is>
       </c>
       <c r="U323" s="14" t="inlineStr">
@@ -44142,7 +44144,7 @@
         <v>83.11434918304937</v>
       </c>
       <c r="L324" s="14" t="n">
-        <v>85.73718689830925</v>
+        <v>85.73718689830926</v>
       </c>
       <c r="M324" s="14" t="n">
         <v>87.57202237545141</v>
@@ -44157,7 +44159,7 @@
       </c>
       <c r="P324" s="14" t="inlineStr">
         <is>
-          <t>$366018.3569654512</t>
+          <t>$366018.35696545115</t>
         </is>
       </c>
       <c r="Q324" s="14" t="inlineStr">
@@ -44167,7 +44169,7 @@
       </c>
       <c r="R324" s="14" t="inlineStr">
         <is>
-          <t>$440790.61141665216</t>
+          <t>$440790.61141665204</t>
         </is>
       </c>
       <c r="S324" s="14" t="inlineStr">
@@ -44177,7 +44179,7 @@
       </c>
       <c r="T324" s="14" t="inlineStr">
         <is>
-          <t>$521287.0599827278</t>
+          <t>$521287.0599827279</t>
         </is>
       </c>
       <c r="U324" s="14" t="inlineStr">
@@ -44577,7 +44579,7 @@
       </c>
       <c r="P327" s="14" t="inlineStr">
         <is>
-          <t>$278919.4875690847</t>
+          <t>$278919.4875690846</t>
         </is>
       </c>
       <c r="Q327" s="14" t="inlineStr">
@@ -44587,7 +44589,7 @@
       </c>
       <c r="R327" s="14" t="inlineStr">
         <is>
-          <t>$326889.015519714</t>
+          <t>$326889.0155197139</t>
         </is>
       </c>
       <c r="S327" s="14" t="inlineStr">
@@ -44597,7 +44599,7 @@
       </c>
       <c r="T327" s="14" t="inlineStr">
         <is>
-          <t>$377292.7489933868</t>
+          <t>$377292.74899338686</t>
         </is>
       </c>
       <c r="U327" s="14" t="inlineStr">
@@ -44717,7 +44719,7 @@
       </c>
       <c r="P328" s="14" t="inlineStr">
         <is>
-          <t>$1680579.9672809432</t>
+          <t>$1680579.967280943</t>
         </is>
       </c>
       <c r="Q328" s="14" t="inlineStr">
@@ -44727,7 +44729,7 @@
       </c>
       <c r="R328" s="14" t="inlineStr">
         <is>
-          <t>$1998104.847547187</t>
+          <t>$1998104.8475471865</t>
         </is>
       </c>
       <c r="S328" s="14" t="inlineStr">
@@ -44737,7 +44739,7 @@
       </c>
       <c r="T328" s="14" t="inlineStr">
         <is>
-          <t>$2375018.1553625027</t>
+          <t>$2375018.155362503</t>
         </is>
       </c>
       <c r="U328" s="14" t="inlineStr">
@@ -44842,7 +44844,7 @@
         <v>4.510602388788568</v>
       </c>
       <c r="L329" s="14" t="n">
-        <v>5.012439116593007</v>
+        <v>5.012439116593008</v>
       </c>
       <c r="M329" s="14" t="n">
         <v>5.569918817277257</v>
@@ -44857,7 +44859,7 @@
       </c>
       <c r="P329" s="14" t="inlineStr">
         <is>
-          <t>$38290.351241887525</t>
+          <t>$38290.35124188751</t>
         </is>
       </c>
       <c r="Q329" s="14" t="inlineStr">
@@ -44867,7 +44869,7 @@
       </c>
       <c r="R329" s="14" t="inlineStr">
         <is>
-          <t>$52130.47852649589</t>
+          <t>$52130.47852649588</t>
         </is>
       </c>
       <c r="S329" s="14" t="inlineStr">
@@ -44877,7 +44879,7 @@
       </c>
       <c r="T329" s="14" t="inlineStr">
         <is>
-          <t>$70967.22625769174</t>
+          <t>$70967.22625769176</t>
         </is>
       </c>
       <c r="U329" s="14" t="inlineStr">
@@ -44982,7 +44984,7 @@
         <v>2.786588995261652</v>
       </c>
       <c r="L330" s="14" t="n">
-        <v>3.024892577871437</v>
+        <v>3.024892577871438</v>
       </c>
       <c r="M330" s="14" t="n">
         <v>3.262235649817025</v>
@@ -44997,7 +44999,7 @@
       </c>
       <c r="P330" s="14" t="inlineStr">
         <is>
-          <t>$63092.13522944098</t>
+          <t>$63092.135229440966</t>
         </is>
       </c>
       <c r="Q330" s="14" t="inlineStr">
@@ -45007,7 +45009,7 @@
       </c>
       <c r="R330" s="14" t="inlineStr">
         <is>
-          <t>$76912.35192989573</t>
+          <t>$76912.35192989571</t>
         </is>
       </c>
       <c r="S330" s="14" t="inlineStr">
@@ -45017,7 +45019,7 @@
       </c>
       <c r="T330" s="14" t="inlineStr">
         <is>
-          <t>$92870.27446310713</t>
+          <t>$92870.27446310714</t>
         </is>
       </c>
       <c r="U330" s="14" t="inlineStr">
@@ -45137,7 +45139,7 @@
       </c>
       <c r="P331" s="14" t="inlineStr">
         <is>
-          <t>$448073.98744502844</t>
+          <t>$448073.9874450284</t>
         </is>
       </c>
       <c r="Q331" s="14" t="inlineStr">
@@ -45147,7 +45149,7 @@
       </c>
       <c r="R331" s="14" t="inlineStr">
         <is>
-          <t>$589375.6671906479</t>
+          <t>$589375.6671906478</t>
         </is>
       </c>
       <c r="S331" s="14" t="inlineStr">
@@ -45157,7 +45159,7 @@
       </c>
       <c r="T331" s="14" t="inlineStr">
         <is>
-          <t>$761187.0405520856</t>
+          <t>$761187.0405520857</t>
         </is>
       </c>
       <c r="U331" s="14" t="inlineStr">
@@ -45402,7 +45404,7 @@
         <v>5.573177990523304</v>
       </c>
       <c r="L333" s="14" t="n">
-        <v>6.049785155742874</v>
+        <v>6.049785155742875</v>
       </c>
       <c r="M333" s="14" t="n">
         <v>6.52447129963405</v>
@@ -45417,7 +45419,7 @@
       </c>
       <c r="P333" s="14" t="inlineStr">
         <is>
-          <t>$391588.3012205485</t>
+          <t>$391588.30122054846</t>
         </is>
       </c>
       <c r="Q333" s="14" t="inlineStr">
@@ -45427,7 +45429,7 @@
       </c>
       <c r="R333" s="14" t="inlineStr">
         <is>
-          <t>$489217.52183216927</t>
+          <t>$489217.52183216915</t>
         </is>
       </c>
       <c r="S333" s="14" t="inlineStr">
@@ -45437,7 +45439,7 @@
       </c>
       <c r="T333" s="14" t="inlineStr">
         <is>
-          <t>$604244.5868222101</t>
+          <t>$604244.5868222102</t>
         </is>
       </c>
       <c r="U333" s="14" t="inlineStr">
@@ -46117,7 +46119,7 @@
       </c>
       <c r="P338" s="14" t="inlineStr">
         <is>
-          <t>$59714.2240393697</t>
+          <t>$59714.224039369685</t>
         </is>
       </c>
       <c r="Q338" s="14" t="inlineStr">
@@ -46127,7 +46129,7 @@
       </c>
       <c r="R338" s="14" t="inlineStr">
         <is>
-          <t>$79839.07217834164</t>
+          <t>$79839.07217834162</t>
         </is>
       </c>
       <c r="S338" s="14" t="inlineStr">
@@ -46137,7 +46139,7 @@
       </c>
       <c r="T338" s="14" t="inlineStr">
         <is>
-          <t>$103995.31680732832</t>
+          <t>$103995.31680732833</t>
         </is>
       </c>
       <c r="U338" s="14" t="inlineStr">
@@ -46257,7 +46259,7 @@
       </c>
       <c r="P339" s="14" t="inlineStr">
         <is>
-          <t>$56386.448464340014</t>
+          <t>$56386.44846434</t>
         </is>
       </c>
       <c r="Q339" s="14" t="inlineStr">
@@ -46267,7 +46269,7 @@
       </c>
       <c r="R339" s="14" t="inlineStr">
         <is>
-          <t>$75389.77188846517</t>
+          <t>$75389.77188846515</t>
         </is>
       </c>
       <c r="S339" s="14" t="inlineStr">
@@ -46277,7 +46279,7 @@
       </c>
       <c r="T339" s="14" t="inlineStr">
         <is>
-          <t>$98199.82870116564</t>
+          <t>$98199.82870116566</t>
         </is>
       </c>
       <c r="U339" s="14" t="inlineStr">
@@ -46397,7 +46399,7 @@
       </c>
       <c r="P340" s="14" t="inlineStr">
         <is>
-          <t>$1505966.13254649</t>
+          <t>$1505966.1325464896</t>
         </is>
       </c>
       <c r="Q340" s="14" t="inlineStr">
@@ -46407,7 +46409,7 @@
       </c>
       <c r="R340" s="14" t="inlineStr">
         <is>
-          <t>$2317051.1627178127</t>
+          <t>$2317051.162717812</t>
         </is>
       </c>
       <c r="S340" s="14" t="inlineStr">
@@ -46417,7 +46419,7 @@
       </c>
       <c r="T340" s="14" t="inlineStr">
         <is>
-          <t>$3564673.8507179935</t>
+          <t>$3564673.8507179944</t>
         </is>
       </c>
       <c r="U340" s="14" t="inlineStr">
@@ -46537,7 +46539,7 @@
       </c>
       <c r="P341" s="14" t="inlineStr">
         <is>
-          <t>$134288.2183389871</t>
+          <t>$134288.21833898706</t>
         </is>
       </c>
       <c r="Q341" s="14" t="inlineStr">
@@ -46547,7 +46549,7 @@
       </c>
       <c r="R341" s="14" t="inlineStr">
         <is>
-          <t>$206613.32663272767</t>
+          <t>$206613.32663272764</t>
         </is>
       </c>
       <c r="S341" s="14" t="inlineStr">
@@ -46557,7 +46559,7 @@
       </c>
       <c r="T341" s="14" t="inlineStr">
         <is>
-          <t>$317864.8510262685</t>
+          <t>$317864.85102626856</t>
         </is>
       </c>
       <c r="U341" s="14" t="inlineStr">
@@ -46662,7 +46664,7 @@
         <v>16.3088511553292</v>
       </c>
       <c r="L342" s="14" t="n">
-        <v>19.26623984786672</v>
+        <v>19.26623984786673</v>
       </c>
       <c r="M342" s="14" t="n">
         <v>22.75913468192541</v>
@@ -46677,7 +46679,7 @@
       </c>
       <c r="P342" s="14" t="inlineStr">
         <is>
-          <t>$12510.89044551465</t>
+          <t>$12510.890445514646</t>
         </is>
       </c>
       <c r="Q342" s="14" t="inlineStr">
@@ -46687,7 +46689,7 @@
       </c>
       <c r="R342" s="14" t="inlineStr">
         <is>
-          <t>$19086.83108410862</t>
+          <t>$19086.831084108617</t>
         </is>
       </c>
       <c r="S342" s="14" t="inlineStr">
@@ -46697,7 +46699,7 @@
       </c>
       <c r="T342" s="14" t="inlineStr">
         <is>
-          <t>$29452.90753356876</t>
+          <t>$29452.907533568767</t>
         </is>
       </c>
       <c r="U342" s="14" t="inlineStr">
@@ -46802,7 +46804,7 @@
         <v>3203.783204735782</v>
       </c>
       <c r="L343" s="14" t="n">
-        <v>3784.745783447597</v>
+        <v>3784.745783447598</v>
       </c>
       <c r="M343" s="14" t="n">
         <v>4470.905568627126</v>
@@ -46817,7 +46819,7 @@
       </c>
       <c r="P343" s="14" t="inlineStr">
         <is>
-          <t>$3236693.361235794</t>
+          <t>$3236693.3612357937</t>
         </is>
       </c>
       <c r="Q343" s="14" t="inlineStr">
@@ -46827,7 +46829,7 @@
       </c>
       <c r="R343" s="14" t="inlineStr">
         <is>
-          <t>$4699091.65270347</t>
+          <t>$4699091.652703469</t>
         </is>
       </c>
       <c r="S343" s="14" t="inlineStr">
@@ -46837,7 +46839,7 @@
       </c>
       <c r="T343" s="14" t="inlineStr">
         <is>
-          <t>$6821659.419026629</t>
+          <t>$6821659.419026631</t>
         </is>
       </c>
       <c r="U343" s="14" t="inlineStr">
@@ -46942,7 +46944,7 @@
         <v>1.812094572814356</v>
       </c>
       <c r="L344" s="14" t="n">
-        <v>2.140693316429636</v>
+        <v>2.140693316429637</v>
       </c>
       <c r="M344" s="14" t="n">
         <v>2.528792742436157</v>
@@ -46957,7 +46959,7 @@
       </c>
       <c r="P344" s="14" t="inlineStr">
         <is>
-          <t>$1232.1848108360232</t>
+          <t>$1232.184810836023</t>
         </is>
       </c>
       <c r="Q344" s="14" t="inlineStr">
@@ -46967,7 +46969,7 @@
       </c>
       <c r="R344" s="14" t="inlineStr">
         <is>
-          <t>$1879.8838393850497</t>
+          <t>$1879.8838393850492</t>
         </is>
       </c>
       <c r="S344" s="14" t="inlineStr">
@@ -46977,7 +46979,7 @@
       </c>
       <c r="T344" s="14" t="inlineStr">
         <is>
-          <t>$2900.8836761311495</t>
+          <t>$2900.88367613115</t>
         </is>
       </c>
       <c r="U344" s="14" t="inlineStr">
@@ -47097,7 +47099,7 @@
       </c>
       <c r="P345" s="14" t="inlineStr">
         <is>
-          <t>$775682.4123377504</t>
+          <t>$775682.4123377502</t>
         </is>
       </c>
       <c r="Q345" s="14" t="inlineStr">
@@ -47107,7 +47109,7 @@
       </c>
       <c r="R345" s="14" t="inlineStr">
         <is>
-          <t>$934701.2145737815</t>
+          <t>$934701.2145737814</t>
         </is>
       </c>
       <c r="S345" s="14" t="inlineStr">
@@ -47117,7 +47119,7 @@
       </c>
       <c r="T345" s="14" t="inlineStr">
         <is>
-          <t>$1105928.5999518728</t>
+          <t>$1105928.599951873</t>
         </is>
       </c>
       <c r="U345" s="14" t="inlineStr">
@@ -47222,7 +47224,7 @@
         <v>3.979964406556381</v>
       </c>
       <c r="L346" s="14" t="n">
-        <v>4.23206704159971</v>
+        <v>4.232067041599711</v>
       </c>
       <c r="M346" s="14" t="n">
         <v>4.462278369161732</v>
@@ -47237,7 +47239,7 @@
       </c>
       <c r="P346" s="14" t="inlineStr">
         <is>
-          <t>$80737.74117345366</t>
+          <t>$80737.74117345363</t>
         </is>
       </c>
       <c r="Q346" s="14" t="inlineStr">
@@ -47247,7 +47249,7 @@
       </c>
       <c r="R346" s="14" t="inlineStr">
         <is>
-          <t>$100070.82239327134</t>
+          <t>$100070.82239327132</t>
         </is>
       </c>
       <c r="S346" s="14" t="inlineStr">
@@ -47257,7 +47259,7 @@
       </c>
       <c r="T346" s="14" t="inlineStr">
         <is>
-          <t>$122654.17053389517</t>
+          <t>$122654.1705338952</t>
         </is>
       </c>
       <c r="U346" s="14" t="inlineStr">
@@ -47362,7 +47364,7 @@
         <v>13.5318071663657</v>
       </c>
       <c r="L347" s="14" t="n">
-        <v>15.03731734977902</v>
+        <v>15.03731734977903</v>
       </c>
       <c r="M347" s="14" t="n">
         <v>16.70975645183177</v>
@@ -47377,7 +47379,7 @@
       </c>
       <c r="P347" s="14" t="inlineStr">
         <is>
-          <t>$651855.1196910358</t>
+          <t>$651855.1196910356</t>
         </is>
       </c>
       <c r="Q347" s="14" t="inlineStr">
@@ -47387,7 +47389,7 @@
       </c>
       <c r="R347" s="14" t="inlineStr">
         <is>
-          <t>$887469.5116994921</t>
+          <t>$887469.5116994919</t>
         </is>
       </c>
       <c r="S347" s="14" t="inlineStr">
@@ -47397,7 +47399,7 @@
       </c>
       <c r="T347" s="14" t="inlineStr">
         <is>
-          <t>$1208146.3936988444</t>
+          <t>$1208146.3936988446</t>
         </is>
       </c>
       <c r="U347" s="14" t="inlineStr">
@@ -47782,7 +47784,7 @@
         <v>5.78972302065707</v>
       </c>
       <c r="L350" s="14" t="n">
-        <v>5.680238698187805</v>
+        <v>5.680238698187806</v>
       </c>
       <c r="M350" s="14" t="n">
         <v>5.581903656331006</v>
@@ -47797,7 +47799,7 @@
       </c>
       <c r="P350" s="14" t="inlineStr">
         <is>
-          <t>$172615.39962841192</t>
+          <t>$172615.3996284119</t>
         </is>
       </c>
       <c r="Q350" s="14" t="inlineStr">
@@ -47807,7 +47809,7 @@
       </c>
       <c r="R350" s="14" t="inlineStr">
         <is>
-          <t>$180294.46830202744</t>
+          <t>$180294.46830202738</t>
         </is>
       </c>
       <c r="S350" s="14" t="inlineStr">
@@ -47817,7 +47819,7 @@
       </c>
       <c r="T350" s="14" t="inlineStr">
         <is>
-          <t>$191946.63917491015</t>
+          <t>$191946.63917491017</t>
         </is>
       </c>
       <c r="U350" s="14" t="inlineStr">
@@ -47937,7 +47939,7 @@
       </c>
       <c r="P351" s="14" t="inlineStr">
         <is>
-          <t>$41098.9046734314</t>
+          <t>$41098.904673431396</t>
         </is>
       </c>
       <c r="Q351" s="14" t="inlineStr">
@@ -47947,7 +47949,7 @@
       </c>
       <c r="R351" s="14" t="inlineStr">
         <is>
-          <t>$42927.25435762558</t>
+          <t>$42927.25435762557</t>
         </is>
       </c>
       <c r="S351" s="14" t="inlineStr">
@@ -47957,7 +47959,7 @@
       </c>
       <c r="T351" s="14" t="inlineStr">
         <is>
-          <t>$45701.58075593098</t>
+          <t>$45701.580755931</t>
         </is>
       </c>
       <c r="U351" s="14" t="inlineStr">
@@ -48077,7 +48079,7 @@
       </c>
       <c r="P352" s="14" t="inlineStr">
         <is>
-          <t>$41098.9046734314</t>
+          <t>$41098.904673431396</t>
         </is>
       </c>
       <c r="Q352" s="14" t="inlineStr">
@@ -48087,7 +48089,7 @@
       </c>
       <c r="R352" s="14" t="inlineStr">
         <is>
-          <t>$42927.25435762558</t>
+          <t>$42927.25435762557</t>
         </is>
       </c>
       <c r="S352" s="14" t="inlineStr">
@@ -48097,7 +48099,7 @@
       </c>
       <c r="T352" s="14" t="inlineStr">
         <is>
-          <t>$45701.58075593098</t>
+          <t>$45701.580755931</t>
         </is>
       </c>
       <c r="U352" s="14" t="inlineStr">
@@ -48202,7 +48204,7 @@
         <v>0.9649538367761784</v>
       </c>
       <c r="L353" s="14" t="n">
-        <v>0.9467064496979675</v>
+        <v>0.9467064496979677</v>
       </c>
       <c r="M353" s="14" t="n">
         <v>0.9303172760551676</v>
@@ -48217,7 +48219,7 @@
       </c>
       <c r="P353" s="14" t="inlineStr">
         <is>
-          <t>$8219.780934686281</t>
+          <t>$8219.78093468628</t>
         </is>
       </c>
       <c r="Q353" s="14" t="inlineStr">
@@ -48227,7 +48229,7 @@
       </c>
       <c r="R353" s="14" t="inlineStr">
         <is>
-          <t>$8585.450871525114</t>
+          <t>$8585.450871525112</t>
         </is>
       </c>
       <c r="S353" s="14" t="inlineStr">
@@ -48237,7 +48239,7 @@
       </c>
       <c r="T353" s="14" t="inlineStr">
         <is>
-          <t>$9140.316151186198</t>
+          <t>$9140.3161511862</t>
         </is>
       </c>
       <c r="U353" s="14" t="inlineStr">
@@ -48357,7 +48359,7 @@
       </c>
       <c r="P354" s="14" t="inlineStr">
         <is>
-          <t>$442101.48006859305</t>
+          <t>$442101.480068593</t>
         </is>
       </c>
       <c r="Q354" s="14" t="inlineStr">
@@ -48367,7 +48369,7 @@
       </c>
       <c r="R354" s="14" t="inlineStr">
         <is>
-          <t>$535695.3611598534</t>
+          <t>$535695.3611598533</t>
         </is>
       </c>
       <c r="S354" s="14" t="inlineStr">
@@ -48377,7 +48379,7 @@
       </c>
       <c r="T354" s="14" t="inlineStr">
         <is>
-          <t>$643002.9208978282</t>
+          <t>$643002.9208978283</t>
         </is>
       </c>
       <c r="U354" s="14" t="inlineStr">
@@ -48482,7 +48484,7 @@
         <v>1.393294497630826</v>
       </c>
       <c r="L355" s="14" t="n">
-        <v>1.512446288935718</v>
+        <v>1.512446288935719</v>
       </c>
       <c r="M355" s="14" t="n">
         <v>1.631117824908513</v>
@@ -48497,7 +48499,7 @@
       </c>
       <c r="P355" s="14" t="inlineStr">
         <is>
-          <t>$111352.17790316633</t>
+          <t>$111352.1779031663</t>
         </is>
       </c>
       <c r="Q355" s="14" t="inlineStr">
@@ -48507,7 +48509,7 @@
       </c>
       <c r="R355" s="14" t="inlineStr">
         <is>
-          <t>$143558.5250602496</t>
+          <t>$143558.52506024958</t>
         </is>
       </c>
       <c r="S355" s="14" t="inlineStr">
@@ -48517,7 +48519,7 @@
       </c>
       <c r="T355" s="14" t="inlineStr">
         <is>
-          <t>$184079.88912770306</t>
+          <t>$184079.88912770312</t>
         </is>
       </c>
       <c r="U355" s="14" t="inlineStr">
@@ -48637,7 +48639,7 @@
       </c>
       <c r="P356" s="14" t="inlineStr">
         <is>
-          <t>$116647.58053677504</t>
+          <t>$116647.58053677501</t>
         </is>
       </c>
       <c r="Q356" s="14" t="inlineStr">
@@ -48647,7 +48649,7 @@
       </c>
       <c r="R356" s="14" t="inlineStr">
         <is>
-          <t>$148059.40792616273</t>
+          <t>$148059.4079261627</t>
         </is>
       </c>
       <c r="S356" s="14" t="inlineStr">
@@ -48657,7 +48659,7 @@
       </c>
       <c r="T356" s="14" t="inlineStr">
         <is>
-          <t>$188313.10573411954</t>
+          <t>$188313.1057341196</t>
         </is>
       </c>
       <c r="U356" s="14" t="inlineStr">
@@ -48777,7 +48779,7 @@
       </c>
       <c r="P357" s="14" t="inlineStr">
         <is>
-          <t>$223772.90960116024</t>
+          <t>$223772.9096011602</t>
         </is>
       </c>
       <c r="Q357" s="14" t="inlineStr">
@@ -48787,7 +48789,7 @@
       </c>
       <c r="R357" s="14" t="inlineStr">
         <is>
-          <t>$284032.33357263874</t>
+          <t>$284032.3335726387</t>
         </is>
       </c>
       <c r="S357" s="14" t="inlineStr">
@@ -48797,7 +48799,7 @@
       </c>
       <c r="T357" s="14" t="inlineStr">
         <is>
-          <t>$361253.7130409641</t>
+          <t>$361253.7130409642</t>
         </is>
       </c>
       <c r="U357" s="14" t="inlineStr">
@@ -48902,7 +48904,7 @@
         <v>22.29271196209321</v>
       </c>
       <c r="L358" s="14" t="n">
-        <v>24.19914062297149</v>
+        <v>24.1991406229715</v>
       </c>
       <c r="M358" s="14" t="n">
         <v>26.0978851985362</v>
@@ -48917,7 +48919,7 @@
       </c>
       <c r="P358" s="14" t="inlineStr">
         <is>
-          <t>$257100.7897545246</t>
+          <t>$257100.78975452454</t>
         </is>
       </c>
       <c r="Q358" s="14" t="inlineStr">
@@ -48927,7 +48929,7 @@
       </c>
       <c r="R358" s="14" t="inlineStr">
         <is>
-          <t>$326335.02155154245</t>
+          <t>$326335.02155154233</t>
         </is>
       </c>
       <c r="S358" s="14" t="inlineStr">
@@ -48937,7 +48939,7 @@
       </c>
       <c r="T358" s="14" t="inlineStr">
         <is>
-          <t>$415057.4575364267</t>
+          <t>$415057.45753642684</t>
         </is>
       </c>
       <c r="U358" s="14" t="inlineStr">
@@ -49042,7 +49044,7 @@
         <v>2.653309604370921</v>
       </c>
       <c r="L359" s="14" t="n">
-        <v>2.82137802773314</v>
+        <v>2.821378027733141</v>
       </c>
       <c r="M359" s="14" t="n">
         <v>2.974852246107821</v>
@@ -49057,7 +49059,7 @@
       </c>
       <c r="P359" s="14" t="inlineStr">
         <is>
-          <t>$71674.86837869481</t>
+          <t>$71674.86837869478</t>
         </is>
       </c>
       <c r="Q359" s="14" t="inlineStr">
@@ -49067,7 +49069,7 @@
       </c>
       <c r="R359" s="14" t="inlineStr">
         <is>
-          <t>$84001.75751797689</t>
+          <t>$84001.75751797688</t>
         </is>
       </c>
       <c r="S359" s="14" t="inlineStr">
@@ -49077,7 +49079,7 @@
       </c>
       <c r="T359" s="14" t="inlineStr">
         <is>
-          <t>$96954.17254643734</t>
+          <t>$96954.17254643737</t>
         </is>
       </c>
       <c r="U359" s="14" t="inlineStr">
@@ -49197,7 +49199,7 @@
       </c>
       <c r="P360" s="14" t="inlineStr">
         <is>
-          <t>$244063.62337135884</t>
+          <t>$244063.6233713588</t>
         </is>
       </c>
       <c r="Q360" s="14" t="inlineStr">
@@ -49207,7 +49209,7 @@
       </c>
       <c r="R360" s="14" t="inlineStr">
         <is>
-          <t>$322584.38835407735</t>
+          <t>$322584.3883540773</t>
         </is>
       </c>
       <c r="S360" s="14" t="inlineStr">
@@ -49217,7 +49219,7 @@
       </c>
       <c r="T360" s="14" t="inlineStr">
         <is>
-          <t>$230702.06340243292</t>
+          <t>$230702.06340243295</t>
         </is>
       </c>
       <c r="U360" s="14" t="inlineStr">
@@ -49602,7 +49604,7 @@
         <v>0.7978420578880465</v>
       </c>
       <c r="L363" s="14" t="n">
-        <v>0.7039026018747564</v>
+        <v>0.7039026018747565</v>
       </c>
       <c r="M363" s="14" t="n">
         <v>0.6106367994429293</v>
@@ -49617,7 +49619,7 @@
       </c>
       <c r="P363" s="14" t="inlineStr">
         <is>
-          <t>$4941.68378264424</t>
+          <t>$4941.683782644239</t>
         </is>
       </c>
       <c r="Q363" s="14" t="inlineStr">
@@ -49627,7 +49629,7 @@
       </c>
       <c r="R363" s="14" t="inlineStr">
         <is>
-          <t>$4059.2602140398694</t>
+          <t>$4059.2602140398685</t>
         </is>
       </c>
       <c r="S363" s="14" t="inlineStr">
@@ -49637,7 +49639,7 @@
       </c>
       <c r="T363" s="14" t="inlineStr">
         <is>
-          <t>$3266.503640458772</t>
+          <t>$3266.5036404587727</t>
         </is>
       </c>
       <c r="U363" s="14" t="inlineStr">
@@ -49742,7 +49744,7 @@
         <v>0.7978420578880465</v>
       </c>
       <c r="L364" s="14" t="n">
-        <v>0.7039026018747564</v>
+        <v>0.7039026018747565</v>
       </c>
       <c r="M364" s="14" t="n">
         <v>0.6106367994429293</v>
@@ -49757,7 +49759,7 @@
       </c>
       <c r="P364" s="14" t="inlineStr">
         <is>
-          <t>$4941.838357338988</t>
+          <t>$4941.838357338987</t>
         </is>
       </c>
       <c r="Q364" s="14" t="inlineStr">
@@ -49767,7 +49769,7 @@
       </c>
       <c r="R364" s="14" t="inlineStr">
         <is>
-          <t>$4059.5810480404757</t>
+          <t>$4059.581048040475</t>
         </is>
       </c>
       <c r="S364" s="14" t="inlineStr">
@@ -49777,7 +49779,7 @@
       </c>
       <c r="T364" s="14" t="inlineStr">
         <is>
-          <t>$3266.9640026230254</t>
+          <t>$3266.964002623026</t>
         </is>
       </c>
       <c r="U364" s="14" t="inlineStr">
@@ -49897,7 +49899,7 @@
       </c>
       <c r="P365" s="14" t="inlineStr">
         <is>
-          <t>$413326.9332937043</t>
+          <t>$413326.9332937042</t>
         </is>
       </c>
       <c r="Q365" s="14" t="inlineStr">
@@ -49907,7 +49909,7 @@
       </c>
       <c r="R365" s="14" t="inlineStr">
         <is>
-          <t>$562724.8150421432</t>
+          <t>$562724.8150421431</t>
         </is>
       </c>
       <c r="S365" s="14" t="inlineStr">
@@ -49917,7 +49919,7 @@
       </c>
       <c r="T365" s="14" t="inlineStr">
         <is>
-          <t>$766058.942843122</t>
+          <t>$766058.9428431221</t>
         </is>
       </c>
       <c r="U365" s="14" t="inlineStr">
@@ -50037,7 +50039,7 @@
       </c>
       <c r="P366" s="14" t="inlineStr">
         <is>
-          <t>$81004.73937130663</t>
+          <t>$81004.73937130661</t>
         </is>
       </c>
       <c r="Q366" s="14" t="inlineStr">
@@ -50047,7 +50049,7 @@
       </c>
       <c r="R366" s="14" t="inlineStr">
         <is>
-          <t>$93607.42504233921</t>
+          <t>$93607.4250423392</t>
         </is>
       </c>
       <c r="S366" s="14" t="inlineStr">
@@ -50057,7 +50059,7 @@
       </c>
       <c r="T366" s="14" t="inlineStr">
         <is>
-          <t>$107585.60363113359</t>
+          <t>$107585.60363113362</t>
         </is>
       </c>
       <c r="U366" s="14" t="inlineStr">
